--- a/Шаблон ЛМК проф ОПО — Машково и Руднево.xlsx
+++ b/Шаблон ЛМК проф ОПО — Машково и Руднево.xlsx
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -330,7 +329,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -579,7 +578,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -587,6 +586,9 @@
     </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1225,11 +1227,11 @@
       <c r="AB3" s="71" t="n"/>
       <c r="AC3" s="71" t="n"/>
       <c r="AD3" s="71" t="n"/>
-      <c r="AE3" s="88" t="n">
+      <c r="AE3" s="91" t="n">
         <v>45098</v>
       </c>
-      <c r="AF3" s="88" t="n"/>
-      <c r="AG3" s="88" t="n"/>
+      <c r="AF3" s="91" t="n"/>
+      <c r="AG3" s="91" t="n"/>
       <c r="AH3" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -1303,11 +1305,11 @@
       <c r="AB4" s="71" t="n"/>
       <c r="AC4" s="71" t="n"/>
       <c r="AD4" s="70" t="n"/>
-      <c r="AE4" s="88" t="n">
+      <c r="AE4" s="91" t="n">
         <v>42849</v>
       </c>
-      <c r="AF4" s="88" t="n"/>
-      <c r="AG4" s="88" t="n"/>
+      <c r="AF4" s="91" t="n"/>
+      <c r="AG4" s="91" t="n"/>
       <c r="AH4" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -1381,11 +1383,11 @@
       <c r="AB5" s="71" t="n"/>
       <c r="AC5" s="71" t="n"/>
       <c r="AD5" s="70" t="n"/>
-      <c r="AE5" s="88" t="n">
+      <c r="AE5" s="91" t="n">
         <v>45698</v>
       </c>
-      <c r="AF5" s="88" t="n"/>
-      <c r="AG5" s="88" t="n"/>
+      <c r="AF5" s="91" t="n"/>
+      <c r="AG5" s="91" t="n"/>
       <c r="AH5" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -1459,11 +1461,11 @@
       <c r="AB6" s="71" t="n"/>
       <c r="AC6" s="71" t="n"/>
       <c r="AD6" s="70" t="n"/>
-      <c r="AE6" s="88" t="n">
+      <c r="AE6" s="91" t="n">
         <v>46086</v>
       </c>
-      <c r="AF6" s="88" t="n"/>
-      <c r="AG6" s="88" t="n"/>
+      <c r="AF6" s="91" t="n"/>
+      <c r="AG6" s="91" t="n"/>
       <c r="AH6" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -1537,11 +1539,11 @@
       <c r="AB7" s="71" t="n"/>
       <c r="AC7" s="71" t="n"/>
       <c r="AD7" s="70" t="n"/>
-      <c r="AE7" s="88" t="n">
+      <c r="AE7" s="91" t="n">
         <v>45978</v>
       </c>
-      <c r="AF7" s="88" t="n"/>
-      <c r="AG7" s="88" t="n"/>
+      <c r="AF7" s="91" t="n"/>
+      <c r="AG7" s="91" t="n"/>
       <c r="AH7" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -1615,11 +1617,11 @@
       <c r="AB8" s="71" t="n"/>
       <c r="AC8" s="71" t="n"/>
       <c r="AD8" s="70" t="n"/>
-      <c r="AE8" s="88" t="n">
+      <c r="AE8" s="91" t="n">
         <v>45936</v>
       </c>
-      <c r="AF8" s="88" t="n"/>
-      <c r="AG8" s="88" t="n"/>
+      <c r="AF8" s="91" t="n"/>
+      <c r="AG8" s="91" t="n"/>
       <c r="AH8" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -1693,11 +1695,11 @@
       <c r="AB9" s="71" t="n"/>
       <c r="AC9" s="71" t="n"/>
       <c r="AD9" s="70" t="n"/>
-      <c r="AE9" s="88" t="n">
+      <c r="AE9" s="91" t="n">
         <v>45930</v>
       </c>
-      <c r="AF9" s="88" t="n"/>
-      <c r="AG9" s="88" t="n"/>
+      <c r="AF9" s="91" t="n"/>
+      <c r="AG9" s="91" t="n"/>
       <c r="AH9" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -1771,11 +1773,11 @@
       <c r="AB10" s="71" t="n"/>
       <c r="AC10" s="71" t="n"/>
       <c r="AD10" s="70" t="n"/>
-      <c r="AE10" s="88" t="n">
+      <c r="AE10" s="91" t="n">
         <v>46237</v>
       </c>
-      <c r="AF10" s="88" t="n"/>
-      <c r="AG10" s="88" t="n"/>
+      <c r="AF10" s="91" t="n"/>
+      <c r="AG10" s="91" t="n"/>
       <c r="AH10" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -1849,11 +1851,11 @@
       <c r="AB11" s="71" t="n"/>
       <c r="AC11" s="71" t="n"/>
       <c r="AD11" s="70" t="n"/>
-      <c r="AE11" s="88" t="n">
+      <c r="AE11" s="91" t="n">
         <v>45999</v>
       </c>
-      <c r="AF11" s="88" t="n"/>
-      <c r="AG11" s="88" t="n"/>
+      <c r="AF11" s="91" t="n"/>
+      <c r="AG11" s="91" t="n"/>
       <c r="AH11" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -1927,11 +1929,11 @@
       <c r="AB12" s="71" t="n"/>
       <c r="AC12" s="71" t="n"/>
       <c r="AD12" s="70" t="n"/>
-      <c r="AE12" s="88" t="n">
+      <c r="AE12" s="91" t="n">
         <v>45719</v>
       </c>
-      <c r="AF12" s="88" t="n"/>
-      <c r="AG12" s="88" t="n"/>
+      <c r="AF12" s="91" t="n"/>
+      <c r="AG12" s="91" t="n"/>
       <c r="AH12" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2005,11 +2007,11 @@
       <c r="AB13" s="71" t="n"/>
       <c r="AC13" s="71" t="n"/>
       <c r="AD13" s="70" t="n"/>
-      <c r="AE13" s="88" t="n">
+      <c r="AE13" s="91" t="n">
         <v>42494</v>
       </c>
-      <c r="AF13" s="88" t="n"/>
-      <c r="AG13" s="88" t="n"/>
+      <c r="AF13" s="91" t="n"/>
+      <c r="AG13" s="91" t="n"/>
       <c r="AH13" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2083,11 +2085,11 @@
       <c r="AB14" s="71" t="n"/>
       <c r="AC14" s="71" t="n"/>
       <c r="AD14" s="70" t="n"/>
-      <c r="AE14" s="88" t="n">
+      <c r="AE14" s="91" t="n">
         <v>45616</v>
       </c>
-      <c r="AF14" s="88" t="n"/>
-      <c r="AG14" s="88" t="n"/>
+      <c r="AF14" s="91" t="n"/>
+      <c r="AG14" s="91" t="n"/>
       <c r="AH14" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2161,11 +2163,11 @@
       <c r="AB15" s="71" t="n"/>
       <c r="AC15" s="71" t="n"/>
       <c r="AD15" s="70" t="n"/>
-      <c r="AE15" s="88" t="n">
+      <c r="AE15" s="91" t="n">
         <v>45159</v>
       </c>
-      <c r="AF15" s="88" t="n"/>
-      <c r="AG15" s="88" t="n"/>
+      <c r="AF15" s="91" t="n"/>
+      <c r="AG15" s="91" t="n"/>
       <c r="AH15" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2239,11 +2241,11 @@
       <c r="AB16" s="71" t="n"/>
       <c r="AC16" s="71" t="n"/>
       <c r="AD16" s="70" t="n"/>
-      <c r="AE16" s="88" t="n">
+      <c r="AE16" s="91" t="n">
         <v>43132</v>
       </c>
-      <c r="AF16" s="88" t="n"/>
-      <c r="AG16" s="88" t="n"/>
+      <c r="AF16" s="91" t="n"/>
+      <c r="AG16" s="91" t="n"/>
       <c r="AH16" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2317,11 +2319,11 @@
       <c r="AB17" s="71" t="n"/>
       <c r="AC17" s="71" t="n"/>
       <c r="AD17" s="70" t="n"/>
-      <c r="AE17" s="88" t="n">
+      <c r="AE17" s="91" t="n">
         <v>43276</v>
       </c>
-      <c r="AF17" s="88" t="n"/>
-      <c r="AG17" s="88" t="n"/>
+      <c r="AF17" s="91" t="n"/>
+      <c r="AG17" s="91" t="n"/>
       <c r="AH17" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2395,11 +2397,11 @@
       <c r="AB18" s="71" t="n"/>
       <c r="AC18" s="71" t="n"/>
       <c r="AD18" s="70" t="n"/>
-      <c r="AE18" s="88" t="n">
+      <c r="AE18" s="91" t="n">
         <v>45768</v>
       </c>
-      <c r="AF18" s="88" t="n"/>
-      <c r="AG18" s="88" t="n"/>
+      <c r="AF18" s="91" t="n"/>
+      <c r="AG18" s="91" t="n"/>
       <c r="AH18" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2473,11 +2475,11 @@
       <c r="AB19" s="71" t="n"/>
       <c r="AC19" s="71" t="n"/>
       <c r="AD19" s="70" t="n"/>
-      <c r="AE19" s="88" t="n">
+      <c r="AE19" s="91" t="n">
         <v>39359</v>
       </c>
-      <c r="AF19" s="88" t="n"/>
-      <c r="AG19" s="88" t="n"/>
+      <c r="AF19" s="91" t="n"/>
+      <c r="AG19" s="91" t="n"/>
       <c r="AH19" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2551,11 +2553,11 @@
       <c r="AB20" s="71" t="n"/>
       <c r="AC20" s="71" t="n"/>
       <c r="AD20" s="70" t="n"/>
-      <c r="AE20" s="88" t="n">
+      <c r="AE20" s="91" t="n">
         <v>45623</v>
       </c>
-      <c r="AF20" s="88" t="n"/>
-      <c r="AG20" s="88" t="n"/>
+      <c r="AF20" s="91" t="n"/>
+      <c r="AG20" s="91" t="n"/>
       <c r="AH20" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2629,11 +2631,11 @@
       <c r="AB21" s="71" t="n"/>
       <c r="AC21" s="71" t="n"/>
       <c r="AD21" s="70" t="n"/>
-      <c r="AE21" s="88" t="n">
+      <c r="AE21" s="91" t="n">
         <v>42570</v>
       </c>
-      <c r="AF21" s="88" t="n"/>
-      <c r="AG21" s="88" t="n"/>
+      <c r="AF21" s="91" t="n"/>
+      <c r="AG21" s="91" t="n"/>
       <c r="AH21" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2707,11 +2709,11 @@
       <c r="AB22" s="71" t="n"/>
       <c r="AC22" s="71" t="n"/>
       <c r="AD22" s="70" t="n"/>
-      <c r="AE22" s="88" t="n">
+      <c r="AE22" s="91" t="n">
         <v>46149</v>
       </c>
-      <c r="AF22" s="88" t="n"/>
-      <c r="AG22" s="88" t="n"/>
+      <c r="AF22" s="91" t="n"/>
+      <c r="AG22" s="91" t="n"/>
       <c r="AH22" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2785,11 +2787,11 @@
       <c r="AB23" s="71" t="n"/>
       <c r="AC23" s="71" t="n"/>
       <c r="AD23" s="70" t="n"/>
-      <c r="AE23" s="88" t="n">
+      <c r="AE23" s="91" t="n">
         <v>46106</v>
       </c>
-      <c r="AF23" s="88" t="n"/>
-      <c r="AG23" s="88" t="n"/>
+      <c r="AF23" s="91" t="n"/>
+      <c r="AG23" s="91" t="n"/>
       <c r="AH23" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2863,11 +2865,11 @@
       <c r="AB24" s="71" t="n"/>
       <c r="AC24" s="71" t="n"/>
       <c r="AD24" s="70" t="n"/>
-      <c r="AE24" s="88" t="n">
+      <c r="AE24" s="91" t="n">
         <v>42614</v>
       </c>
-      <c r="AF24" s="88" t="n"/>
-      <c r="AG24" s="88" t="n"/>
+      <c r="AF24" s="91" t="n"/>
+      <c r="AG24" s="91" t="n"/>
       <c r="AH24" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -2941,11 +2943,11 @@
       <c r="AB25" s="71" t="n"/>
       <c r="AC25" s="71" t="n"/>
       <c r="AD25" s="70" t="n"/>
-      <c r="AE25" s="88" t="n">
+      <c r="AE25" s="91" t="n">
         <v>41381</v>
       </c>
-      <c r="AF25" s="88" t="n"/>
-      <c r="AG25" s="88" t="n"/>
+      <c r="AF25" s="91" t="n"/>
+      <c r="AG25" s="91" t="n"/>
       <c r="AH25" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -3019,11 +3021,11 @@
       <c r="AB26" s="71" t="n"/>
       <c r="AC26" s="71" t="n"/>
       <c r="AD26" s="70" t="n"/>
-      <c r="AE26" s="88" t="n">
+      <c r="AE26" s="91" t="n">
         <v>44655</v>
       </c>
-      <c r="AF26" s="88" t="n"/>
-      <c r="AG26" s="88" t="n"/>
+      <c r="AF26" s="91" t="n"/>
+      <c r="AG26" s="91" t="n"/>
       <c r="AH26" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -3097,11 +3099,11 @@
       <c r="AB27" s="71" t="n"/>
       <c r="AC27" s="71" t="n"/>
       <c r="AD27" s="70" t="n"/>
-      <c r="AE27" s="88" t="n">
+      <c r="AE27" s="91" t="n">
         <v>45593</v>
       </c>
-      <c r="AF27" s="88" t="n"/>
-      <c r="AG27" s="88" t="n"/>
+      <c r="AF27" s="91" t="n"/>
+      <c r="AG27" s="91" t="n"/>
       <c r="AH27" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -3175,11 +3177,11 @@
       <c r="AB28" s="71" t="n"/>
       <c r="AC28" s="71" t="n"/>
       <c r="AD28" s="70" t="n"/>
-      <c r="AE28" s="88" t="n">
+      <c r="AE28" s="91" t="n">
         <v>41295</v>
       </c>
-      <c r="AF28" s="88" t="n"/>
-      <c r="AG28" s="88" t="n"/>
+      <c r="AF28" s="91" t="n"/>
+      <c r="AG28" s="91" t="n"/>
       <c r="AH28" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -3253,11 +3255,11 @@
       <c r="AB29" s="71" t="n"/>
       <c r="AC29" s="71" t="n"/>
       <c r="AD29" s="70" t="n"/>
-      <c r="AE29" s="88" t="n">
+      <c r="AE29" s="91" t="n">
         <v>39419</v>
       </c>
-      <c r="AF29" s="88" t="n"/>
-      <c r="AG29" s="88" t="n"/>
+      <c r="AF29" s="91" t="n"/>
+      <c r="AG29" s="91" t="n"/>
       <c r="AH29" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -3331,11 +3333,11 @@
       <c r="AB30" s="71" t="n"/>
       <c r="AC30" s="71" t="n"/>
       <c r="AD30" s="70" t="n"/>
-      <c r="AE30" s="88" t="n">
+      <c r="AE30" s="91" t="n">
         <v>42461</v>
       </c>
-      <c r="AF30" s="88" t="n"/>
-      <c r="AG30" s="88" t="n"/>
+      <c r="AF30" s="91" t="n"/>
+      <c r="AG30" s="91" t="n"/>
       <c r="AH30" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -3409,11 +3411,11 @@
       <c r="AB31" s="71" t="n"/>
       <c r="AC31" s="71" t="n"/>
       <c r="AD31" s="70" t="n"/>
-      <c r="AE31" s="88" t="n">
+      <c r="AE31" s="91" t="n">
         <v>40148</v>
       </c>
-      <c r="AF31" s="88" t="n"/>
-      <c r="AG31" s="88" t="n"/>
+      <c r="AF31" s="91" t="n"/>
+      <c r="AG31" s="91" t="n"/>
       <c r="AH31" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -3487,11 +3489,11 @@
       <c r="AB32" s="71" t="n"/>
       <c r="AC32" s="71" t="n"/>
       <c r="AD32" s="70" t="n"/>
-      <c r="AE32" s="88" t="n">
+      <c r="AE32" s="91" t="n">
         <v>44636</v>
       </c>
-      <c r="AF32" s="88" t="n"/>
-      <c r="AG32" s="88" t="n"/>
+      <c r="AF32" s="91" t="n"/>
+      <c r="AG32" s="91" t="n"/>
       <c r="AH32" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -3565,11 +3567,11 @@
       <c r="AB33" s="71" t="n"/>
       <c r="AC33" s="71" t="n"/>
       <c r="AD33" s="70" t="n"/>
-      <c r="AE33" s="88" t="n">
+      <c r="AE33" s="91" t="n">
         <v>46163</v>
       </c>
-      <c r="AF33" s="88" t="n"/>
-      <c r="AG33" s="88" t="n"/>
+      <c r="AF33" s="91" t="n"/>
+      <c r="AG33" s="91" t="n"/>
       <c r="AH33" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -3643,11 +3645,11 @@
       <c r="AB34" s="71" t="n"/>
       <c r="AC34" s="71" t="n"/>
       <c r="AD34" s="70" t="n"/>
-      <c r="AE34" s="88" t="n">
+      <c r="AE34" s="91" t="n">
         <v>45688</v>
       </c>
-      <c r="AF34" s="88" t="n"/>
-      <c r="AG34" s="88" t="n"/>
+      <c r="AF34" s="91" t="n"/>
+      <c r="AG34" s="91" t="n"/>
       <c r="AH34" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -3721,13 +3723,13 @@
       <c r="AB35" s="71" t="n"/>
       <c r="AC35" s="71" t="n"/>
       <c r="AD35" s="70" t="n"/>
-      <c r="AE35" s="88" t="n">
+      <c r="AE35" s="91" t="n">
         <v>45812</v>
       </c>
-      <c r="AF35" s="88" t="n">
+      <c r="AF35" s="91" t="n">
         <v>45803</v>
       </c>
-      <c r="AG35" s="88" t="n">
+      <c r="AG35" s="91" t="n">
         <v>46168</v>
       </c>
       <c r="AH35" s="6" t="inlineStr">
@@ -3803,11 +3805,11 @@
       <c r="AB36" s="71" t="n"/>
       <c r="AC36" s="71" t="n"/>
       <c r="AD36" s="70" t="n"/>
-      <c r="AE36" s="88" t="n">
+      <c r="AE36" s="91" t="n">
         <v>39753</v>
       </c>
-      <c r="AF36" s="88" t="n"/>
-      <c r="AG36" s="88" t="n"/>
+      <c r="AF36" s="91" t="n"/>
+      <c r="AG36" s="91" t="n"/>
       <c r="AH36" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -3881,11 +3883,11 @@
       <c r="AB37" s="71" t="n"/>
       <c r="AC37" s="71" t="n"/>
       <c r="AD37" s="70" t="n"/>
-      <c r="AE37" s="88" t="n">
+      <c r="AE37" s="91" t="n">
         <v>38363</v>
       </c>
-      <c r="AF37" s="88" t="n"/>
-      <c r="AG37" s="88" t="n"/>
+      <c r="AF37" s="91" t="n"/>
+      <c r="AG37" s="91" t="n"/>
       <c r="AH37" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -3959,11 +3961,11 @@
       <c r="AB38" s="71" t="n"/>
       <c r="AC38" s="71" t="n"/>
       <c r="AD38" s="70" t="n"/>
-      <c r="AE38" s="88" t="n">
+      <c r="AE38" s="91" t="n">
         <v>45832</v>
       </c>
-      <c r="AF38" s="88" t="n"/>
-      <c r="AG38" s="88" t="n"/>
+      <c r="AF38" s="91" t="n"/>
+      <c r="AG38" s="91" t="n"/>
       <c r="AH38" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4037,11 +4039,11 @@
       <c r="AB39" s="71" t="n"/>
       <c r="AC39" s="71" t="n"/>
       <c r="AD39" s="70" t="n"/>
-      <c r="AE39" s="88" t="n">
+      <c r="AE39" s="91" t="n">
         <v>43678</v>
       </c>
-      <c r="AF39" s="88" t="n"/>
-      <c r="AG39" s="88" t="n"/>
+      <c r="AF39" s="91" t="n"/>
+      <c r="AG39" s="91" t="n"/>
       <c r="AH39" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4115,11 +4117,11 @@
       <c r="AB40" s="71" t="n"/>
       <c r="AC40" s="71" t="n"/>
       <c r="AD40" s="70" t="n"/>
-      <c r="AE40" s="88" t="n">
+      <c r="AE40" s="91" t="n">
         <v>40926</v>
       </c>
-      <c r="AF40" s="88" t="n"/>
-      <c r="AG40" s="88" t="n"/>
+      <c r="AF40" s="91" t="n"/>
+      <c r="AG40" s="91" t="n"/>
       <c r="AH40" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4193,11 +4195,11 @@
       <c r="AB41" s="71" t="n"/>
       <c r="AC41" s="71" t="n"/>
       <c r="AD41" s="70" t="n"/>
-      <c r="AE41" s="88" t="n">
+      <c r="AE41" s="91" t="n">
         <v>46036</v>
       </c>
-      <c r="AF41" s="88" t="n"/>
-      <c r="AG41" s="88" t="n"/>
+      <c r="AF41" s="91" t="n"/>
+      <c r="AG41" s="91" t="n"/>
       <c r="AH41" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4271,11 +4273,11 @@
       <c r="AB42" s="71" t="n"/>
       <c r="AC42" s="71" t="n"/>
       <c r="AD42" s="70" t="n"/>
-      <c r="AE42" s="88" t="n">
+      <c r="AE42" s="91" t="n">
         <v>43046</v>
       </c>
-      <c r="AF42" s="88" t="n"/>
-      <c r="AG42" s="88" t="n"/>
+      <c r="AF42" s="91" t="n"/>
+      <c r="AG42" s="91" t="n"/>
       <c r="AH42" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4349,11 +4351,11 @@
       <c r="AB43" s="71" t="n"/>
       <c r="AC43" s="71" t="n"/>
       <c r="AD43" s="70" t="n"/>
-      <c r="AE43" s="88" t="n">
+      <c r="AE43" s="91" t="n">
         <v>39356</v>
       </c>
-      <c r="AF43" s="88" t="n"/>
-      <c r="AG43" s="88" t="n"/>
+      <c r="AF43" s="91" t="n"/>
+      <c r="AG43" s="91" t="n"/>
       <c r="AH43" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4427,11 +4429,11 @@
       <c r="AB44" s="71" t="n"/>
       <c r="AC44" s="71" t="n"/>
       <c r="AD44" s="70" t="n"/>
-      <c r="AE44" s="88" t="n">
+      <c r="AE44" s="91" t="n">
         <v>38810</v>
       </c>
-      <c r="AF44" s="88" t="n"/>
-      <c r="AG44" s="88" t="n"/>
+      <c r="AF44" s="91" t="n"/>
+      <c r="AG44" s="91" t="n"/>
       <c r="AH44" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4505,11 +4507,11 @@
       <c r="AB45" s="71" t="n"/>
       <c r="AC45" s="71" t="n"/>
       <c r="AD45" s="70" t="n"/>
-      <c r="AE45" s="88" t="n">
+      <c r="AE45" s="91" t="n">
         <v>46051</v>
       </c>
-      <c r="AF45" s="88" t="n"/>
-      <c r="AG45" s="88" t="n"/>
+      <c r="AF45" s="91" t="n"/>
+      <c r="AG45" s="91" t="n"/>
       <c r="AH45" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4583,11 +4585,11 @@
       <c r="AB46" s="71" t="n"/>
       <c r="AC46" s="71" t="n"/>
       <c r="AD46" s="70" t="n"/>
-      <c r="AE46" s="88" t="n">
+      <c r="AE46" s="91" t="n">
         <v>38728</v>
       </c>
-      <c r="AF46" s="88" t="n"/>
-      <c r="AG46" s="88" t="n"/>
+      <c r="AF46" s="91" t="n"/>
+      <c r="AG46" s="91" t="n"/>
       <c r="AH46" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4661,11 +4663,11 @@
       <c r="AB47" s="71" t="n"/>
       <c r="AC47" s="71" t="n"/>
       <c r="AD47" s="70" t="n"/>
-      <c r="AE47" s="88" t="n">
+      <c r="AE47" s="91" t="n">
         <v>45125</v>
       </c>
-      <c r="AF47" s="88" t="n"/>
-      <c r="AG47" s="88" t="n"/>
+      <c r="AF47" s="91" t="n"/>
+      <c r="AG47" s="91" t="n"/>
       <c r="AH47" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4739,11 +4741,11 @@
       <c r="AB48" s="71" t="n"/>
       <c r="AC48" s="71" t="n"/>
       <c r="AD48" s="70" t="n"/>
-      <c r="AE48" s="88" t="n">
+      <c r="AE48" s="91" t="n">
         <v>38810</v>
       </c>
-      <c r="AF48" s="88" t="n"/>
-      <c r="AG48" s="88" t="n"/>
+      <c r="AF48" s="91" t="n"/>
+      <c r="AG48" s="91" t="n"/>
       <c r="AH48" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4817,11 +4819,11 @@
       <c r="AB49" s="71" t="n"/>
       <c r="AC49" s="71" t="n"/>
       <c r="AD49" s="70" t="n"/>
-      <c r="AE49" s="88" t="n">
+      <c r="AE49" s="91" t="n">
         <v>45688</v>
       </c>
-      <c r="AF49" s="88" t="n"/>
-      <c r="AG49" s="88" t="n"/>
+      <c r="AF49" s="91" t="n"/>
+      <c r="AG49" s="91" t="n"/>
       <c r="AH49" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4895,11 +4897,11 @@
       <c r="AB50" s="71" t="n"/>
       <c r="AC50" s="71" t="n"/>
       <c r="AD50" s="70" t="n"/>
-      <c r="AE50" s="88" t="n">
+      <c r="AE50" s="91" t="n">
         <v>45509</v>
       </c>
-      <c r="AF50" s="88" t="n"/>
-      <c r="AG50" s="88" t="n"/>
+      <c r="AF50" s="91" t="n"/>
+      <c r="AG50" s="91" t="n"/>
       <c r="AH50" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -4973,11 +4975,11 @@
       <c r="AB51" s="71" t="n"/>
       <c r="AC51" s="71" t="n"/>
       <c r="AD51" s="70" t="n"/>
-      <c r="AE51" s="88" t="n">
+      <c r="AE51" s="91" t="n">
         <v>45565</v>
       </c>
-      <c r="AF51" s="88" t="n"/>
-      <c r="AG51" s="88" t="n"/>
+      <c r="AF51" s="91" t="n"/>
+      <c r="AG51" s="91" t="n"/>
       <c r="AH51" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -5051,11 +5053,11 @@
       <c r="AB52" s="71" t="n"/>
       <c r="AC52" s="71" t="n"/>
       <c r="AD52" s="70" t="n"/>
-      <c r="AE52" s="88" t="n">
+      <c r="AE52" s="91" t="n">
         <v>45691</v>
       </c>
-      <c r="AF52" s="88" t="n"/>
-      <c r="AG52" s="88" t="n"/>
+      <c r="AF52" s="91" t="n"/>
+      <c r="AG52" s="91" t="n"/>
       <c r="AH52" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -5129,11 +5131,11 @@
       <c r="AB53" s="71" t="n"/>
       <c r="AC53" s="71" t="n"/>
       <c r="AD53" s="70" t="n"/>
-      <c r="AE53" s="88" t="n">
+      <c r="AE53" s="91" t="n">
         <v>45362</v>
       </c>
-      <c r="AF53" s="88" t="n"/>
-      <c r="AG53" s="88" t="n"/>
+      <c r="AF53" s="91" t="n"/>
+      <c r="AG53" s="91" t="n"/>
       <c r="AH53" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -5207,11 +5209,11 @@
       <c r="AB54" s="71" t="n"/>
       <c r="AC54" s="71" t="n"/>
       <c r="AD54" s="70" t="n"/>
-      <c r="AE54" s="88" t="n">
+      <c r="AE54" s="91" t="n">
         <v>45917</v>
       </c>
-      <c r="AF54" s="88" t="n"/>
-      <c r="AG54" s="88" t="n"/>
+      <c r="AF54" s="91" t="n"/>
+      <c r="AG54" s="91" t="n"/>
       <c r="AH54" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -5285,11 +5287,11 @@
       <c r="AB55" s="71" t="n"/>
       <c r="AC55" s="71" t="n"/>
       <c r="AD55" s="70" t="n"/>
-      <c r="AE55" s="88" t="n">
+      <c r="AE55" s="91" t="n">
         <v>45922</v>
       </c>
-      <c r="AF55" s="88" t="n"/>
-      <c r="AG55" s="88" t="n"/>
+      <c r="AF55" s="91" t="n"/>
+      <c r="AG55" s="91" t="n"/>
       <c r="AH55" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -5363,11 +5365,11 @@
       <c r="AB56" s="71" t="n"/>
       <c r="AC56" s="71" t="n"/>
       <c r="AD56" s="70" t="n"/>
-      <c r="AE56" s="88" t="n">
+      <c r="AE56" s="91" t="n">
         <v>45454</v>
       </c>
-      <c r="AF56" s="88" t="n"/>
-      <c r="AG56" s="88" t="n"/>
+      <c r="AF56" s="91" t="n"/>
+      <c r="AG56" s="91" t="n"/>
       <c r="AH56" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -5441,11 +5443,11 @@
       <c r="AB57" s="71" t="n"/>
       <c r="AC57" s="71" t="n"/>
       <c r="AD57" s="70" t="n"/>
-      <c r="AE57" s="88" t="n">
+      <c r="AE57" s="91" t="n">
         <v>45638</v>
       </c>
-      <c r="AF57" s="88" t="n"/>
-      <c r="AG57" s="88" t="n"/>
+      <c r="AF57" s="91" t="n"/>
+      <c r="AG57" s="91" t="n"/>
       <c r="AH57" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -5519,11 +5521,11 @@
       <c r="AB58" s="71" t="n"/>
       <c r="AC58" s="71" t="n"/>
       <c r="AD58" s="70" t="n"/>
-      <c r="AE58" s="88" t="n">
+      <c r="AE58" s="91" t="n">
         <v>45792</v>
       </c>
-      <c r="AF58" s="88" t="n"/>
-      <c r="AG58" s="88" t="n"/>
+      <c r="AF58" s="91" t="n"/>
+      <c r="AG58" s="91" t="n"/>
       <c r="AH58" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -5597,13 +5599,13 @@
       <c r="AB59" s="71" t="n"/>
       <c r="AC59" s="71" t="n"/>
       <c r="AD59" s="70" t="n"/>
-      <c r="AE59" s="88" t="n">
+      <c r="AE59" s="91" t="n">
         <v>45924</v>
       </c>
-      <c r="AF59" s="88" t="n">
+      <c r="AF59" s="91" t="n">
         <v>45882</v>
       </c>
-      <c r="AG59" s="88" t="n">
+      <c r="AG59" s="91" t="n">
         <v>46247</v>
       </c>
       <c r="AH59" s="6" t="inlineStr">
@@ -5679,13 +5681,13 @@
       <c r="AB60" s="71" t="n"/>
       <c r="AC60" s="71" t="n"/>
       <c r="AD60" s="70" t="n"/>
-      <c r="AE60" s="88" t="n">
+      <c r="AE60" s="91" t="n">
         <v>45930</v>
       </c>
-      <c r="AF60" s="88" t="n">
+      <c r="AF60" s="91" t="n">
         <v>45916</v>
       </c>
-      <c r="AG60" s="88" t="n">
+      <c r="AG60" s="91" t="n">
         <v>46281</v>
       </c>
       <c r="AH60" s="6" t="inlineStr">
@@ -5761,13 +5763,13 @@
       <c r="AB61" s="71" t="n"/>
       <c r="AC61" s="71" t="n"/>
       <c r="AD61" s="70" t="n"/>
-      <c r="AE61" s="88" t="n">
+      <c r="AE61" s="91" t="n">
         <v>45840</v>
       </c>
-      <c r="AF61" s="88" t="n">
+      <c r="AF61" s="91" t="n">
         <v>45835</v>
       </c>
-      <c r="AG61" s="88" t="n">
+      <c r="AG61" s="91" t="n">
         <v>46200</v>
       </c>
       <c r="AH61" s="6" t="inlineStr">
@@ -5843,11 +5845,11 @@
       <c r="AB62" s="71" t="n"/>
       <c r="AC62" s="71" t="n"/>
       <c r="AD62" s="70" t="n"/>
-      <c r="AE62" s="88" t="n">
+      <c r="AE62" s="91" t="n">
         <v>44692</v>
       </c>
-      <c r="AF62" s="88" t="n"/>
-      <c r="AG62" s="88" t="n"/>
+      <c r="AF62" s="91" t="n"/>
+      <c r="AG62" s="91" t="n"/>
       <c r="AH62" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -5921,11 +5923,11 @@
       <c r="AB63" s="71" t="n"/>
       <c r="AC63" s="71" t="n"/>
       <c r="AD63" s="70" t="n"/>
-      <c r="AE63" s="88" t="n">
+      <c r="AE63" s="91" t="n">
         <v>45212</v>
       </c>
-      <c r="AF63" s="88" t="n"/>
-      <c r="AG63" s="88" t="n"/>
+      <c r="AF63" s="91" t="n"/>
+      <c r="AG63" s="91" t="n"/>
       <c r="AH63" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -5999,11 +6001,11 @@
       <c r="AB64" s="71" t="n"/>
       <c r="AC64" s="71" t="n"/>
       <c r="AD64" s="70" t="n"/>
-      <c r="AE64" s="88" t="n">
+      <c r="AE64" s="91" t="n">
         <v>39615</v>
       </c>
-      <c r="AF64" s="88" t="n"/>
-      <c r="AG64" s="88" t="n"/>
+      <c r="AF64" s="91" t="n"/>
+      <c r="AG64" s="91" t="n"/>
       <c r="AH64" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -6077,11 +6079,11 @@
       <c r="AB65" s="71" t="n"/>
       <c r="AC65" s="71" t="n"/>
       <c r="AD65" s="70" t="n"/>
-      <c r="AE65" s="88" t="n">
+      <c r="AE65" s="91" t="n">
         <v>45938</v>
       </c>
-      <c r="AF65" s="88" t="n"/>
-      <c r="AG65" s="88" t="n"/>
+      <c r="AF65" s="91" t="n"/>
+      <c r="AG65" s="91" t="n"/>
       <c r="AH65" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -6155,11 +6157,11 @@
       <c r="AB66" s="71" t="n"/>
       <c r="AC66" s="71" t="n"/>
       <c r="AD66" s="70" t="n"/>
-      <c r="AE66" s="88" t="n">
+      <c r="AE66" s="91" t="n">
         <v>45545</v>
       </c>
-      <c r="AF66" s="88" t="n"/>
-      <c r="AG66" s="88" t="n"/>
+      <c r="AF66" s="91" t="n"/>
+      <c r="AG66" s="91" t="n"/>
       <c r="AH66" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -6233,11 +6235,11 @@
       <c r="AB67" s="71" t="n"/>
       <c r="AC67" s="71" t="n"/>
       <c r="AD67" s="70" t="n"/>
-      <c r="AE67" s="88" t="n">
+      <c r="AE67" s="91" t="n">
         <v>42919</v>
       </c>
-      <c r="AF67" s="88" t="n"/>
-      <c r="AG67" s="88" t="n"/>
+      <c r="AF67" s="91" t="n"/>
+      <c r="AG67" s="91" t="n"/>
       <c r="AH67" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -6311,11 +6313,11 @@
       <c r="AB68" s="71" t="n"/>
       <c r="AC68" s="71" t="n"/>
       <c r="AD68" s="70" t="n"/>
-      <c r="AE68" s="88" t="n">
+      <c r="AE68" s="91" t="n">
         <v>42919</v>
       </c>
-      <c r="AF68" s="88" t="n"/>
-      <c r="AG68" s="88" t="n"/>
+      <c r="AF68" s="91" t="n"/>
+      <c r="AG68" s="91" t="n"/>
       <c r="AH68" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -6389,11 +6391,11 @@
       <c r="AB69" s="71" t="n"/>
       <c r="AC69" s="71" t="n"/>
       <c r="AD69" s="70" t="n"/>
-      <c r="AE69" s="88" t="n">
+      <c r="AE69" s="91" t="n">
         <v>45398</v>
       </c>
-      <c r="AF69" s="88" t="n"/>
-      <c r="AG69" s="88" t="n"/>
+      <c r="AF69" s="91" t="n"/>
+      <c r="AG69" s="91" t="n"/>
       <c r="AH69" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -6467,11 +6469,11 @@
       <c r="AB70" s="71" t="n"/>
       <c r="AC70" s="71" t="n"/>
       <c r="AD70" s="70" t="n"/>
-      <c r="AE70" s="88" t="n">
+      <c r="AE70" s="91" t="n">
         <v>42919</v>
       </c>
-      <c r="AF70" s="88" t="n"/>
-      <c r="AG70" s="88" t="n"/>
+      <c r="AF70" s="91" t="n"/>
+      <c r="AG70" s="91" t="n"/>
       <c r="AH70" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -6545,11 +6547,11 @@
       <c r="AB71" s="71" t="n"/>
       <c r="AC71" s="71" t="n"/>
       <c r="AD71" s="70" t="n"/>
-      <c r="AE71" s="88" t="n">
+      <c r="AE71" s="91" t="n">
         <v>42919</v>
       </c>
-      <c r="AF71" s="88" t="n"/>
-      <c r="AG71" s="88" t="n"/>
+      <c r="AF71" s="91" t="n"/>
+      <c r="AG71" s="91" t="n"/>
       <c r="AH71" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -6623,11 +6625,11 @@
       <c r="AB72" s="71" t="n"/>
       <c r="AC72" s="71" t="n"/>
       <c r="AD72" s="70" t="n"/>
-      <c r="AE72" s="88" t="n">
+      <c r="AE72" s="91" t="n">
         <v>42919</v>
       </c>
-      <c r="AF72" s="88" t="n"/>
-      <c r="AG72" s="88" t="n"/>
+      <c r="AF72" s="91" t="n"/>
+      <c r="AG72" s="91" t="n"/>
       <c r="AH72" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -6701,11 +6703,11 @@
       <c r="AB73" s="71" t="n"/>
       <c r="AC73" s="71" t="n"/>
       <c r="AD73" s="70" t="n"/>
-      <c r="AE73" s="88" t="n">
+      <c r="AE73" s="91" t="n">
         <v>42919</v>
       </c>
-      <c r="AF73" s="88" t="n"/>
-      <c r="AG73" s="88" t="n"/>
+      <c r="AF73" s="91" t="n"/>
+      <c r="AG73" s="91" t="n"/>
       <c r="AH73" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -6779,11 +6781,11 @@
       <c r="AB74" s="71" t="n"/>
       <c r="AC74" s="71" t="n"/>
       <c r="AD74" s="70" t="n"/>
-      <c r="AE74" s="88" t="n">
+      <c r="AE74" s="91" t="n">
         <v>45756</v>
       </c>
-      <c r="AF74" s="88" t="n"/>
-      <c r="AG74" s="88" t="n"/>
+      <c r="AF74" s="91" t="n"/>
+      <c r="AG74" s="91" t="n"/>
       <c r="AH74" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -6857,11 +6859,11 @@
       <c r="AB75" s="71" t="n"/>
       <c r="AC75" s="71" t="n"/>
       <c r="AD75" s="70" t="n"/>
-      <c r="AE75" s="88" t="n">
+      <c r="AE75" s="91" t="n">
         <v>45720</v>
       </c>
-      <c r="AF75" s="88" t="n"/>
-      <c r="AG75" s="88" t="n"/>
+      <c r="AF75" s="91" t="n"/>
+      <c r="AG75" s="91" t="n"/>
       <c r="AH75" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -6935,11 +6937,11 @@
       <c r="AB76" s="71" t="n"/>
       <c r="AC76" s="71" t="n"/>
       <c r="AD76" s="70" t="n"/>
-      <c r="AE76" s="88" t="n">
+      <c r="AE76" s="91" t="n">
         <v>45908</v>
       </c>
-      <c r="AF76" s="88" t="n"/>
-      <c r="AG76" s="88" t="n"/>
+      <c r="AF76" s="91" t="n"/>
+      <c r="AG76" s="91" t="n"/>
       <c r="AH76" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7013,11 +7015,11 @@
       <c r="AB77" s="71" t="n"/>
       <c r="AC77" s="71" t="n"/>
       <c r="AD77" s="70" t="n"/>
-      <c r="AE77" s="88" t="n">
+      <c r="AE77" s="91" t="n">
         <v>38664</v>
       </c>
-      <c r="AF77" s="88" t="n"/>
-      <c r="AG77" s="88" t="n"/>
+      <c r="AF77" s="91" t="n"/>
+      <c r="AG77" s="91" t="n"/>
       <c r="AH77" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7091,11 +7093,11 @@
       <c r="AB78" s="71" t="n"/>
       <c r="AC78" s="71" t="n"/>
       <c r="AD78" s="70" t="n"/>
-      <c r="AE78" s="88" t="n">
+      <c r="AE78" s="91" t="n">
         <v>45943</v>
       </c>
-      <c r="AF78" s="88" t="n"/>
-      <c r="AG78" s="88" t="n"/>
+      <c r="AF78" s="91" t="n"/>
+      <c r="AG78" s="91" t="n"/>
       <c r="AH78" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7169,11 +7171,11 @@
       <c r="AB79" s="71" t="n"/>
       <c r="AC79" s="71" t="n"/>
       <c r="AD79" s="70" t="n"/>
-      <c r="AE79" s="88" t="n">
+      <c r="AE79" s="91" t="n">
         <v>46077</v>
       </c>
-      <c r="AF79" s="88" t="n"/>
-      <c r="AG79" s="88" t="n"/>
+      <c r="AF79" s="91" t="n"/>
+      <c r="AG79" s="91" t="n"/>
       <c r="AH79" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7247,11 +7249,11 @@
       <c r="AB80" s="71" t="n"/>
       <c r="AC80" s="71" t="n"/>
       <c r="AD80" s="70" t="n"/>
-      <c r="AE80" s="88" t="n">
+      <c r="AE80" s="91" t="n">
         <v>46097</v>
       </c>
-      <c r="AF80" s="88" t="n"/>
-      <c r="AG80" s="88" t="n"/>
+      <c r="AF80" s="91" t="n"/>
+      <c r="AG80" s="91" t="n"/>
       <c r="AH80" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7325,11 +7327,11 @@
       <c r="AB81" s="71" t="n"/>
       <c r="AC81" s="71" t="n"/>
       <c r="AD81" s="70" t="n"/>
-      <c r="AE81" s="88" t="n">
+      <c r="AE81" s="91" t="n">
         <v>43024</v>
       </c>
-      <c r="AF81" s="88" t="n"/>
-      <c r="AG81" s="88" t="n"/>
+      <c r="AF81" s="91" t="n"/>
+      <c r="AG81" s="91" t="n"/>
       <c r="AH81" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7407,11 +7409,11 @@
       <c r="AB82" s="71" t="n"/>
       <c r="AC82" s="71" t="n"/>
       <c r="AD82" s="70" t="n"/>
-      <c r="AE82" s="88" t="n">
+      <c r="AE82" s="91" t="n">
         <v>41219</v>
       </c>
-      <c r="AF82" s="88" t="n"/>
-      <c r="AG82" s="88" t="n"/>
+      <c r="AF82" s="91" t="n"/>
+      <c r="AG82" s="91" t="n"/>
       <c r="AH82" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7489,11 +7491,11 @@
       <c r="AB83" s="71" t="n"/>
       <c r="AC83" s="71" t="n"/>
       <c r="AD83" s="70" t="n"/>
-      <c r="AE83" s="88" t="n">
+      <c r="AE83" s="91" t="n">
         <v>43557</v>
       </c>
-      <c r="AF83" s="88" t="n"/>
-      <c r="AG83" s="88" t="n"/>
+      <c r="AF83" s="91" t="n"/>
+      <c r="AG83" s="91" t="n"/>
       <c r="AH83" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7571,11 +7573,11 @@
       <c r="AB84" s="71" t="n"/>
       <c r="AC84" s="71" t="n"/>
       <c r="AD84" s="70" t="n"/>
-      <c r="AE84" s="88" t="n">
+      <c r="AE84" s="91" t="n">
         <v>41183</v>
       </c>
-      <c r="AF84" s="88" t="n"/>
-      <c r="AG84" s="88" t="n"/>
+      <c r="AF84" s="91" t="n"/>
+      <c r="AG84" s="91" t="n"/>
       <c r="AH84" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7653,11 +7655,11 @@
       <c r="AB85" s="71" t="n"/>
       <c r="AC85" s="71" t="n"/>
       <c r="AD85" s="70" t="n"/>
-      <c r="AE85" s="88" t="n">
+      <c r="AE85" s="91" t="n">
         <v>40035</v>
       </c>
-      <c r="AF85" s="88" t="n"/>
-      <c r="AG85" s="88" t="n"/>
+      <c r="AF85" s="91" t="n"/>
+      <c r="AG85" s="91" t="n"/>
       <c r="AH85" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7735,11 +7737,11 @@
       <c r="AB86" s="71" t="n"/>
       <c r="AC86" s="71" t="n"/>
       <c r="AD86" s="70" t="n"/>
-      <c r="AE86" s="88" t="n">
+      <c r="AE86" s="91" t="n">
         <v>44879</v>
       </c>
-      <c r="AF86" s="88" t="n"/>
-      <c r="AG86" s="88" t="n"/>
+      <c r="AF86" s="91" t="n"/>
+      <c r="AG86" s="91" t="n"/>
       <c r="AH86" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7817,11 +7819,11 @@
       <c r="AB87" s="71" t="n"/>
       <c r="AC87" s="71" t="n"/>
       <c r="AD87" s="70" t="n"/>
-      <c r="AE87" s="88" t="n">
+      <c r="AE87" s="91" t="n">
         <v>41375</v>
       </c>
-      <c r="AF87" s="88" t="n"/>
-      <c r="AG87" s="88" t="n"/>
+      <c r="AF87" s="91" t="n"/>
+      <c r="AG87" s="91" t="n"/>
       <c r="AH87" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7899,11 +7901,11 @@
       <c r="AB88" s="71" t="n"/>
       <c r="AC88" s="71" t="n"/>
       <c r="AD88" s="70" t="n"/>
-      <c r="AE88" s="88" t="n">
+      <c r="AE88" s="91" t="n">
         <v>43557</v>
       </c>
-      <c r="AF88" s="88" t="n"/>
-      <c r="AG88" s="88" t="n"/>
+      <c r="AF88" s="91" t="n"/>
+      <c r="AG88" s="91" t="n"/>
       <c r="AH88" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -7981,11 +7983,11 @@
       <c r="AB89" s="71" t="n"/>
       <c r="AC89" s="71" t="n"/>
       <c r="AD89" s="70" t="n"/>
-      <c r="AE89" s="88" t="n">
+      <c r="AE89" s="91" t="n">
         <v>39875</v>
       </c>
-      <c r="AF89" s="88" t="n"/>
-      <c r="AG89" s="88" t="n"/>
+      <c r="AF89" s="91" t="n"/>
+      <c r="AG89" s="91" t="n"/>
       <c r="AH89" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8063,11 +8065,11 @@
       <c r="AB90" s="71" t="n"/>
       <c r="AC90" s="71" t="n"/>
       <c r="AD90" s="70" t="n"/>
-      <c r="AE90" s="88" t="n">
+      <c r="AE90" s="91" t="n">
         <v>45719</v>
       </c>
-      <c r="AF90" s="88" t="n"/>
-      <c r="AG90" s="88" t="n"/>
+      <c r="AF90" s="91" t="n"/>
+      <c r="AG90" s="91" t="n"/>
       <c r="AH90" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8141,11 +8143,11 @@
       <c r="AB91" s="71" t="n"/>
       <c r="AC91" s="71" t="n"/>
       <c r="AD91" s="70" t="n"/>
-      <c r="AE91" s="88" t="n">
+      <c r="AE91" s="91" t="n">
         <v>45803</v>
       </c>
-      <c r="AF91" s="88" t="n"/>
-      <c r="AG91" s="88" t="n"/>
+      <c r="AF91" s="91" t="n"/>
+      <c r="AG91" s="91" t="n"/>
       <c r="AH91" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8219,11 +8221,11 @@
       <c r="AB92" s="71" t="n"/>
       <c r="AC92" s="71" t="n"/>
       <c r="AD92" s="70" t="n"/>
-      <c r="AE92" s="88" t="n">
+      <c r="AE92" s="91" t="n">
         <v>45833</v>
       </c>
-      <c r="AF92" s="88" t="n"/>
-      <c r="AG92" s="88" t="n"/>
+      <c r="AF92" s="91" t="n"/>
+      <c r="AG92" s="91" t="n"/>
       <c r="AH92" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8297,11 +8299,11 @@
       <c r="AB93" s="71" t="n"/>
       <c r="AC93" s="71" t="n"/>
       <c r="AD93" s="70" t="n"/>
-      <c r="AE93" s="88" t="n">
+      <c r="AE93" s="91" t="n">
         <v>45691</v>
       </c>
-      <c r="AF93" s="88" t="n"/>
-      <c r="AG93" s="88" t="n"/>
+      <c r="AF93" s="91" t="n"/>
+      <c r="AG93" s="91" t="n"/>
       <c r="AH93" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8375,11 +8377,11 @@
       <c r="AB94" s="71" t="n"/>
       <c r="AC94" s="71" t="n"/>
       <c r="AD94" s="70" t="n"/>
-      <c r="AE94" s="88" t="n">
+      <c r="AE94" s="91" t="n">
         <v>45537</v>
       </c>
-      <c r="AF94" s="88" t="n"/>
-      <c r="AG94" s="88" t="n"/>
+      <c r="AF94" s="91" t="n"/>
+      <c r="AG94" s="91" t="n"/>
       <c r="AH94" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8453,11 +8455,11 @@
       <c r="AB95" s="71" t="n"/>
       <c r="AC95" s="71" t="n"/>
       <c r="AD95" s="70" t="n"/>
-      <c r="AE95" s="88" t="n">
+      <c r="AE95" s="91" t="n">
         <v>45908</v>
       </c>
-      <c r="AF95" s="88" t="n"/>
-      <c r="AG95" s="88" t="n"/>
+      <c r="AF95" s="91" t="n"/>
+      <c r="AG95" s="91" t="n"/>
       <c r="AH95" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8531,11 +8533,11 @@
       <c r="AB96" s="71" t="n"/>
       <c r="AC96" s="71" t="n"/>
       <c r="AD96" s="70" t="n"/>
-      <c r="AE96" s="88" t="n">
+      <c r="AE96" s="91" t="n">
         <v>42360</v>
       </c>
-      <c r="AF96" s="88" t="n"/>
-      <c r="AG96" s="88" t="n"/>
+      <c r="AF96" s="91" t="n"/>
+      <c r="AG96" s="91" t="n"/>
       <c r="AH96" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8609,11 +8611,11 @@
       <c r="AB97" s="71" t="n"/>
       <c r="AC97" s="71" t="n"/>
       <c r="AD97" s="70" t="n"/>
-      <c r="AE97" s="88" t="n">
+      <c r="AE97" s="91" t="n">
         <v>45966</v>
       </c>
-      <c r="AF97" s="88" t="n"/>
-      <c r="AG97" s="88" t="n"/>
+      <c r="AF97" s="91" t="n"/>
+      <c r="AG97" s="91" t="n"/>
       <c r="AH97" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8687,11 +8689,11 @@
       <c r="AB98" s="71" t="n"/>
       <c r="AC98" s="71" t="n"/>
       <c r="AD98" s="70" t="n"/>
-      <c r="AE98" s="88" t="n">
+      <c r="AE98" s="91" t="n">
         <v>46113</v>
       </c>
-      <c r="AF98" s="88" t="n"/>
-      <c r="AG98" s="88" t="n"/>
+      <c r="AF98" s="91" t="n"/>
+      <c r="AG98" s="91" t="n"/>
       <c r="AH98" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8765,11 +8767,11 @@
       <c r="AB99" s="71" t="n"/>
       <c r="AC99" s="71" t="n"/>
       <c r="AD99" s="70" t="n"/>
-      <c r="AE99" s="88" t="n">
+      <c r="AE99" s="91" t="n">
         <v>45579</v>
       </c>
-      <c r="AF99" s="88" t="n"/>
-      <c r="AG99" s="88" t="n"/>
+      <c r="AF99" s="91" t="n"/>
+      <c r="AG99" s="91" t="n"/>
       <c r="AH99" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8843,11 +8845,11 @@
       <c r="AB100" s="71" t="n"/>
       <c r="AC100" s="71" t="n"/>
       <c r="AD100" s="70" t="n"/>
-      <c r="AE100" s="88" t="n">
+      <c r="AE100" s="91" t="n">
         <v>40616</v>
       </c>
-      <c r="AF100" s="88" t="n"/>
-      <c r="AG100" s="88" t="n"/>
+      <c r="AF100" s="91" t="n"/>
+      <c r="AG100" s="91" t="n"/>
       <c r="AH100" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8921,11 +8923,11 @@
       <c r="AB101" s="71" t="n"/>
       <c r="AC101" s="71" t="n"/>
       <c r="AD101" s="70" t="n"/>
-      <c r="AE101" s="88" t="n">
+      <c r="AE101" s="91" t="n">
         <v>45397</v>
       </c>
-      <c r="AF101" s="88" t="n"/>
-      <c r="AG101" s="88" t="n"/>
+      <c r="AF101" s="91" t="n"/>
+      <c r="AG101" s="91" t="n"/>
       <c r="AH101" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -8999,11 +9001,11 @@
       <c r="AB102" s="71" t="n"/>
       <c r="AC102" s="71" t="n"/>
       <c r="AD102" s="70" t="n"/>
-      <c r="AE102" s="88" t="n">
+      <c r="AE102" s="91" t="n">
         <v>43031</v>
       </c>
-      <c r="AF102" s="88" t="n"/>
-      <c r="AG102" s="88" t="n"/>
+      <c r="AF102" s="91" t="n"/>
+      <c r="AG102" s="91" t="n"/>
       <c r="AH102" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -9077,11 +9079,11 @@
       <c r="AB103" s="71" t="n"/>
       <c r="AC103" s="71" t="n"/>
       <c r="AD103" s="70" t="n"/>
-      <c r="AE103" s="88" t="n">
+      <c r="AE103" s="91" t="n">
         <v>46139</v>
       </c>
-      <c r="AF103" s="88" t="n"/>
-      <c r="AG103" s="88" t="n"/>
+      <c r="AF103" s="91" t="n"/>
+      <c r="AG103" s="91" t="n"/>
       <c r="AH103" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -9155,11 +9157,11 @@
       <c r="AB104" s="71" t="n"/>
       <c r="AC104" s="71" t="n"/>
       <c r="AD104" s="70" t="n"/>
-      <c r="AE104" s="88" t="n">
+      <c r="AE104" s="91" t="n">
         <v>45782</v>
       </c>
-      <c r="AF104" s="88" t="n"/>
-      <c r="AG104" s="88" t="n"/>
+      <c r="AF104" s="91" t="n"/>
+      <c r="AG104" s="91" t="n"/>
       <c r="AH104" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -9233,11 +9235,11 @@
       <c r="AB105" s="71" t="n"/>
       <c r="AC105" s="71" t="n"/>
       <c r="AD105" s="70" t="n"/>
-      <c r="AE105" s="88" t="n">
+      <c r="AE105" s="91" t="n">
         <v>40560</v>
       </c>
-      <c r="AF105" s="88" t="n"/>
-      <c r="AG105" s="88" t="n"/>
+      <c r="AF105" s="91" t="n"/>
+      <c r="AG105" s="91" t="n"/>
       <c r="AH105" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -9311,11 +9313,11 @@
       <c r="AB106" s="71" t="n"/>
       <c r="AC106" s="71" t="n"/>
       <c r="AD106" s="70" t="n"/>
-      <c r="AE106" s="88" t="n">
+      <c r="AE106" s="91" t="n">
         <v>42461</v>
       </c>
-      <c r="AF106" s="88" t="n"/>
-      <c r="AG106" s="88" t="n"/>
+      <c r="AF106" s="91" t="n"/>
+      <c r="AG106" s="91" t="n"/>
       <c r="AH106" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -9389,11 +9391,11 @@
       <c r="AB107" s="71" t="n"/>
       <c r="AC107" s="71" t="n"/>
       <c r="AD107" s="70" t="n"/>
-      <c r="AE107" s="88" t="n">
+      <c r="AE107" s="91" t="n">
         <v>45771</v>
       </c>
-      <c r="AF107" s="88" t="n"/>
-      <c r="AG107" s="88" t="n"/>
+      <c r="AF107" s="91" t="n"/>
+      <c r="AG107" s="91" t="n"/>
       <c r="AH107" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -9467,11 +9469,11 @@
       <c r="AB108" s="71" t="n"/>
       <c r="AC108" s="71" t="n"/>
       <c r="AD108" s="70" t="n"/>
-      <c r="AE108" s="88" t="n">
+      <c r="AE108" s="91" t="n">
         <v>46083</v>
       </c>
-      <c r="AF108" s="88" t="n"/>
-      <c r="AG108" s="88" t="n"/>
+      <c r="AF108" s="91" t="n"/>
+      <c r="AG108" s="91" t="n"/>
       <c r="AH108" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -9545,11 +9547,11 @@
       <c r="AB109" s="71" t="n"/>
       <c r="AC109" s="71" t="n"/>
       <c r="AD109" s="70" t="n"/>
-      <c r="AE109" s="88" t="n">
+      <c r="AE109" s="91" t="n">
         <v>45805</v>
       </c>
-      <c r="AF109" s="88" t="n"/>
-      <c r="AG109" s="88" t="n"/>
+      <c r="AF109" s="91" t="n"/>
+      <c r="AG109" s="91" t="n"/>
       <c r="AH109" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -9623,11 +9625,11 @@
       <c r="AB110" s="71" t="n"/>
       <c r="AC110" s="71" t="n"/>
       <c r="AD110" s="70" t="n"/>
-      <c r="AE110" s="88" t="n">
+      <c r="AE110" s="91" t="n">
         <v>45365</v>
       </c>
-      <c r="AF110" s="88" t="n"/>
-      <c r="AG110" s="88" t="n"/>
+      <c r="AF110" s="91" t="n"/>
+      <c r="AG110" s="91" t="n"/>
       <c r="AH110" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -9701,11 +9703,11 @@
       <c r="AB111" s="71" t="n"/>
       <c r="AC111" s="71" t="n"/>
       <c r="AD111" s="70" t="n"/>
-      <c r="AE111" s="88" t="n">
+      <c r="AE111" s="91" t="n">
         <v>45828</v>
       </c>
-      <c r="AF111" s="88" t="n"/>
-      <c r="AG111" s="88" t="n"/>
+      <c r="AF111" s="91" t="n"/>
+      <c r="AG111" s="91" t="n"/>
       <c r="AH111" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -9779,11 +9781,11 @@
       <c r="AB112" s="71" t="n"/>
       <c r="AC112" s="71" t="n"/>
       <c r="AD112" s="70" t="n"/>
-      <c r="AE112" s="88" t="n">
+      <c r="AE112" s="91" t="n">
         <v>42016</v>
       </c>
-      <c r="AF112" s="88" t="n"/>
-      <c r="AG112" s="88" t="n"/>
+      <c r="AF112" s="91" t="n"/>
+      <c r="AG112" s="91" t="n"/>
       <c r="AH112" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -9857,11 +9859,11 @@
       <c r="AB113" s="71" t="n"/>
       <c r="AC113" s="71" t="n"/>
       <c r="AD113" s="70" t="n"/>
-      <c r="AE113" s="88" t="n">
+      <c r="AE113" s="91" t="n">
         <v>45971</v>
       </c>
-      <c r="AF113" s="88" t="n"/>
-      <c r="AG113" s="88" t="n"/>
+      <c r="AF113" s="91" t="n"/>
+      <c r="AG113" s="91" t="n"/>
       <c r="AH113" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -9935,11 +9937,11 @@
       <c r="AB114" s="71" t="n"/>
       <c r="AC114" s="71" t="n"/>
       <c r="AD114" s="70" t="n"/>
-      <c r="AE114" s="88" t="n">
+      <c r="AE114" s="91" t="n">
         <v>45775</v>
       </c>
-      <c r="AF114" s="88" t="n"/>
-      <c r="AG114" s="88" t="n"/>
+      <c r="AF114" s="91" t="n"/>
+      <c r="AG114" s="91" t="n"/>
       <c r="AH114" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10013,11 +10015,11 @@
       <c r="AB115" s="71" t="n"/>
       <c r="AC115" s="71" t="n"/>
       <c r="AD115" s="70" t="n"/>
-      <c r="AE115" s="88" t="n">
+      <c r="AE115" s="91" t="n">
         <v>44802</v>
       </c>
-      <c r="AF115" s="88" t="n"/>
-      <c r="AG115" s="88" t="n"/>
+      <c r="AF115" s="91" t="n"/>
+      <c r="AG115" s="91" t="n"/>
       <c r="AH115" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10091,11 +10093,11 @@
       <c r="AB116" s="71" t="n"/>
       <c r="AC116" s="71" t="n"/>
       <c r="AD116" s="70" t="n"/>
-      <c r="AE116" s="88" t="n">
+      <c r="AE116" s="91" t="n">
         <v>45791</v>
       </c>
-      <c r="AF116" s="88" t="n"/>
-      <c r="AG116" s="88" t="n"/>
+      <c r="AF116" s="91" t="n"/>
+      <c r="AG116" s="91" t="n"/>
       <c r="AH116" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10169,11 +10171,11 @@
       <c r="AB117" s="71" t="n"/>
       <c r="AC117" s="71" t="n"/>
       <c r="AD117" s="70" t="n"/>
-      <c r="AE117" s="88" t="n">
+      <c r="AE117" s="91" t="n">
         <v>42248</v>
       </c>
-      <c r="AF117" s="88" t="n"/>
-      <c r="AG117" s="88" t="n"/>
+      <c r="AF117" s="91" t="n"/>
+      <c r="AG117" s="91" t="n"/>
       <c r="AH117" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10247,11 +10249,11 @@
       <c r="AB118" s="71" t="n"/>
       <c r="AC118" s="71" t="n"/>
       <c r="AD118" s="70" t="n"/>
-      <c r="AE118" s="88" t="n">
+      <c r="AE118" s="91" t="n">
         <v>45950</v>
       </c>
-      <c r="AF118" s="88" t="n"/>
-      <c r="AG118" s="88" t="n"/>
+      <c r="AF118" s="91" t="n"/>
+      <c r="AG118" s="91" t="n"/>
       <c r="AH118" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10325,11 +10327,11 @@
       <c r="AB119" s="71" t="n"/>
       <c r="AC119" s="71" t="n"/>
       <c r="AD119" s="70" t="n"/>
-      <c r="AE119" s="88" t="n">
+      <c r="AE119" s="91" t="n">
         <v>45789</v>
       </c>
-      <c r="AF119" s="88" t="n"/>
-      <c r="AG119" s="88" t="n"/>
+      <c r="AF119" s="91" t="n"/>
+      <c r="AG119" s="91" t="n"/>
       <c r="AH119" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10403,11 +10405,11 @@
       <c r="AB120" s="71" t="n"/>
       <c r="AC120" s="71" t="n"/>
       <c r="AD120" s="70" t="n"/>
-      <c r="AE120" s="88" t="n">
+      <c r="AE120" s="91" t="n">
         <v>41673</v>
       </c>
-      <c r="AF120" s="88" t="n"/>
-      <c r="AG120" s="88" t="n"/>
+      <c r="AF120" s="91" t="n"/>
+      <c r="AG120" s="91" t="n"/>
       <c r="AH120" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10481,11 +10483,11 @@
       <c r="AB121" s="71" t="n"/>
       <c r="AC121" s="71" t="n"/>
       <c r="AD121" s="70" t="n"/>
-      <c r="AE121" s="88" t="n">
+      <c r="AE121" s="91" t="n">
         <v>45974</v>
       </c>
-      <c r="AF121" s="88" t="n"/>
-      <c r="AG121" s="88" t="n"/>
+      <c r="AF121" s="91" t="n"/>
+      <c r="AG121" s="91" t="n"/>
       <c r="AH121" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10559,11 +10561,11 @@
       <c r="AB122" s="71" t="n"/>
       <c r="AC122" s="71" t="n"/>
       <c r="AD122" s="70" t="n"/>
-      <c r="AE122" s="88" t="n">
+      <c r="AE122" s="91" t="n">
         <v>45714</v>
       </c>
-      <c r="AF122" s="88" t="n"/>
-      <c r="AG122" s="88" t="n"/>
+      <c r="AF122" s="91" t="n"/>
+      <c r="AG122" s="91" t="n"/>
       <c r="AH122" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10637,11 +10639,11 @@
       <c r="AB123" s="71" t="n"/>
       <c r="AC123" s="71" t="n"/>
       <c r="AD123" s="70" t="n"/>
-      <c r="AE123" s="88" t="n">
+      <c r="AE123" s="91" t="n">
         <v>45958</v>
       </c>
-      <c r="AF123" s="88" t="n"/>
-      <c r="AG123" s="88" t="n"/>
+      <c r="AF123" s="91" t="n"/>
+      <c r="AG123" s="91" t="n"/>
       <c r="AH123" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10715,11 +10717,11 @@
       <c r="AB124" s="71" t="n"/>
       <c r="AC124" s="71" t="n"/>
       <c r="AD124" s="70" t="n"/>
-      <c r="AE124" s="88" t="n">
+      <c r="AE124" s="91" t="n">
         <v>45643</v>
       </c>
-      <c r="AF124" s="88" t="n"/>
-      <c r="AG124" s="88" t="n"/>
+      <c r="AF124" s="91" t="n"/>
+      <c r="AG124" s="91" t="n"/>
       <c r="AH124" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10793,11 +10795,11 @@
       <c r="AB125" s="71" t="n"/>
       <c r="AC125" s="71" t="n"/>
       <c r="AD125" s="70" t="n"/>
-      <c r="AE125" s="88" t="n">
+      <c r="AE125" s="91" t="n">
         <v>45833</v>
       </c>
-      <c r="AF125" s="88" t="n"/>
-      <c r="AG125" s="88" t="n"/>
+      <c r="AF125" s="91" t="n"/>
+      <c r="AG125" s="91" t="n"/>
       <c r="AH125" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10871,11 +10873,11 @@
       <c r="AB126" s="71" t="n"/>
       <c r="AC126" s="71" t="n"/>
       <c r="AD126" s="70" t="n"/>
-      <c r="AE126" s="88" t="n">
+      <c r="AE126" s="91" t="n">
         <v>45565</v>
       </c>
-      <c r="AF126" s="88" t="n"/>
-      <c r="AG126" s="88" t="n"/>
+      <c r="AF126" s="91" t="n"/>
+      <c r="AG126" s="91" t="n"/>
       <c r="AH126" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -10949,11 +10951,11 @@
       <c r="AB127" s="71" t="n"/>
       <c r="AC127" s="71" t="n"/>
       <c r="AD127" s="70" t="n"/>
-      <c r="AE127" s="88" t="n">
+      <c r="AE127" s="91" t="n">
         <v>44795</v>
       </c>
-      <c r="AF127" s="88" t="n"/>
-      <c r="AG127" s="88" t="n"/>
+      <c r="AF127" s="91" t="n"/>
+      <c r="AG127" s="91" t="n"/>
       <c r="AH127" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11027,11 +11029,11 @@
       <c r="AB128" s="71" t="n"/>
       <c r="AC128" s="71" t="n"/>
       <c r="AD128" s="70" t="n"/>
-      <c r="AE128" s="88" t="n">
+      <c r="AE128" s="91" t="n">
         <v>45587</v>
       </c>
-      <c r="AF128" s="88" t="n"/>
-      <c r="AG128" s="88" t="n"/>
+      <c r="AF128" s="91" t="n"/>
+      <c r="AG128" s="91" t="n"/>
       <c r="AH128" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11105,11 +11107,11 @@
       <c r="AB129" s="71" t="n"/>
       <c r="AC129" s="71" t="n"/>
       <c r="AD129" s="70" t="n"/>
-      <c r="AE129" s="88" t="n">
+      <c r="AE129" s="91" t="n">
         <v>37438</v>
       </c>
-      <c r="AF129" s="88" t="n"/>
-      <c r="AG129" s="88" t="n"/>
+      <c r="AF129" s="91" t="n"/>
+      <c r="AG129" s="91" t="n"/>
       <c r="AH129" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11183,11 +11185,11 @@
       <c r="AB130" s="71" t="n"/>
       <c r="AC130" s="71" t="n"/>
       <c r="AD130" s="70" t="n"/>
-      <c r="AE130" s="88" t="n">
+      <c r="AE130" s="91" t="n">
         <v>45714</v>
       </c>
-      <c r="AF130" s="88" t="n"/>
-      <c r="AG130" s="88" t="n"/>
+      <c r="AF130" s="91" t="n"/>
+      <c r="AG130" s="91" t="n"/>
       <c r="AH130" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11261,11 +11263,11 @@
       <c r="AB131" s="71" t="n"/>
       <c r="AC131" s="71" t="n"/>
       <c r="AD131" s="70" t="n"/>
-      <c r="AE131" s="88" t="n">
+      <c r="AE131" s="91" t="n">
         <v>42429</v>
       </c>
-      <c r="AF131" s="88" t="n"/>
-      <c r="AG131" s="88" t="n"/>
+      <c r="AF131" s="91" t="n"/>
+      <c r="AG131" s="91" t="n"/>
       <c r="AH131" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11339,11 +11341,11 @@
       <c r="AB132" s="71" t="n"/>
       <c r="AC132" s="71" t="n"/>
       <c r="AD132" s="70" t="n"/>
-      <c r="AE132" s="88" t="n">
+      <c r="AE132" s="91" t="n">
         <v>45649</v>
       </c>
-      <c r="AF132" s="88" t="n"/>
-      <c r="AG132" s="88" t="n"/>
+      <c r="AF132" s="91" t="n"/>
+      <c r="AG132" s="91" t="n"/>
       <c r="AH132" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11417,11 +11419,11 @@
       <c r="AB133" s="71" t="n"/>
       <c r="AC133" s="71" t="n"/>
       <c r="AD133" s="70" t="n"/>
-      <c r="AE133" s="88" t="n">
+      <c r="AE133" s="91" t="n">
         <v>46036</v>
       </c>
-      <c r="AF133" s="88" t="n"/>
-      <c r="AG133" s="88" t="n"/>
+      <c r="AF133" s="91" t="n"/>
+      <c r="AG133" s="91" t="n"/>
       <c r="AH133" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11499,11 +11501,11 @@
       <c r="AB134" s="71" t="n"/>
       <c r="AC134" s="71" t="n"/>
       <c r="AD134" s="70" t="n"/>
-      <c r="AE134" s="88" t="n">
+      <c r="AE134" s="91" t="n">
         <v>44621</v>
       </c>
-      <c r="AF134" s="88" t="n"/>
-      <c r="AG134" s="88" t="n"/>
+      <c r="AF134" s="91" t="n"/>
+      <c r="AG134" s="91" t="n"/>
       <c r="AH134" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11581,11 +11583,11 @@
       <c r="AB135" s="71" t="n"/>
       <c r="AC135" s="71" t="n"/>
       <c r="AD135" s="70" t="n"/>
-      <c r="AE135" s="88" t="n">
+      <c r="AE135" s="91" t="n">
         <v>45817</v>
       </c>
-      <c r="AF135" s="88" t="n"/>
-      <c r="AG135" s="88" t="n"/>
+      <c r="AF135" s="91" t="n"/>
+      <c r="AG135" s="91" t="n"/>
       <c r="AH135" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11663,11 +11665,11 @@
       <c r="AB136" s="71" t="n"/>
       <c r="AC136" s="71" t="n"/>
       <c r="AD136" s="70" t="n"/>
-      <c r="AE136" s="88" t="n">
+      <c r="AE136" s="91" t="n">
         <v>46080</v>
       </c>
-      <c r="AF136" s="88" t="n"/>
-      <c r="AG136" s="88" t="n"/>
+      <c r="AF136" s="91" t="n"/>
+      <c r="AG136" s="91" t="n"/>
       <c r="AH136" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11741,11 +11743,11 @@
       <c r="AB137" s="71" t="n"/>
       <c r="AC137" s="71" t="n"/>
       <c r="AD137" s="70" t="n"/>
-      <c r="AE137" s="88" t="n">
+      <c r="AE137" s="91" t="n">
         <v>45748</v>
       </c>
-      <c r="AF137" s="88" t="n"/>
-      <c r="AG137" s="88" t="n"/>
+      <c r="AF137" s="91" t="n"/>
+      <c r="AG137" s="91" t="n"/>
       <c r="AH137" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11823,11 +11825,11 @@
       <c r="AB138" s="71" t="n"/>
       <c r="AC138" s="71" t="n"/>
       <c r="AD138" s="70" t="n"/>
-      <c r="AE138" s="88" t="n">
+      <c r="AE138" s="91" t="n">
         <v>45596</v>
       </c>
-      <c r="AF138" s="88" t="n"/>
-      <c r="AG138" s="88" t="n"/>
+      <c r="AF138" s="91" t="n"/>
+      <c r="AG138" s="91" t="n"/>
       <c r="AH138" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11901,11 +11903,11 @@
       <c r="AB139" s="71" t="n"/>
       <c r="AC139" s="71" t="n"/>
       <c r="AD139" s="70" t="n"/>
-      <c r="AE139" s="88" t="n">
+      <c r="AE139" s="91" t="n">
         <v>46084</v>
       </c>
-      <c r="AF139" s="88" t="n"/>
-      <c r="AG139" s="88" t="n"/>
+      <c r="AF139" s="91" t="n"/>
+      <c r="AG139" s="91" t="n"/>
       <c r="AH139" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -11983,11 +11985,11 @@
       <c r="AB140" s="71" t="n"/>
       <c r="AC140" s="71" t="n"/>
       <c r="AD140" s="70" t="n"/>
-      <c r="AE140" s="88" t="n">
+      <c r="AE140" s="91" t="n">
         <v>46064</v>
       </c>
-      <c r="AF140" s="88" t="n"/>
-      <c r="AG140" s="88" t="n"/>
+      <c r="AF140" s="91" t="n"/>
+      <c r="AG140" s="91" t="n"/>
       <c r="AH140" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -12061,11 +12063,11 @@
       <c r="AB141" s="71" t="n"/>
       <c r="AC141" s="71" t="n"/>
       <c r="AD141" s="70" t="n"/>
-      <c r="AE141" s="88" t="n">
+      <c r="AE141" s="91" t="n">
         <v>46111</v>
       </c>
-      <c r="AF141" s="88" t="n"/>
-      <c r="AG141" s="88" t="n"/>
+      <c r="AF141" s="91" t="n"/>
+      <c r="AG141" s="91" t="n"/>
       <c r="AH141" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -12139,11 +12141,11 @@
       <c r="AB142" s="71" t="n"/>
       <c r="AC142" s="71" t="n"/>
       <c r="AD142" s="70" t="n"/>
-      <c r="AE142" s="88" t="n">
+      <c r="AE142" s="91" t="n">
         <v>46049</v>
       </c>
-      <c r="AF142" s="88" t="n"/>
-      <c r="AG142" s="88" t="n"/>
+      <c r="AF142" s="91" t="n"/>
+      <c r="AG142" s="91" t="n"/>
       <c r="AH142" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -12217,11 +12219,11 @@
       <c r="AB143" s="71" t="n"/>
       <c r="AC143" s="71" t="n"/>
       <c r="AD143" s="70" t="n"/>
-      <c r="AE143" s="88" t="n">
+      <c r="AE143" s="91" t="n">
         <v>46091</v>
       </c>
-      <c r="AF143" s="88" t="n"/>
-      <c r="AG143" s="88" t="n"/>
+      <c r="AF143" s="91" t="n"/>
+      <c r="AG143" s="91" t="n"/>
       <c r="AH143" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -12295,11 +12297,11 @@
       <c r="AB144" s="71" t="n"/>
       <c r="AC144" s="71" t="n"/>
       <c r="AD144" s="70" t="n"/>
-      <c r="AE144" s="88" t="n">
+      <c r="AE144" s="91" t="n">
         <v>43040</v>
       </c>
-      <c r="AF144" s="88" t="n"/>
-      <c r="AG144" s="88" t="n"/>
+      <c r="AF144" s="91" t="n"/>
+      <c r="AG144" s="91" t="n"/>
       <c r="AH144" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -12373,11 +12375,11 @@
       <c r="AB145" s="71" t="n"/>
       <c r="AC145" s="71" t="n"/>
       <c r="AD145" s="70" t="n"/>
-      <c r="AE145" s="88" t="n">
+      <c r="AE145" s="91" t="n">
         <v>42388</v>
       </c>
-      <c r="AF145" s="88" t="n"/>
-      <c r="AG145" s="88" t="n"/>
+      <c r="AF145" s="91" t="n"/>
+      <c r="AG145" s="91" t="n"/>
       <c r="AH145" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -12451,13 +12453,13 @@
       <c r="AB146" s="71" t="n"/>
       <c r="AC146" s="71" t="n"/>
       <c r="AD146" s="70" t="n"/>
-      <c r="AE146" s="88" t="n">
+      <c r="AE146" s="91" t="n">
         <v>45846</v>
       </c>
-      <c r="AF146" s="88" t="n">
+      <c r="AF146" s="91" t="n">
         <v>45840</v>
       </c>
-      <c r="AG146" s="88" t="n">
+      <c r="AG146" s="91" t="n">
         <v>46205</v>
       </c>
       <c r="AH146" s="6" t="inlineStr">
@@ -12537,11 +12539,11 @@
       <c r="AB147" s="71" t="n"/>
       <c r="AC147" s="71" t="n"/>
       <c r="AD147" s="70" t="n"/>
-      <c r="AE147" s="88" t="n">
+      <c r="AE147" s="91" t="n">
         <v>45958</v>
       </c>
-      <c r="AF147" s="88" t="n"/>
-      <c r="AG147" s="88" t="n"/>
+      <c r="AF147" s="91" t="n"/>
+      <c r="AG147" s="91" t="n"/>
       <c r="AH147" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -12619,11 +12621,11 @@
       <c r="AB148" s="71" t="n"/>
       <c r="AC148" s="71" t="n"/>
       <c r="AD148" s="70" t="n"/>
-      <c r="AE148" s="88" t="n">
+      <c r="AE148" s="91" t="n">
         <v>43313</v>
       </c>
-      <c r="AF148" s="88" t="n"/>
-      <c r="AG148" s="88" t="n"/>
+      <c r="AF148" s="91" t="n"/>
+      <c r="AG148" s="91" t="n"/>
       <c r="AH148" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -12701,11 +12703,11 @@
       <c r="AB149" s="71" t="n"/>
       <c r="AC149" s="71" t="n"/>
       <c r="AD149" s="70" t="n"/>
-      <c r="AE149" s="88" t="n">
+      <c r="AE149" s="91" t="n">
         <v>42289</v>
       </c>
-      <c r="AF149" s="88" t="n"/>
-      <c r="AG149" s="88" t="n"/>
+      <c r="AF149" s="91" t="n"/>
+      <c r="AG149" s="91" t="n"/>
       <c r="AH149" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -12783,11 +12785,11 @@
       <c r="AB150" s="71" t="n"/>
       <c r="AC150" s="71" t="n"/>
       <c r="AD150" s="70" t="n"/>
-      <c r="AE150" s="88" t="n">
+      <c r="AE150" s="91" t="n">
         <v>42443</v>
       </c>
-      <c r="AF150" s="88" t="n"/>
-      <c r="AG150" s="88" t="n"/>
+      <c r="AF150" s="91" t="n"/>
+      <c r="AG150" s="91" t="n"/>
       <c r="AH150" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -12861,11 +12863,11 @@
       <c r="AB151" s="71" t="n"/>
       <c r="AC151" s="71" t="n"/>
       <c r="AD151" s="70" t="n"/>
-      <c r="AE151" s="88" t="n">
+      <c r="AE151" s="91" t="n">
         <v>42382</v>
       </c>
-      <c r="AF151" s="88" t="n"/>
-      <c r="AG151" s="88" t="n"/>
+      <c r="AF151" s="91" t="n"/>
+      <c r="AG151" s="91" t="n"/>
       <c r="AH151" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -12939,11 +12941,11 @@
       <c r="AB152" s="71" t="n"/>
       <c r="AC152" s="71" t="n"/>
       <c r="AD152" s="70" t="n"/>
-      <c r="AE152" s="88" t="n">
+      <c r="AE152" s="91" t="n">
         <v>45972</v>
       </c>
-      <c r="AF152" s="88" t="n"/>
-      <c r="AG152" s="88" t="n"/>
+      <c r="AF152" s="91" t="n"/>
+      <c r="AG152" s="91" t="n"/>
       <c r="AH152" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -13017,11 +13019,11 @@
       <c r="AB153" s="71" t="n"/>
       <c r="AC153" s="71" t="n"/>
       <c r="AD153" s="70" t="n"/>
-      <c r="AE153" s="88" t="n">
+      <c r="AE153" s="91" t="n">
         <v>39824</v>
       </c>
-      <c r="AF153" s="88" t="n"/>
-      <c r="AG153" s="88" t="n"/>
+      <c r="AF153" s="91" t="n"/>
+      <c r="AG153" s="91" t="n"/>
       <c r="AH153" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -13095,11 +13097,11 @@
       <c r="AB154" s="71" t="n"/>
       <c r="AC154" s="71" t="n"/>
       <c r="AD154" s="70" t="n"/>
-      <c r="AE154" s="88" t="n">
+      <c r="AE154" s="91" t="n">
         <v>45754</v>
       </c>
-      <c r="AF154" s="88" t="n"/>
-      <c r="AG154" s="88" t="n"/>
+      <c r="AF154" s="91" t="n"/>
+      <c r="AG154" s="91" t="n"/>
       <c r="AH154" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -13173,11 +13175,11 @@
       <c r="AB155" s="71" t="n"/>
       <c r="AC155" s="71" t="n"/>
       <c r="AD155" s="70" t="n"/>
-      <c r="AE155" s="88" t="n">
+      <c r="AE155" s="91" t="n">
         <v>46136</v>
       </c>
-      <c r="AF155" s="88" t="n"/>
-      <c r="AG155" s="88" t="n"/>
+      <c r="AF155" s="91" t="n"/>
+      <c r="AG155" s="91" t="n"/>
       <c r="AH155" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -13251,11 +13253,11 @@
       <c r="AB156" s="71" t="n"/>
       <c r="AC156" s="71" t="n"/>
       <c r="AD156" s="70" t="n"/>
-      <c r="AE156" s="88" t="n">
+      <c r="AE156" s="91" t="n">
         <v>42495</v>
       </c>
-      <c r="AF156" s="88" t="n"/>
-      <c r="AG156" s="88" t="n"/>
+      <c r="AF156" s="91" t="n"/>
+      <c r="AG156" s="91" t="n"/>
       <c r="AH156" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -13329,11 +13331,11 @@
       <c r="AB157" s="71" t="n"/>
       <c r="AC157" s="71" t="n"/>
       <c r="AD157" s="70" t="n"/>
-      <c r="AE157" s="88" t="n">
+      <c r="AE157" s="91" t="n">
         <v>39734</v>
       </c>
-      <c r="AF157" s="88" t="n"/>
-      <c r="AG157" s="88" t="n"/>
+      <c r="AF157" s="91" t="n"/>
+      <c r="AG157" s="91" t="n"/>
       <c r="AH157" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -13407,11 +13409,11 @@
       <c r="AB158" s="71" t="n"/>
       <c r="AC158" s="71" t="n"/>
       <c r="AD158" s="70" t="n"/>
-      <c r="AE158" s="88" t="n">
+      <c r="AE158" s="91" t="n">
         <v>45428</v>
       </c>
-      <c r="AF158" s="88" t="n"/>
-      <c r="AG158" s="88" t="n"/>
+      <c r="AF158" s="91" t="n"/>
+      <c r="AG158" s="91" t="n"/>
       <c r="AH158" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -13485,11 +13487,11 @@
       <c r="AB159" s="71" t="n"/>
       <c r="AC159" s="71" t="n"/>
       <c r="AD159" s="70" t="n"/>
-      <c r="AE159" s="88" t="n">
+      <c r="AE159" s="91" t="n">
         <v>46080</v>
       </c>
-      <c r="AF159" s="88" t="n"/>
-      <c r="AG159" s="88" t="n"/>
+      <c r="AF159" s="91" t="n"/>
+      <c r="AG159" s="91" t="n"/>
       <c r="AH159" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -13563,11 +13565,11 @@
       <c r="AB160" s="71" t="n"/>
       <c r="AC160" s="71" t="n"/>
       <c r="AD160" s="70" t="n"/>
-      <c r="AE160" s="88" t="n">
+      <c r="AE160" s="91" t="n">
         <v>44706</v>
       </c>
-      <c r="AF160" s="88" t="n"/>
-      <c r="AG160" s="88" t="n"/>
+      <c r="AF160" s="91" t="n"/>
+      <c r="AG160" s="91" t="n"/>
       <c r="AH160" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -13641,13 +13643,13 @@
       <c r="AB161" s="71" t="n"/>
       <c r="AC161" s="71" t="n"/>
       <c r="AD161" s="70" t="n"/>
-      <c r="AE161" s="88" t="n">
+      <c r="AE161" s="91" t="n">
         <v>45952</v>
       </c>
-      <c r="AF161" s="88" t="n">
+      <c r="AF161" s="91" t="n">
         <v>45945</v>
       </c>
-      <c r="AG161" s="88" t="n">
+      <c r="AG161" s="91" t="n">
         <v>46310</v>
       </c>
       <c r="AH161" s="6" t="inlineStr">
@@ -13723,11 +13725,11 @@
       <c r="AB162" s="71" t="n"/>
       <c r="AC162" s="71" t="n"/>
       <c r="AD162" s="70" t="n"/>
-      <c r="AE162" s="88" t="n">
+      <c r="AE162" s="91" t="n">
         <v>40819</v>
       </c>
-      <c r="AF162" s="88" t="n"/>
-      <c r="AG162" s="88" t="n"/>
+      <c r="AF162" s="91" t="n"/>
+      <c r="AG162" s="91" t="n"/>
       <c r="AH162" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -13801,11 +13803,11 @@
       <c r="AB163" s="71" t="n"/>
       <c r="AC163" s="71" t="n"/>
       <c r="AD163" s="70" t="n"/>
-      <c r="AE163" s="88" t="n">
+      <c r="AE163" s="91" t="n">
         <v>39420</v>
       </c>
-      <c r="AF163" s="88" t="n"/>
-      <c r="AG163" s="88" t="n"/>
+      <c r="AF163" s="91" t="n"/>
+      <c r="AG163" s="91" t="n"/>
       <c r="AH163" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -13879,11 +13881,11 @@
       <c r="AB164" s="71" t="n"/>
       <c r="AC164" s="71" t="n"/>
       <c r="AD164" s="70" t="n"/>
-      <c r="AE164" s="88" t="n">
+      <c r="AE164" s="91" t="n">
         <v>44482</v>
       </c>
-      <c r="AF164" s="88" t="n"/>
-      <c r="AG164" s="88" t="n"/>
+      <c r="AF164" s="91" t="n"/>
+      <c r="AG164" s="91" t="n"/>
       <c r="AH164" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -13957,11 +13959,11 @@
       <c r="AB165" s="71" t="n"/>
       <c r="AC165" s="71" t="n"/>
       <c r="AD165" s="70" t="n"/>
-      <c r="AE165" s="88" t="n">
+      <c r="AE165" s="91" t="n">
         <v>37683</v>
       </c>
-      <c r="AF165" s="88" t="n"/>
-      <c r="AG165" s="88" t="n"/>
+      <c r="AF165" s="91" t="n"/>
+      <c r="AG165" s="91" t="n"/>
       <c r="AH165" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -14035,11 +14037,11 @@
       <c r="AB166" s="71" t="n"/>
       <c r="AC166" s="71" t="n"/>
       <c r="AD166" s="70" t="n"/>
-      <c r="AE166" s="88" t="n">
+      <c r="AE166" s="91" t="n">
         <v>46148</v>
       </c>
-      <c r="AF166" s="88" t="n"/>
-      <c r="AG166" s="88" t="n"/>
+      <c r="AF166" s="91" t="n"/>
+      <c r="AG166" s="91" t="n"/>
       <c r="AH166" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -14113,11 +14115,11 @@
       <c r="AB167" s="71" t="n"/>
       <c r="AC167" s="71" t="n"/>
       <c r="AD167" s="70" t="n"/>
-      <c r="AE167" s="88" t="n">
+      <c r="AE167" s="91" t="n">
         <v>45831</v>
       </c>
-      <c r="AF167" s="88" t="n"/>
-      <c r="AG167" s="88" t="n"/>
+      <c r="AF167" s="91" t="n"/>
+      <c r="AG167" s="91" t="n"/>
       <c r="AH167" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -14187,14 +14189,10 @@
       <c r="AB168" s="71" t="n"/>
       <c r="AC168" s="71" t="n"/>
       <c r="AD168" s="70" t="n"/>
-      <c r="AE168" s="88" t="n"/>
-      <c r="AF168" s="88" t="n"/>
-      <c r="AG168" s="88" t="n"/>
-      <c r="AH168" s="6" t="inlineStr">
-        <is>
-          <t>Не входит в список периодич. осмотра</t>
-        </is>
-      </c>
+      <c r="AE168" s="91" t="n"/>
+      <c r="AF168" s="91" t="n"/>
+      <c r="AG168" s="91" t="n"/>
+      <c r="AH168" s="6" t="n"/>
       <c r="AI168" s="6" t="inlineStr">
         <is>
           <t>п.11 Прил.№2: руководство работами по монтажу, наладке, ремонту электроустановок. Относится также мастер участка РЭО.</t>
@@ -14267,11 +14265,11 @@
       <c r="AB169" s="71" t="n"/>
       <c r="AC169" s="71" t="n"/>
       <c r="AD169" s="70" t="n"/>
-      <c r="AE169" s="88" t="n">
+      <c r="AE169" s="91" t="n">
         <v>45446</v>
       </c>
-      <c r="AF169" s="88" t="n"/>
-      <c r="AG169" s="88" t="n"/>
+      <c r="AF169" s="91" t="n"/>
+      <c r="AG169" s="91" t="n"/>
       <c r="AH169" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -14345,11 +14343,11 @@
       <c r="AB170" s="71" t="n"/>
       <c r="AC170" s="71" t="n"/>
       <c r="AD170" s="70" t="n"/>
-      <c r="AE170" s="88" t="n">
+      <c r="AE170" s="91" t="n">
         <v>45944</v>
       </c>
-      <c r="AF170" s="88" t="n"/>
-      <c r="AG170" s="88" t="n"/>
+      <c r="AF170" s="91" t="n"/>
+      <c r="AG170" s="91" t="n"/>
       <c r="AH170" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -14423,11 +14421,11 @@
       <c r="AB171" s="71" t="n"/>
       <c r="AC171" s="71" t="n"/>
       <c r="AD171" s="70" t="n"/>
-      <c r="AE171" s="88" t="n">
+      <c r="AE171" s="91" t="n">
         <v>46104</v>
       </c>
-      <c r="AF171" s="88" t="n"/>
-      <c r="AG171" s="88" t="n"/>
+      <c r="AF171" s="91" t="n"/>
+      <c r="AG171" s="91" t="n"/>
       <c r="AH171" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -14501,11 +14499,11 @@
       <c r="AB172" s="71" t="n"/>
       <c r="AC172" s="71" t="n"/>
       <c r="AD172" s="70" t="n"/>
-      <c r="AE172" s="88" t="n">
+      <c r="AE172" s="91" t="n">
         <v>46113</v>
       </c>
-      <c r="AF172" s="88" t="n"/>
-      <c r="AG172" s="88" t="n"/>
+      <c r="AF172" s="91" t="n"/>
+      <c r="AG172" s="91" t="n"/>
       <c r="AH172" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -14579,11 +14577,11 @@
       <c r="AB173" s="71" t="n"/>
       <c r="AC173" s="71" t="n"/>
       <c r="AD173" s="70" t="n"/>
-      <c r="AE173" s="88" t="n">
+      <c r="AE173" s="91" t="n">
         <v>46084</v>
       </c>
-      <c r="AF173" s="88" t="n"/>
-      <c r="AG173" s="88" t="n"/>
+      <c r="AF173" s="91" t="n"/>
+      <c r="AG173" s="91" t="n"/>
       <c r="AH173" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -14657,11 +14655,11 @@
       <c r="AB174" s="71" t="n"/>
       <c r="AC174" s="71" t="n"/>
       <c r="AD174" s="70" t="n"/>
-      <c r="AE174" s="88" t="n">
+      <c r="AE174" s="91" t="n">
         <v>45812</v>
       </c>
-      <c r="AF174" s="88" t="n"/>
-      <c r="AG174" s="88" t="n"/>
+      <c r="AF174" s="91" t="n"/>
+      <c r="AG174" s="91" t="n"/>
       <c r="AH174" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -14735,11 +14733,11 @@
       <c r="AB175" s="71" t="n"/>
       <c r="AC175" s="71" t="n"/>
       <c r="AD175" s="70" t="n"/>
-      <c r="AE175" s="88" t="n">
+      <c r="AE175" s="91" t="n">
         <v>45993</v>
       </c>
-      <c r="AF175" s="88" t="n"/>
-      <c r="AG175" s="88" t="n"/>
+      <c r="AF175" s="91" t="n"/>
+      <c r="AG175" s="91" t="n"/>
       <c r="AH175" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -14813,13 +14811,13 @@
       <c r="AB176" s="71" t="n"/>
       <c r="AC176" s="71" t="n"/>
       <c r="AD176" s="70" t="n"/>
-      <c r="AE176" s="88" t="n">
+      <c r="AE176" s="91" t="n">
         <v>45924</v>
       </c>
-      <c r="AF176" s="88" t="n">
+      <c r="AF176" s="91" t="n">
         <v>45922</v>
       </c>
-      <c r="AG176" s="88" t="n">
+      <c r="AG176" s="91" t="n">
         <v>46287</v>
       </c>
       <c r="AH176" s="6" t="inlineStr">
@@ -14895,11 +14893,11 @@
       <c r="AB177" s="71" t="n"/>
       <c r="AC177" s="71" t="n"/>
       <c r="AD177" s="70" t="n"/>
-      <c r="AE177" s="88" t="n">
+      <c r="AE177" s="91" t="n">
         <v>45798</v>
       </c>
-      <c r="AF177" s="88" t="n"/>
-      <c r="AG177" s="88" t="n"/>
+      <c r="AF177" s="91" t="n"/>
+      <c r="AG177" s="91" t="n"/>
       <c r="AH177" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -14973,11 +14971,11 @@
       <c r="AB178" s="71" t="n"/>
       <c r="AC178" s="71" t="n"/>
       <c r="AD178" s="70" t="n"/>
-      <c r="AE178" s="88" t="n">
+      <c r="AE178" s="91" t="n">
         <v>46001</v>
       </c>
-      <c r="AF178" s="88" t="n"/>
-      <c r="AG178" s="88" t="n"/>
+      <c r="AF178" s="91" t="n"/>
+      <c r="AG178" s="91" t="n"/>
       <c r="AH178" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -15051,13 +15049,13 @@
       <c r="AB179" s="71" t="n"/>
       <c r="AC179" s="71" t="n"/>
       <c r="AD179" s="71" t="n"/>
-      <c r="AE179" s="88" t="n">
+      <c r="AE179" s="91" t="n">
         <v>45932</v>
       </c>
-      <c r="AF179" s="88" t="n">
+      <c r="AF179" s="91" t="n">
         <v>45926</v>
       </c>
-      <c r="AG179" s="88" t="n">
+      <c r="AG179" s="91" t="n">
         <v>46291</v>
       </c>
       <c r="AH179" s="6" t="inlineStr">
@@ -15133,13 +15131,13 @@
       <c r="AB180" s="71" t="n"/>
       <c r="AC180" s="71" t="n"/>
       <c r="AD180" s="71" t="n"/>
-      <c r="AE180" s="88" t="n">
+      <c r="AE180" s="91" t="n">
         <v>45922</v>
       </c>
-      <c r="AF180" s="88" t="n">
+      <c r="AF180" s="91" t="n">
         <v>45919</v>
       </c>
-      <c r="AG180" s="88" t="n">
+      <c r="AG180" s="91" t="n">
         <v>46284</v>
       </c>
       <c r="AH180" s="6" t="inlineStr">
@@ -15215,11 +15213,11 @@
       <c r="AB181" s="71" t="n"/>
       <c r="AC181" s="71" t="n"/>
       <c r="AD181" s="71" t="n"/>
-      <c r="AE181" s="88" t="n">
+      <c r="AE181" s="91" t="n">
         <v>45993</v>
       </c>
-      <c r="AF181" s="88" t="n"/>
-      <c r="AG181" s="88" t="n"/>
+      <c r="AF181" s="91" t="n"/>
+      <c r="AG181" s="91" t="n"/>
       <c r="AH181" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -15293,11 +15291,11 @@
       <c r="AB182" s="71" t="n"/>
       <c r="AC182" s="71" t="n"/>
       <c r="AD182" s="71" t="n"/>
-      <c r="AE182" s="88" t="n">
+      <c r="AE182" s="91" t="n">
         <v>46044</v>
       </c>
-      <c r="AF182" s="88" t="n"/>
-      <c r="AG182" s="88" t="n"/>
+      <c r="AF182" s="91" t="n"/>
+      <c r="AG182" s="91" t="n"/>
       <c r="AH182" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -15371,11 +15369,11 @@
       <c r="AB183" s="71" t="n"/>
       <c r="AC183" s="71" t="n"/>
       <c r="AD183" s="71" t="n"/>
-      <c r="AE183" s="88" t="n">
+      <c r="AE183" s="91" t="n">
         <v>45744</v>
       </c>
-      <c r="AF183" s="88" t="n"/>
-      <c r="AG183" s="88" t="n"/>
+      <c r="AF183" s="91" t="n"/>
+      <c r="AG183" s="91" t="n"/>
       <c r="AH183" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -15449,11 +15447,11 @@
       <c r="AB184" s="71" t="n"/>
       <c r="AC184" s="71" t="n"/>
       <c r="AD184" s="71" t="n"/>
-      <c r="AE184" s="88" t="n">
+      <c r="AE184" s="91" t="n">
         <v>46148</v>
       </c>
-      <c r="AF184" s="88" t="n"/>
-      <c r="AG184" s="88" t="n"/>
+      <c r="AF184" s="91" t="n"/>
+      <c r="AG184" s="91" t="n"/>
       <c r="AH184" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -15527,11 +15525,11 @@
       <c r="AB185" s="71" t="n"/>
       <c r="AC185" s="71" t="n"/>
       <c r="AD185" s="71" t="n"/>
-      <c r="AE185" s="88" t="n">
+      <c r="AE185" s="91" t="n">
         <v>45910</v>
       </c>
-      <c r="AF185" s="88" t="n"/>
-      <c r="AG185" s="88" t="n"/>
+      <c r="AF185" s="91" t="n"/>
+      <c r="AG185" s="91" t="n"/>
       <c r="AH185" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -15605,13 +15603,13 @@
       <c r="AB186" s="71" t="n"/>
       <c r="AC186" s="71" t="n"/>
       <c r="AD186" s="71" t="n"/>
-      <c r="AE186" s="88" t="n">
+      <c r="AE186" s="91" t="n">
         <v>45931</v>
       </c>
-      <c r="AF186" s="88" t="n">
+      <c r="AF186" s="91" t="n">
         <v>45922</v>
       </c>
-      <c r="AG186" s="88" t="n">
+      <c r="AG186" s="91" t="n">
         <v>46287</v>
       </c>
       <c r="AH186" s="6" t="inlineStr">
@@ -15687,11 +15685,11 @@
       <c r="AB187" s="71" t="n"/>
       <c r="AC187" s="71" t="n"/>
       <c r="AD187" s="71" t="n"/>
-      <c r="AE187" s="88" t="n">
+      <c r="AE187" s="91" t="n">
         <v>46034</v>
       </c>
-      <c r="AF187" s="88" t="n"/>
-      <c r="AG187" s="88" t="n"/>
+      <c r="AF187" s="91" t="n"/>
+      <c r="AG187" s="91" t="n"/>
       <c r="AH187" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -15765,11 +15763,11 @@
       <c r="AB188" s="71" t="n"/>
       <c r="AC188" s="71" t="n"/>
       <c r="AD188" s="71" t="n"/>
-      <c r="AE188" s="88" t="n">
+      <c r="AE188" s="91" t="n">
         <v>44713</v>
       </c>
-      <c r="AF188" s="88" t="n"/>
-      <c r="AG188" s="88" t="n"/>
+      <c r="AF188" s="91" t="n"/>
+      <c r="AG188" s="91" t="n"/>
       <c r="AH188" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -15843,11 +15841,11 @@
       <c r="AB189" s="71" t="n"/>
       <c r="AC189" s="71" t="n"/>
       <c r="AD189" s="71" t="n"/>
-      <c r="AE189" s="88" t="n">
+      <c r="AE189" s="91" t="n">
         <v>45558</v>
       </c>
-      <c r="AF189" s="88" t="n"/>
-      <c r="AG189" s="88" t="n"/>
+      <c r="AF189" s="91" t="n"/>
+      <c r="AG189" s="91" t="n"/>
       <c r="AH189" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -15921,11 +15919,11 @@
       <c r="AB190" s="71" t="n"/>
       <c r="AC190" s="71" t="n"/>
       <c r="AD190" s="71" t="n"/>
-      <c r="AE190" s="88" t="n">
+      <c r="AE190" s="91" t="n">
         <v>46156</v>
       </c>
-      <c r="AF190" s="88" t="n"/>
-      <c r="AG190" s="88" t="n"/>
+      <c r="AF190" s="91" t="n"/>
+      <c r="AG190" s="91" t="n"/>
       <c r="AH190" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -15999,11 +15997,11 @@
       <c r="AB191" s="71" t="n"/>
       <c r="AC191" s="71" t="n"/>
       <c r="AD191" s="71" t="n"/>
-      <c r="AE191" s="88" t="n">
+      <c r="AE191" s="91" t="n">
         <v>45793</v>
       </c>
-      <c r="AF191" s="88" t="n"/>
-      <c r="AG191" s="88" t="n"/>
+      <c r="AF191" s="91" t="n"/>
+      <c r="AG191" s="91" t="n"/>
       <c r="AH191" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -16077,11 +16075,11 @@
       <c r="AB192" s="71" t="n"/>
       <c r="AC192" s="71" t="n"/>
       <c r="AD192" s="71" t="n"/>
-      <c r="AE192" s="88" t="n">
+      <c r="AE192" s="91" t="n">
         <v>46155</v>
       </c>
-      <c r="AF192" s="88" t="n"/>
-      <c r="AG192" s="88" t="n"/>
+      <c r="AF192" s="91" t="n"/>
+      <c r="AG192" s="91" t="n"/>
       <c r="AH192" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -16155,11 +16153,11 @@
       <c r="AB193" s="71" t="n"/>
       <c r="AC193" s="71" t="n"/>
       <c r="AD193" s="71" t="n"/>
-      <c r="AE193" s="88" t="n">
+      <c r="AE193" s="91" t="n">
         <v>40931</v>
       </c>
-      <c r="AF193" s="88" t="n"/>
-      <c r="AG193" s="88" t="n"/>
+      <c r="AF193" s="91" t="n"/>
+      <c r="AG193" s="91" t="n"/>
       <c r="AH193" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -16233,11 +16231,11 @@
       <c r="AB194" s="71" t="n"/>
       <c r="AC194" s="71" t="n"/>
       <c r="AD194" s="71" t="n"/>
-      <c r="AE194" s="88" t="n">
+      <c r="AE194" s="91" t="n">
         <v>45252</v>
       </c>
-      <c r="AF194" s="88" t="n"/>
-      <c r="AG194" s="88" t="n"/>
+      <c r="AF194" s="91" t="n"/>
+      <c r="AG194" s="91" t="n"/>
       <c r="AH194" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -16311,11 +16309,11 @@
       <c r="AB195" s="71" t="n"/>
       <c r="AC195" s="71" t="n"/>
       <c r="AD195" s="71" t="n"/>
-      <c r="AE195" s="88" t="n">
+      <c r="AE195" s="91" t="n">
         <v>45265</v>
       </c>
-      <c r="AF195" s="88" t="n"/>
-      <c r="AG195" s="88" t="n"/>
+      <c r="AF195" s="91" t="n"/>
+      <c r="AG195" s="91" t="n"/>
       <c r="AH195" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -16389,11 +16387,11 @@
       <c r="AB196" s="71" t="n"/>
       <c r="AC196" s="71" t="n"/>
       <c r="AD196" s="71" t="n"/>
-      <c r="AE196" s="88" t="n">
+      <c r="AE196" s="91" t="n">
         <v>46119</v>
       </c>
-      <c r="AF196" s="88" t="n"/>
-      <c r="AG196" s="88" t="n"/>
+      <c r="AF196" s="91" t="n"/>
+      <c r="AG196" s="91" t="n"/>
       <c r="AH196" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -16467,11 +16465,11 @@
       <c r="AB197" s="71" t="n"/>
       <c r="AC197" s="71" t="n"/>
       <c r="AD197" s="71" t="n"/>
-      <c r="AE197" s="88" t="n">
+      <c r="AE197" s="91" t="n">
         <v>46094</v>
       </c>
-      <c r="AF197" s="88" t="n"/>
-      <c r="AG197" s="88" t="n"/>
+      <c r="AF197" s="91" t="n"/>
+      <c r="AG197" s="91" t="n"/>
       <c r="AH197" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -16545,11 +16543,11 @@
       <c r="AB198" s="71" t="n"/>
       <c r="AC198" s="71" t="n"/>
       <c r="AD198" s="71" t="n"/>
-      <c r="AE198" s="88" t="n">
+      <c r="AE198" s="91" t="n">
         <v>46055</v>
       </c>
-      <c r="AF198" s="88" t="n"/>
-      <c r="AG198" s="88" t="n"/>
+      <c r="AF198" s="91" t="n"/>
+      <c r="AG198" s="91" t="n"/>
       <c r="AH198" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -16623,11 +16621,11 @@
       <c r="AB199" s="71" t="n"/>
       <c r="AC199" s="71" t="n"/>
       <c r="AD199" s="71" t="n"/>
-      <c r="AE199" s="88" t="n">
+      <c r="AE199" s="91" t="n">
         <v>45516</v>
       </c>
-      <c r="AF199" s="88" t="n"/>
-      <c r="AG199" s="88" t="n"/>
+      <c r="AF199" s="91" t="n"/>
+      <c r="AG199" s="91" t="n"/>
       <c r="AH199" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -16701,11 +16699,11 @@
       <c r="AB200" s="71" t="n"/>
       <c r="AC200" s="71" t="n"/>
       <c r="AD200" s="71" t="n"/>
-      <c r="AE200" s="88" t="n">
+      <c r="AE200" s="91" t="n">
         <v>44602</v>
       </c>
-      <c r="AF200" s="88" t="n"/>
-      <c r="AG200" s="88" t="n"/>
+      <c r="AF200" s="91" t="n"/>
+      <c r="AG200" s="91" t="n"/>
       <c r="AH200" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -16779,11 +16777,11 @@
       <c r="AB201" s="71" t="n"/>
       <c r="AC201" s="71" t="n"/>
       <c r="AD201" s="71" t="n"/>
-      <c r="AE201" s="88" t="n">
+      <c r="AE201" s="91" t="n">
         <v>45243</v>
       </c>
-      <c r="AF201" s="88" t="n"/>
-      <c r="AG201" s="88" t="n"/>
+      <c r="AF201" s="91" t="n"/>
+      <c r="AG201" s="91" t="n"/>
       <c r="AH201" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -16857,11 +16855,11 @@
       <c r="AB202" s="71" t="n"/>
       <c r="AC202" s="71" t="n"/>
       <c r="AD202" s="71" t="n"/>
-      <c r="AE202" s="88" t="n">
+      <c r="AE202" s="91" t="n">
         <v>45250</v>
       </c>
-      <c r="AF202" s="88" t="n"/>
-      <c r="AG202" s="88" t="n"/>
+      <c r="AF202" s="91" t="n"/>
+      <c r="AG202" s="91" t="n"/>
       <c r="AH202" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -16935,11 +16933,11 @@
       <c r="AB203" s="71" t="n"/>
       <c r="AC203" s="71" t="n"/>
       <c r="AD203" s="71" t="n"/>
-      <c r="AE203" s="88" t="n">
+      <c r="AE203" s="91" t="n">
         <v>45560</v>
       </c>
-      <c r="AF203" s="88" t="n"/>
-      <c r="AG203" s="88" t="n"/>
+      <c r="AF203" s="91" t="n"/>
+      <c r="AG203" s="91" t="n"/>
       <c r="AH203" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -17013,13 +17011,13 @@
       <c r="AB204" s="71" t="n"/>
       <c r="AC204" s="71" t="n"/>
       <c r="AD204" s="71" t="n"/>
-      <c r="AE204" s="88" t="n">
+      <c r="AE204" s="91" t="n">
         <v>45937</v>
       </c>
-      <c r="AF204" s="88" t="n">
+      <c r="AF204" s="91" t="n">
         <v>45932</v>
       </c>
-      <c r="AG204" s="88" t="n">
+      <c r="AG204" s="91" t="n">
         <v>46297</v>
       </c>
       <c r="AH204" s="6" t="inlineStr">
@@ -17095,11 +17093,11 @@
       <c r="AB205" s="71" t="n"/>
       <c r="AC205" s="71" t="n"/>
       <c r="AD205" s="71" t="n"/>
-      <c r="AE205" s="88" t="n">
+      <c r="AE205" s="91" t="n">
         <v>45544</v>
       </c>
-      <c r="AF205" s="88" t="n"/>
-      <c r="AG205" s="88" t="n"/>
+      <c r="AF205" s="91" t="n"/>
+      <c r="AG205" s="91" t="n"/>
       <c r="AH205" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -17173,11 +17171,11 @@
       <c r="AB206" s="71" t="n"/>
       <c r="AC206" s="71" t="n"/>
       <c r="AD206" s="71" t="n"/>
-      <c r="AE206" s="88" t="n">
+      <c r="AE206" s="91" t="n">
         <v>45545</v>
       </c>
-      <c r="AF206" s="88" t="n"/>
-      <c r="AG206" s="88" t="n"/>
+      <c r="AF206" s="91" t="n"/>
+      <c r="AG206" s="91" t="n"/>
       <c r="AH206" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -17251,11 +17249,11 @@
       <c r="AB207" s="71" t="n"/>
       <c r="AC207" s="71" t="n"/>
       <c r="AD207" s="71" t="n"/>
-      <c r="AE207" s="88" t="n">
+      <c r="AE207" s="91" t="n">
         <v>42494</v>
       </c>
-      <c r="AF207" s="88" t="n"/>
-      <c r="AG207" s="88" t="n"/>
+      <c r="AF207" s="91" t="n"/>
+      <c r="AG207" s="91" t="n"/>
       <c r="AH207" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -17329,11 +17327,11 @@
       <c r="AB208" s="71" t="n"/>
       <c r="AC208" s="71" t="n"/>
       <c r="AD208" s="71" t="n"/>
-      <c r="AE208" s="88" t="n">
+      <c r="AE208" s="91" t="n">
         <v>45551</v>
       </c>
-      <c r="AF208" s="88" t="n"/>
-      <c r="AG208" s="88" t="n"/>
+      <c r="AF208" s="91" t="n"/>
+      <c r="AG208" s="91" t="n"/>
       <c r="AH208" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -17407,11 +17405,11 @@
       <c r="AB209" s="71" t="n"/>
       <c r="AC209" s="71" t="n"/>
       <c r="AD209" s="71" t="n"/>
-      <c r="AE209" s="88" t="n">
+      <c r="AE209" s="91" t="n">
         <v>45497</v>
       </c>
-      <c r="AF209" s="88" t="n"/>
-      <c r="AG209" s="88" t="n"/>
+      <c r="AF209" s="91" t="n"/>
+      <c r="AG209" s="91" t="n"/>
       <c r="AH209" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -17485,11 +17483,11 @@
       <c r="AB210" s="71" t="n"/>
       <c r="AC210" s="71" t="n"/>
       <c r="AD210" s="71" t="n"/>
-      <c r="AE210" s="88" t="n">
+      <c r="AE210" s="91" t="n">
         <v>46057</v>
       </c>
-      <c r="AF210" s="88" t="n"/>
-      <c r="AG210" s="88" t="n"/>
+      <c r="AF210" s="91" t="n"/>
+      <c r="AG210" s="91" t="n"/>
       <c r="AH210" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -17563,11 +17561,11 @@
       <c r="AB211" s="71" t="n"/>
       <c r="AC211" s="71" t="n"/>
       <c r="AD211" s="71" t="n"/>
-      <c r="AE211" s="88" t="n">
+      <c r="AE211" s="91" t="n">
         <v>42156</v>
       </c>
-      <c r="AF211" s="88" t="n"/>
-      <c r="AG211" s="88" t="n"/>
+      <c r="AF211" s="91" t="n"/>
+      <c r="AG211" s="91" t="n"/>
       <c r="AH211" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -17641,11 +17639,11 @@
       <c r="AB212" s="71" t="n"/>
       <c r="AC212" s="71" t="n"/>
       <c r="AD212" s="71" t="n"/>
-      <c r="AE212" s="88" t="n">
+      <c r="AE212" s="91" t="n">
         <v>44718</v>
       </c>
-      <c r="AF212" s="88" t="n"/>
-      <c r="AG212" s="88" t="n"/>
+      <c r="AF212" s="91" t="n"/>
+      <c r="AG212" s="91" t="n"/>
       <c r="AH212" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -17719,11 +17717,11 @@
       <c r="AB213" s="71" t="n"/>
       <c r="AC213" s="71" t="n"/>
       <c r="AD213" s="71" t="n"/>
-      <c r="AE213" s="88" t="n">
+      <c r="AE213" s="91" t="n">
         <v>45194</v>
       </c>
-      <c r="AF213" s="88" t="n"/>
-      <c r="AG213" s="88" t="n"/>
+      <c r="AF213" s="91" t="n"/>
+      <c r="AG213" s="91" t="n"/>
       <c r="AH213" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -17797,11 +17795,11 @@
       <c r="AB214" s="71" t="n"/>
       <c r="AC214" s="71" t="n"/>
       <c r="AD214" s="71" t="n"/>
-      <c r="AE214" s="88" t="n">
+      <c r="AE214" s="91" t="n">
         <v>45859</v>
       </c>
-      <c r="AF214" s="88" t="n"/>
-      <c r="AG214" s="88" t="n"/>
+      <c r="AF214" s="91" t="n"/>
+      <c r="AG214" s="91" t="n"/>
       <c r="AH214" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -17875,11 +17873,11 @@
       <c r="AB215" s="71" t="n"/>
       <c r="AC215" s="71" t="n"/>
       <c r="AD215" s="71" t="n"/>
-      <c r="AE215" s="88" t="n">
+      <c r="AE215" s="91" t="n">
         <v>44621</v>
       </c>
-      <c r="AF215" s="88" t="n"/>
-      <c r="AG215" s="88" t="n"/>
+      <c r="AF215" s="91" t="n"/>
+      <c r="AG215" s="91" t="n"/>
       <c r="AH215" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -17953,11 +17951,11 @@
       <c r="AB216" s="71" t="n"/>
       <c r="AC216" s="71" t="n"/>
       <c r="AD216" s="71" t="n"/>
-      <c r="AE216" s="88" t="n">
+      <c r="AE216" s="91" t="n">
         <v>45819</v>
       </c>
-      <c r="AF216" s="88" t="n"/>
-      <c r="AG216" s="88" t="n"/>
+      <c r="AF216" s="91" t="n"/>
+      <c r="AG216" s="91" t="n"/>
       <c r="AH216" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -18031,13 +18029,13 @@
       <c r="AB217" s="71" t="n"/>
       <c r="AC217" s="71" t="n"/>
       <c r="AD217" s="71" t="n"/>
-      <c r="AE217" s="88" t="n">
+      <c r="AE217" s="91" t="n">
         <v>45968</v>
       </c>
-      <c r="AF217" s="88" t="n">
+      <c r="AF217" s="91" t="n">
         <v>45957</v>
       </c>
-      <c r="AG217" s="88" t="n">
+      <c r="AG217" s="91" t="n">
         <v>46322</v>
       </c>
       <c r="AH217" s="6" t="inlineStr">
@@ -18113,11 +18111,11 @@
       <c r="AB218" s="71" t="n"/>
       <c r="AC218" s="71" t="n"/>
       <c r="AD218" s="71" t="n"/>
-      <c r="AE218" s="88" t="n">
+      <c r="AE218" s="91" t="n">
         <v>45034</v>
       </c>
-      <c r="AF218" s="88" t="n"/>
-      <c r="AG218" s="88" t="n"/>
+      <c r="AF218" s="91" t="n"/>
+      <c r="AG218" s="91" t="n"/>
       <c r="AH218" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -18191,11 +18189,11 @@
       <c r="AB219" s="71" t="n"/>
       <c r="AC219" s="71" t="n"/>
       <c r="AD219" s="71" t="n"/>
-      <c r="AE219" s="88" t="n">
+      <c r="AE219" s="91" t="n">
         <v>43132</v>
       </c>
-      <c r="AF219" s="88" t="n"/>
-      <c r="AG219" s="88" t="n"/>
+      <c r="AF219" s="91" t="n"/>
+      <c r="AG219" s="91" t="n"/>
       <c r="AH219" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -18269,11 +18267,11 @@
       <c r="AB220" s="71" t="n"/>
       <c r="AC220" s="71" t="n"/>
       <c r="AD220" s="71" t="n"/>
-      <c r="AE220" s="88" t="n">
+      <c r="AE220" s="91" t="n">
         <v>46077</v>
       </c>
-      <c r="AF220" s="88" t="n"/>
-      <c r="AG220" s="88" t="n"/>
+      <c r="AF220" s="91" t="n"/>
+      <c r="AG220" s="91" t="n"/>
       <c r="AH220" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -18347,11 +18345,11 @@
       <c r="AB221" s="71" t="n"/>
       <c r="AC221" s="71" t="n"/>
       <c r="AD221" s="71" t="n"/>
-      <c r="AE221" s="88" t="n">
+      <c r="AE221" s="91" t="n">
         <v>40088</v>
       </c>
-      <c r="AF221" s="88" t="n"/>
-      <c r="AG221" s="88" t="n"/>
+      <c r="AF221" s="91" t="n"/>
+      <c r="AG221" s="91" t="n"/>
       <c r="AH221" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -18425,11 +18423,11 @@
       <c r="AB222" s="71" t="n"/>
       <c r="AC222" s="71" t="n"/>
       <c r="AD222" s="71" t="n"/>
-      <c r="AE222" s="88" t="n">
+      <c r="AE222" s="91" t="n">
         <v>42380</v>
       </c>
-      <c r="AF222" s="88" t="n"/>
-      <c r="AG222" s="88" t="n"/>
+      <c r="AF222" s="91" t="n"/>
+      <c r="AG222" s="91" t="n"/>
       <c r="AH222" s="6" t="inlineStr">
         <is>
           <t>Нет сведений об осмотрах</t>
@@ -18499,14 +18497,10 @@
       <c r="AB223" s="71" t="n"/>
       <c r="AC223" s="71" t="n"/>
       <c r="AD223" s="71" t="n"/>
-      <c r="AE223" s="88" t="n"/>
-      <c r="AF223" s="88" t="n"/>
-      <c r="AG223" s="88" t="n"/>
-      <c r="AH223" s="6" t="inlineStr">
-        <is>
-          <t>Не входит в список периодич. осмотра</t>
-        </is>
-      </c>
+      <c r="AE223" s="91" t="n"/>
+      <c r="AF223" s="91" t="n"/>
+      <c r="AG223" s="91" t="n"/>
+      <c r="AH223" s="6" t="n"/>
       <c r="AI223" s="6" t="inlineStr">
         <is>
           <t>п.11 Прил.№2: обслуживание электроустановок предприятия.</t>

--- a/Шаблон ЛМК проф ОПО — Машково и Руднево.xlsx
+++ b/Шаблон ЛМК проф ОПО — Машково и Руднево.xlsx
@@ -886,7 +886,7 @@
     <col width="19.85546875" customWidth="1" style="30" min="25" max="25"/>
     <col hidden="1" width="21.5703125" customWidth="1" style="30" min="26" max="29"/>
     <col width="36.140625" customWidth="1" style="30" min="30" max="30"/>
-    <col width="19.85546875" customWidth="1" style="30" min="31" max="31"/>
+    <col width="14" customWidth="1" style="30" min="31" max="31"/>
     <col width="10" customWidth="1" style="30" min="32" max="50"/>
   </cols>
   <sheetData>
@@ -1117,7 +1117,11 @@
           <t>Организация</t>
         </is>
       </c>
-      <c r="AE2" s="5" t="n"/>
+      <c r="AE2" s="16" t="inlineStr">
+        <is>
+          <t>Площадка</t>
+        </is>
+      </c>
       <c r="AF2" s="5" t="n"/>
       <c r="AG2" s="5" t="n"/>
       <c r="AH2" s="5" t="n"/>
@@ -1185,7 +1189,11 @@
       <c r="AB3" s="71" t="n"/>
       <c r="AC3" s="71" t="n"/>
       <c r="AD3" s="71" t="n"/>
-      <c r="AE3" s="6" t="n"/>
+      <c r="AE3" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF3" s="6" t="n"/>
       <c r="AG3" s="6" t="n"/>
       <c r="AH3" s="6" t="n"/>
@@ -1253,7 +1261,11 @@
       <c r="AB4" s="71" t="n"/>
       <c r="AC4" s="71" t="n"/>
       <c r="AD4" s="71" t="n"/>
-      <c r="AE4" s="6" t="n"/>
+      <c r="AE4" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF4" s="6" t="n"/>
       <c r="AG4" s="6" t="n"/>
       <c r="AH4" s="6" t="n"/>
@@ -1321,7 +1333,11 @@
       <c r="AB5" s="71" t="n"/>
       <c r="AC5" s="71" t="n"/>
       <c r="AD5" s="71" t="n"/>
-      <c r="AE5" s="6" t="n"/>
+      <c r="AE5" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF5" s="6" t="n"/>
       <c r="AG5" s="6" t="n"/>
       <c r="AH5" s="6" t="n"/>
@@ -1389,7 +1405,11 @@
       <c r="AB6" s="71" t="n"/>
       <c r="AC6" s="71" t="n"/>
       <c r="AD6" s="71" t="n"/>
-      <c r="AE6" s="6" t="n"/>
+      <c r="AE6" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF6" s="6" t="n"/>
       <c r="AG6" s="6" t="n"/>
       <c r="AH6" s="6" t="n"/>
@@ -1457,7 +1477,11 @@
       <c r="AB7" s="71" t="n"/>
       <c r="AC7" s="71" t="n"/>
       <c r="AD7" s="71" t="n"/>
-      <c r="AE7" s="6" t="n"/>
+      <c r="AE7" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF7" s="6" t="n"/>
       <c r="AG7" s="6" t="n"/>
       <c r="AH7" s="6" t="n"/>
@@ -1525,7 +1549,11 @@
       <c r="AB8" s="71" t="n"/>
       <c r="AC8" s="71" t="n"/>
       <c r="AD8" s="71" t="n"/>
-      <c r="AE8" s="6" t="n"/>
+      <c r="AE8" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF8" s="6" t="n"/>
       <c r="AG8" s="6" t="n"/>
       <c r="AH8" s="6" t="n"/>
@@ -1593,7 +1621,11 @@
       <c r="AB9" s="71" t="n"/>
       <c r="AC9" s="71" t="n"/>
       <c r="AD9" s="71" t="n"/>
-      <c r="AE9" s="6" t="n"/>
+      <c r="AE9" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF9" s="6" t="n"/>
       <c r="AG9" s="6" t="n"/>
       <c r="AH9" s="6" t="n"/>
@@ -1661,7 +1693,11 @@
       <c r="AB10" s="71" t="n"/>
       <c r="AC10" s="71" t="n"/>
       <c r="AD10" s="71" t="n"/>
-      <c r="AE10" s="6" t="n"/>
+      <c r="AE10" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF10" s="6" t="n"/>
       <c r="AG10" s="6" t="n"/>
       <c r="AH10" s="6" t="n"/>
@@ -1729,7 +1765,11 @@
       <c r="AB11" s="71" t="n"/>
       <c r="AC11" s="71" t="n"/>
       <c r="AD11" s="71" t="n"/>
-      <c r="AE11" s="6" t="n"/>
+      <c r="AE11" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF11" s="6" t="n"/>
       <c r="AG11" s="6" t="n"/>
       <c r="AH11" s="6" t="n"/>
@@ -1797,7 +1837,11 @@
       <c r="AB12" s="71" t="n"/>
       <c r="AC12" s="71" t="n"/>
       <c r="AD12" s="71" t="n"/>
-      <c r="AE12" s="6" t="n"/>
+      <c r="AE12" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF12" s="6" t="n"/>
       <c r="AG12" s="6" t="n"/>
       <c r="AH12" s="6" t="n"/>
@@ -1865,7 +1909,11 @@
       <c r="AB13" s="71" t="n"/>
       <c r="AC13" s="71" t="n"/>
       <c r="AD13" s="71" t="n"/>
-      <c r="AE13" s="6" t="n"/>
+      <c r="AE13" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF13" s="6" t="n"/>
       <c r="AG13" s="6" t="n"/>
       <c r="AH13" s="6" t="n"/>
@@ -1933,7 +1981,11 @@
       <c r="AB14" s="71" t="n"/>
       <c r="AC14" s="71" t="n"/>
       <c r="AD14" s="71" t="n"/>
-      <c r="AE14" s="6" t="n"/>
+      <c r="AE14" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF14" s="6" t="n"/>
       <c r="AG14" s="6" t="n"/>
       <c r="AH14" s="6" t="n"/>
@@ -2001,7 +2053,11 @@
       <c r="AB15" s="71" t="n"/>
       <c r="AC15" s="71" t="n"/>
       <c r="AD15" s="71" t="n"/>
-      <c r="AE15" s="6" t="n"/>
+      <c r="AE15" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF15" s="6" t="n"/>
       <c r="AG15" s="6" t="n"/>
       <c r="AH15" s="6" t="n"/>
@@ -2069,7 +2125,11 @@
       <c r="AB16" s="71" t="n"/>
       <c r="AC16" s="71" t="n"/>
       <c r="AD16" s="71" t="n"/>
-      <c r="AE16" s="6" t="n"/>
+      <c r="AE16" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF16" s="6" t="n"/>
       <c r="AG16" s="6" t="n"/>
       <c r="AH16" s="6" t="n"/>
@@ -2137,7 +2197,11 @@
       <c r="AB17" s="71" t="n"/>
       <c r="AC17" s="71" t="n"/>
       <c r="AD17" s="71" t="n"/>
-      <c r="AE17" s="6" t="n"/>
+      <c r="AE17" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF17" s="6" t="n"/>
       <c r="AG17" s="6" t="n"/>
       <c r="AH17" s="6" t="n"/>
@@ -2205,7 +2269,11 @@
       <c r="AB18" s="71" t="n"/>
       <c r="AC18" s="71" t="n"/>
       <c r="AD18" s="71" t="n"/>
-      <c r="AE18" s="6" t="n"/>
+      <c r="AE18" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF18" s="6" t="n"/>
       <c r="AG18" s="6" t="n"/>
       <c r="AH18" s="6" t="n"/>
@@ -2273,7 +2341,11 @@
       <c r="AB19" s="71" t="n"/>
       <c r="AC19" s="71" t="n"/>
       <c r="AD19" s="71" t="n"/>
-      <c r="AE19" s="6" t="n"/>
+      <c r="AE19" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF19" s="6" t="n"/>
       <c r="AG19" s="6" t="n"/>
       <c r="AH19" s="6" t="n"/>
@@ -2341,7 +2413,11 @@
       <c r="AB20" s="71" t="n"/>
       <c r="AC20" s="71" t="n"/>
       <c r="AD20" s="71" t="n"/>
-      <c r="AE20" s="6" t="n"/>
+      <c r="AE20" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF20" s="6" t="n"/>
       <c r="AG20" s="6" t="n"/>
       <c r="AH20" s="6" t="n"/>
@@ -2409,7 +2485,11 @@
       <c r="AB21" s="71" t="n"/>
       <c r="AC21" s="71" t="n"/>
       <c r="AD21" s="71" t="n"/>
-      <c r="AE21" s="6" t="n"/>
+      <c r="AE21" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF21" s="6" t="n"/>
       <c r="AG21" s="6" t="n"/>
       <c r="AH21" s="6" t="n"/>
@@ -2477,7 +2557,11 @@
       <c r="AB22" s="71" t="n"/>
       <c r="AC22" s="71" t="n"/>
       <c r="AD22" s="71" t="n"/>
-      <c r="AE22" s="6" t="n"/>
+      <c r="AE22" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF22" s="6" t="n"/>
       <c r="AG22" s="6" t="n"/>
       <c r="AH22" s="6" t="n"/>
@@ -2545,7 +2629,11 @@
       <c r="AB23" s="71" t="n"/>
       <c r="AC23" s="71" t="n"/>
       <c r="AD23" s="71" t="n"/>
-      <c r="AE23" s="6" t="n"/>
+      <c r="AE23" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF23" s="6" t="n"/>
       <c r="AG23" s="6" t="n"/>
       <c r="AH23" s="6" t="n"/>
@@ -2613,7 +2701,11 @@
       <c r="AB24" s="71" t="n"/>
       <c r="AC24" s="71" t="n"/>
       <c r="AD24" s="71" t="n"/>
-      <c r="AE24" s="6" t="n"/>
+      <c r="AE24" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF24" s="6" t="n"/>
       <c r="AG24" s="6" t="n"/>
       <c r="AH24" s="6" t="n"/>
@@ -2681,7 +2773,11 @@
       <c r="AB25" s="71" t="n"/>
       <c r="AC25" s="71" t="n"/>
       <c r="AD25" s="71" t="n"/>
-      <c r="AE25" s="6" t="n"/>
+      <c r="AE25" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF25" s="6" t="n"/>
       <c r="AG25" s="6" t="n"/>
       <c r="AH25" s="6" t="n"/>
@@ -2749,7 +2845,11 @@
       <c r="AB26" s="71" t="n"/>
       <c r="AC26" s="71" t="n"/>
       <c r="AD26" s="71" t="n"/>
-      <c r="AE26" s="6" t="n"/>
+      <c r="AE26" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF26" s="6" t="n"/>
       <c r="AG26" s="6" t="n"/>
       <c r="AH26" s="6" t="n"/>
@@ -2817,7 +2917,11 @@
       <c r="AB27" s="71" t="n"/>
       <c r="AC27" s="71" t="n"/>
       <c r="AD27" s="71" t="n"/>
-      <c r="AE27" s="6" t="n"/>
+      <c r="AE27" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF27" s="6" t="n"/>
       <c r="AG27" s="6" t="n"/>
       <c r="AH27" s="6" t="n"/>
@@ -2885,7 +2989,11 @@
       <c r="AB28" s="71" t="n"/>
       <c r="AC28" s="71" t="n"/>
       <c r="AD28" s="71" t="n"/>
-      <c r="AE28" s="6" t="n"/>
+      <c r="AE28" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF28" s="6" t="n"/>
       <c r="AG28" s="6" t="n"/>
       <c r="AH28" s="6" t="n"/>
@@ -2953,7 +3061,11 @@
       <c r="AB29" s="71" t="n"/>
       <c r="AC29" s="71" t="n"/>
       <c r="AD29" s="71" t="n"/>
-      <c r="AE29" s="6" t="n"/>
+      <c r="AE29" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF29" s="6" t="n"/>
       <c r="AG29" s="6" t="n"/>
       <c r="AH29" s="6" t="n"/>
@@ -3021,7 +3133,11 @@
       <c r="AB30" s="71" t="n"/>
       <c r="AC30" s="71" t="n"/>
       <c r="AD30" s="71" t="n"/>
-      <c r="AE30" s="6" t="n"/>
+      <c r="AE30" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF30" s="6" t="n"/>
       <c r="AG30" s="6" t="n"/>
       <c r="AH30" s="6" t="n"/>
@@ -3089,7 +3205,11 @@
       <c r="AB31" s="71" t="n"/>
       <c r="AC31" s="71" t="n"/>
       <c r="AD31" s="71" t="n"/>
-      <c r="AE31" s="6" t="n"/>
+      <c r="AE31" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF31" s="6" t="n"/>
       <c r="AG31" s="6" t="n"/>
       <c r="AH31" s="6" t="n"/>
@@ -3157,7 +3277,11 @@
       <c r="AB32" s="71" t="n"/>
       <c r="AC32" s="71" t="n"/>
       <c r="AD32" s="71" t="n"/>
-      <c r="AE32" s="6" t="n"/>
+      <c r="AE32" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF32" s="6" t="n"/>
       <c r="AG32" s="6" t="n"/>
       <c r="AH32" s="6" t="n"/>
@@ -3225,7 +3349,11 @@
       <c r="AB33" s="71" t="n"/>
       <c r="AC33" s="71" t="n"/>
       <c r="AD33" s="71" t="n"/>
-      <c r="AE33" s="6" t="n"/>
+      <c r="AE33" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF33" s="6" t="n"/>
       <c r="AG33" s="6" t="n"/>
       <c r="AH33" s="6" t="n"/>
@@ -3293,7 +3421,11 @@
       <c r="AB34" s="71" t="n"/>
       <c r="AC34" s="71" t="n"/>
       <c r="AD34" s="71" t="n"/>
-      <c r="AE34" s="6" t="n"/>
+      <c r="AE34" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF34" s="6" t="n"/>
       <c r="AG34" s="6" t="n"/>
       <c r="AH34" s="6" t="n"/>
@@ -3361,7 +3493,11 @@
       <c r="AB35" s="71" t="n"/>
       <c r="AC35" s="71" t="n"/>
       <c r="AD35" s="71" t="n"/>
-      <c r="AE35" s="6" t="n"/>
+      <c r="AE35" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF35" s="6" t="n"/>
       <c r="AG35" s="6" t="n"/>
       <c r="AH35" s="6" t="n"/>
@@ -3429,7 +3565,11 @@
       <c r="AB36" s="71" t="n"/>
       <c r="AC36" s="71" t="n"/>
       <c r="AD36" s="71" t="n"/>
-      <c r="AE36" s="6" t="n"/>
+      <c r="AE36" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF36" s="6" t="n"/>
       <c r="AG36" s="6" t="n"/>
       <c r="AH36" s="6" t="n"/>
@@ -3497,7 +3637,11 @@
       <c r="AB37" s="71" t="n"/>
       <c r="AC37" s="71" t="n"/>
       <c r="AD37" s="71" t="n"/>
-      <c r="AE37" s="6" t="n"/>
+      <c r="AE37" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF37" s="6" t="n"/>
       <c r="AG37" s="6" t="n"/>
       <c r="AH37" s="6" t="n"/>
@@ -3565,7 +3709,11 @@
       <c r="AB38" s="71" t="n"/>
       <c r="AC38" s="71" t="n"/>
       <c r="AD38" s="71" t="n"/>
-      <c r="AE38" s="6" t="n"/>
+      <c r="AE38" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF38" s="6" t="n"/>
       <c r="AG38" s="6" t="n"/>
       <c r="AH38" s="6" t="n"/>
@@ -3633,7 +3781,11 @@
       <c r="AB39" s="71" t="n"/>
       <c r="AC39" s="71" t="n"/>
       <c r="AD39" s="71" t="n"/>
-      <c r="AE39" s="6" t="n"/>
+      <c r="AE39" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF39" s="6" t="n"/>
       <c r="AG39" s="6" t="n"/>
       <c r="AH39" s="6" t="n"/>
@@ -3701,7 +3853,11 @@
       <c r="AB40" s="71" t="n"/>
       <c r="AC40" s="71" t="n"/>
       <c r="AD40" s="71" t="n"/>
-      <c r="AE40" s="6" t="n"/>
+      <c r="AE40" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF40" s="6" t="n"/>
       <c r="AG40" s="6" t="n"/>
       <c r="AH40" s="6" t="n"/>
@@ -3769,7 +3925,11 @@
       <c r="AB41" s="71" t="n"/>
       <c r="AC41" s="71" t="n"/>
       <c r="AD41" s="71" t="n"/>
-      <c r="AE41" s="6" t="n"/>
+      <c r="AE41" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF41" s="6" t="n"/>
       <c r="AG41" s="6" t="n"/>
       <c r="AH41" s="6" t="n"/>
@@ -3837,7 +3997,11 @@
       <c r="AB42" s="71" t="n"/>
       <c r="AC42" s="71" t="n"/>
       <c r="AD42" s="71" t="n"/>
-      <c r="AE42" s="6" t="n"/>
+      <c r="AE42" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF42" s="6" t="n"/>
       <c r="AG42" s="6" t="n"/>
       <c r="AH42" s="6" t="n"/>
@@ -3905,7 +4069,11 @@
       <c r="AB43" s="71" t="n"/>
       <c r="AC43" s="71" t="n"/>
       <c r="AD43" s="71" t="n"/>
-      <c r="AE43" s="6" t="n"/>
+      <c r="AE43" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF43" s="6" t="n"/>
       <c r="AG43" s="6" t="n"/>
       <c r="AH43" s="6" t="n"/>
@@ -3973,7 +4141,11 @@
       <c r="AB44" s="71" t="n"/>
       <c r="AC44" s="71" t="n"/>
       <c r="AD44" s="71" t="n"/>
-      <c r="AE44" s="6" t="n"/>
+      <c r="AE44" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF44" s="6" t="n"/>
       <c r="AG44" s="6" t="n"/>
       <c r="AH44" s="6" t="n"/>
@@ -4041,7 +4213,11 @@
       <c r="AB45" s="71" t="n"/>
       <c r="AC45" s="71" t="n"/>
       <c r="AD45" s="71" t="n"/>
-      <c r="AE45" s="6" t="n"/>
+      <c r="AE45" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF45" s="6" t="n"/>
       <c r="AG45" s="6" t="n"/>
       <c r="AH45" s="6" t="n"/>
@@ -4109,7 +4285,11 @@
       <c r="AB46" s="71" t="n"/>
       <c r="AC46" s="71" t="n"/>
       <c r="AD46" s="71" t="n"/>
-      <c r="AE46" s="6" t="n"/>
+      <c r="AE46" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF46" s="6" t="n"/>
       <c r="AG46" s="6" t="n"/>
       <c r="AH46" s="6" t="n"/>
@@ -4177,7 +4357,11 @@
       <c r="AB47" s="71" t="n"/>
       <c r="AC47" s="71" t="n"/>
       <c r="AD47" s="71" t="n"/>
-      <c r="AE47" s="6" t="n"/>
+      <c r="AE47" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF47" s="6" t="n"/>
       <c r="AG47" s="6" t="n"/>
       <c r="AH47" s="6" t="n"/>
@@ -4245,7 +4429,11 @@
       <c r="AB48" s="71" t="n"/>
       <c r="AC48" s="71" t="n"/>
       <c r="AD48" s="71" t="n"/>
-      <c r="AE48" s="6" t="n"/>
+      <c r="AE48" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF48" s="6" t="n"/>
       <c r="AG48" s="6" t="n"/>
       <c r="AH48" s="6" t="n"/>
@@ -4313,7 +4501,11 @@
       <c r="AB49" s="71" t="n"/>
       <c r="AC49" s="71" t="n"/>
       <c r="AD49" s="71" t="n"/>
-      <c r="AE49" s="6" t="n"/>
+      <c r="AE49" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF49" s="6" t="n"/>
       <c r="AG49" s="6" t="n"/>
       <c r="AH49" s="6" t="n"/>
@@ -4381,7 +4573,11 @@
       <c r="AB50" s="71" t="n"/>
       <c r="AC50" s="71" t="n"/>
       <c r="AD50" s="71" t="n"/>
-      <c r="AE50" s="6" t="n"/>
+      <c r="AE50" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF50" s="6" t="n"/>
       <c r="AG50" s="6" t="n"/>
       <c r="AH50" s="6" t="n"/>
@@ -4449,7 +4645,11 @@
       <c r="AB51" s="71" t="n"/>
       <c r="AC51" s="71" t="n"/>
       <c r="AD51" s="71" t="n"/>
-      <c r="AE51" s="6" t="n"/>
+      <c r="AE51" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF51" s="6" t="n"/>
       <c r="AG51" s="6" t="n"/>
       <c r="AH51" s="6" t="n"/>
@@ -4517,7 +4717,11 @@
       <c r="AB52" s="71" t="n"/>
       <c r="AC52" s="71" t="n"/>
       <c r="AD52" s="71" t="n"/>
-      <c r="AE52" s="6" t="n"/>
+      <c r="AE52" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF52" s="6" t="n"/>
       <c r="AG52" s="6" t="n"/>
       <c r="AH52" s="6" t="n"/>
@@ -4585,7 +4789,11 @@
       <c r="AB53" s="71" t="n"/>
       <c r="AC53" s="71" t="n"/>
       <c r="AD53" s="71" t="n"/>
-      <c r="AE53" s="6" t="n"/>
+      <c r="AE53" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF53" s="6" t="n"/>
       <c r="AG53" s="6" t="n"/>
       <c r="AH53" s="6" t="n"/>
@@ -4653,7 +4861,11 @@
       <c r="AB54" s="71" t="n"/>
       <c r="AC54" s="71" t="n"/>
       <c r="AD54" s="71" t="n"/>
-      <c r="AE54" s="6" t="n"/>
+      <c r="AE54" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF54" s="6" t="n"/>
       <c r="AG54" s="6" t="n"/>
       <c r="AH54" s="6" t="n"/>
@@ -4721,7 +4933,11 @@
       <c r="AB55" s="71" t="n"/>
       <c r="AC55" s="71" t="n"/>
       <c r="AD55" s="71" t="n"/>
-      <c r="AE55" s="6" t="n"/>
+      <c r="AE55" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF55" s="6" t="n"/>
       <c r="AG55" s="6" t="n"/>
       <c r="AH55" s="6" t="n"/>
@@ -4789,7 +5005,11 @@
       <c r="AB56" s="71" t="n"/>
       <c r="AC56" s="71" t="n"/>
       <c r="AD56" s="71" t="n"/>
-      <c r="AE56" s="6" t="n"/>
+      <c r="AE56" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF56" s="6" t="n"/>
       <c r="AG56" s="6" t="n"/>
       <c r="AH56" s="6" t="n"/>
@@ -4857,7 +5077,11 @@
       <c r="AB57" s="71" t="n"/>
       <c r="AC57" s="71" t="n"/>
       <c r="AD57" s="71" t="n"/>
-      <c r="AE57" s="6" t="n"/>
+      <c r="AE57" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF57" s="6" t="n"/>
       <c r="AG57" s="6" t="n"/>
       <c r="AH57" s="6" t="n"/>
@@ -4925,7 +5149,11 @@
       <c r="AB58" s="71" t="n"/>
       <c r="AC58" s="71" t="n"/>
       <c r="AD58" s="71" t="n"/>
-      <c r="AE58" s="6" t="n"/>
+      <c r="AE58" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF58" s="6" t="n"/>
       <c r="AG58" s="6" t="n"/>
       <c r="AH58" s="6" t="n"/>
@@ -4993,7 +5221,11 @@
       <c r="AB59" s="71" t="n"/>
       <c r="AC59" s="71" t="n"/>
       <c r="AD59" s="71" t="n"/>
-      <c r="AE59" s="6" t="n"/>
+      <c r="AE59" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF59" s="6" t="n"/>
       <c r="AG59" s="6" t="n"/>
       <c r="AH59" s="6" t="n"/>
@@ -5061,7 +5293,11 @@
       <c r="AB60" s="71" t="n"/>
       <c r="AC60" s="71" t="n"/>
       <c r="AD60" s="71" t="n"/>
-      <c r="AE60" s="6" t="n"/>
+      <c r="AE60" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF60" s="6" t="n"/>
       <c r="AG60" s="6" t="n"/>
       <c r="AH60" s="6" t="n"/>
@@ -5129,7 +5365,11 @@
       <c r="AB61" s="71" t="n"/>
       <c r="AC61" s="71" t="n"/>
       <c r="AD61" s="71" t="n"/>
-      <c r="AE61" s="6" t="n"/>
+      <c r="AE61" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF61" s="6" t="n"/>
       <c r="AG61" s="6" t="n"/>
       <c r="AH61" s="6" t="n"/>
@@ -5197,7 +5437,11 @@
       <c r="AB62" s="71" t="n"/>
       <c r="AC62" s="71" t="n"/>
       <c r="AD62" s="71" t="n"/>
-      <c r="AE62" s="6" t="n"/>
+      <c r="AE62" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF62" s="6" t="n"/>
       <c r="AG62" s="6" t="n"/>
       <c r="AH62" s="6" t="n"/>
@@ -5265,7 +5509,11 @@
       <c r="AB63" s="71" t="n"/>
       <c r="AC63" s="71" t="n"/>
       <c r="AD63" s="71" t="n"/>
-      <c r="AE63" s="6" t="n"/>
+      <c r="AE63" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF63" s="6" t="n"/>
       <c r="AG63" s="6" t="n"/>
       <c r="AH63" s="6" t="n"/>
@@ -5333,7 +5581,11 @@
       <c r="AB64" s="71" t="n"/>
       <c r="AC64" s="71" t="n"/>
       <c r="AD64" s="71" t="n"/>
-      <c r="AE64" s="6" t="n"/>
+      <c r="AE64" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF64" s="6" t="n"/>
       <c r="AG64" s="6" t="n"/>
       <c r="AH64" s="6" t="n"/>
@@ -5401,7 +5653,11 @@
       <c r="AB65" s="71" t="n"/>
       <c r="AC65" s="71" t="n"/>
       <c r="AD65" s="71" t="n"/>
-      <c r="AE65" s="6" t="n"/>
+      <c r="AE65" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF65" s="6" t="n"/>
       <c r="AG65" s="6" t="n"/>
       <c r="AH65" s="6" t="n"/>
@@ -5469,7 +5725,11 @@
       <c r="AB66" s="71" t="n"/>
       <c r="AC66" s="71" t="n"/>
       <c r="AD66" s="71" t="n"/>
-      <c r="AE66" s="6" t="n"/>
+      <c r="AE66" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF66" s="6" t="n"/>
       <c r="AG66" s="6" t="n"/>
       <c r="AH66" s="6" t="n"/>
@@ -5537,7 +5797,11 @@
       <c r="AB67" s="71" t="n"/>
       <c r="AC67" s="71" t="n"/>
       <c r="AD67" s="71" t="n"/>
-      <c r="AE67" s="6" t="n"/>
+      <c r="AE67" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF67" s="6" t="n"/>
       <c r="AG67" s="6" t="n"/>
       <c r="AH67" s="6" t="n"/>
@@ -5605,7 +5869,11 @@
       <c r="AB68" s="71" t="n"/>
       <c r="AC68" s="71" t="n"/>
       <c r="AD68" s="71" t="n"/>
-      <c r="AE68" s="6" t="n"/>
+      <c r="AE68" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF68" s="6" t="n"/>
       <c r="AG68" s="6" t="n"/>
       <c r="AH68" s="6" t="n"/>
@@ -5673,7 +5941,11 @@
       <c r="AB69" s="71" t="n"/>
       <c r="AC69" s="71" t="n"/>
       <c r="AD69" s="71" t="n"/>
-      <c r="AE69" s="6" t="n"/>
+      <c r="AE69" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF69" s="6" t="n"/>
       <c r="AG69" s="6" t="n"/>
       <c r="AH69" s="6" t="n"/>
@@ -5741,7 +6013,11 @@
       <c r="AB70" s="71" t="n"/>
       <c r="AC70" s="71" t="n"/>
       <c r="AD70" s="71" t="n"/>
-      <c r="AE70" s="6" t="n"/>
+      <c r="AE70" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF70" s="6" t="n"/>
       <c r="AG70" s="6" t="n"/>
       <c r="AH70" s="6" t="n"/>
@@ -5809,7 +6085,11 @@
       <c r="AB71" s="71" t="n"/>
       <c r="AC71" s="71" t="n"/>
       <c r="AD71" s="71" t="n"/>
-      <c r="AE71" s="6" t="n"/>
+      <c r="AE71" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF71" s="6" t="n"/>
       <c r="AG71" s="6" t="n"/>
       <c r="AH71" s="6" t="n"/>
@@ -5877,7 +6157,11 @@
       <c r="AB72" s="71" t="n"/>
       <c r="AC72" s="71" t="n"/>
       <c r="AD72" s="71" t="n"/>
-      <c r="AE72" s="6" t="n"/>
+      <c r="AE72" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF72" s="6" t="n"/>
       <c r="AG72" s="6" t="n"/>
       <c r="AH72" s="6" t="n"/>
@@ -5945,7 +6229,11 @@
       <c r="AB73" s="71" t="n"/>
       <c r="AC73" s="71" t="n"/>
       <c r="AD73" s="71" t="n"/>
-      <c r="AE73" s="6" t="n"/>
+      <c r="AE73" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF73" s="6" t="n"/>
       <c r="AG73" s="6" t="n"/>
       <c r="AH73" s="6" t="n"/>
@@ -6013,7 +6301,11 @@
       <c r="AB74" s="71" t="n"/>
       <c r="AC74" s="71" t="n"/>
       <c r="AD74" s="71" t="n"/>
-      <c r="AE74" s="6" t="n"/>
+      <c r="AE74" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF74" s="6" t="n"/>
       <c r="AG74" s="6" t="n"/>
       <c r="AH74" s="6" t="n"/>
@@ -6081,7 +6373,11 @@
       <c r="AB75" s="71" t="n"/>
       <c r="AC75" s="71" t="n"/>
       <c r="AD75" s="71" t="n"/>
-      <c r="AE75" s="6" t="n"/>
+      <c r="AE75" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF75" s="6" t="n"/>
       <c r="AG75" s="6" t="n"/>
       <c r="AH75" s="6" t="n"/>
@@ -6149,7 +6445,11 @@
       <c r="AB76" s="71" t="n"/>
       <c r="AC76" s="71" t="n"/>
       <c r="AD76" s="71" t="n"/>
-      <c r="AE76" s="6" t="n"/>
+      <c r="AE76" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF76" s="6" t="n"/>
       <c r="AG76" s="6" t="n"/>
       <c r="AH76" s="6" t="n"/>
@@ -6217,7 +6517,11 @@
       <c r="AB77" s="71" t="n"/>
       <c r="AC77" s="71" t="n"/>
       <c r="AD77" s="71" t="n"/>
-      <c r="AE77" s="6" t="n"/>
+      <c r="AE77" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF77" s="6" t="n"/>
       <c r="AG77" s="6" t="n"/>
       <c r="AH77" s="6" t="n"/>
@@ -6285,7 +6589,11 @@
       <c r="AB78" s="71" t="n"/>
       <c r="AC78" s="71" t="n"/>
       <c r="AD78" s="71" t="n"/>
-      <c r="AE78" s="6" t="n"/>
+      <c r="AE78" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF78" s="6" t="n"/>
       <c r="AG78" s="6" t="n"/>
       <c r="AH78" s="6" t="n"/>
@@ -6353,7 +6661,11 @@
       <c r="AB79" s="71" t="n"/>
       <c r="AC79" s="71" t="n"/>
       <c r="AD79" s="71" t="n"/>
-      <c r="AE79" s="6" t="n"/>
+      <c r="AE79" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF79" s="6" t="n"/>
       <c r="AG79" s="6" t="n"/>
       <c r="AH79" s="6" t="n"/>
@@ -6421,7 +6733,11 @@
       <c r="AB80" s="71" t="n"/>
       <c r="AC80" s="71" t="n"/>
       <c r="AD80" s="71" t="n"/>
-      <c r="AE80" s="6" t="n"/>
+      <c r="AE80" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF80" s="6" t="n"/>
       <c r="AG80" s="6" t="n"/>
       <c r="AH80" s="6" t="n"/>
@@ -6497,7 +6813,11 @@
       <c r="AB81" s="71" t="n"/>
       <c r="AC81" s="71" t="n"/>
       <c r="AD81" s="71" t="n"/>
-      <c r="AE81" s="6" t="n"/>
+      <c r="AE81" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF81" s="6" t="n"/>
       <c r="AG81" s="6" t="n"/>
       <c r="AH81" s="6" t="n"/>
@@ -6573,7 +6893,11 @@
       <c r="AB82" s="71" t="n"/>
       <c r="AC82" s="71" t="n"/>
       <c r="AD82" s="71" t="n"/>
-      <c r="AE82" s="6" t="n"/>
+      <c r="AE82" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF82" s="6" t="n"/>
       <c r="AG82" s="6" t="n"/>
       <c r="AH82" s="6" t="n"/>
@@ -6649,7 +6973,11 @@
       <c r="AB83" s="71" t="n"/>
       <c r="AC83" s="71" t="n"/>
       <c r="AD83" s="71" t="n"/>
-      <c r="AE83" s="6" t="n"/>
+      <c r="AE83" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF83" s="6" t="n"/>
       <c r="AG83" s="6" t="n"/>
       <c r="AH83" s="6" t="n"/>
@@ -6725,7 +7053,11 @@
       <c r="AB84" s="71" t="n"/>
       <c r="AC84" s="71" t="n"/>
       <c r="AD84" s="71" t="n"/>
-      <c r="AE84" s="6" t="n"/>
+      <c r="AE84" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF84" s="6" t="n"/>
       <c r="AG84" s="6" t="n"/>
       <c r="AH84" s="6" t="n"/>
@@ -6801,7 +7133,11 @@
       <c r="AB85" s="71" t="n"/>
       <c r="AC85" s="71" t="n"/>
       <c r="AD85" s="71" t="n"/>
-      <c r="AE85" s="6" t="n"/>
+      <c r="AE85" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF85" s="6" t="n"/>
       <c r="AG85" s="6" t="n"/>
       <c r="AH85" s="6" t="n"/>
@@ -6877,7 +7213,11 @@
       <c r="AB86" s="71" t="n"/>
       <c r="AC86" s="71" t="n"/>
       <c r="AD86" s="71" t="n"/>
-      <c r="AE86" s="6" t="n"/>
+      <c r="AE86" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF86" s="6" t="n"/>
       <c r="AG86" s="6" t="n"/>
       <c r="AH86" s="6" t="n"/>
@@ -6953,7 +7293,11 @@
       <c r="AB87" s="71" t="n"/>
       <c r="AC87" s="71" t="n"/>
       <c r="AD87" s="71" t="n"/>
-      <c r="AE87" s="6" t="n"/>
+      <c r="AE87" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF87" s="6" t="n"/>
       <c r="AG87" s="6" t="n"/>
       <c r="AH87" s="6" t="n"/>
@@ -7029,7 +7373,11 @@
       <c r="AB88" s="71" t="n"/>
       <c r="AC88" s="71" t="n"/>
       <c r="AD88" s="71" t="n"/>
-      <c r="AE88" s="6" t="n"/>
+      <c r="AE88" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF88" s="6" t="n"/>
       <c r="AG88" s="6" t="n"/>
       <c r="AH88" s="6" t="n"/>
@@ -7105,7 +7453,11 @@
       <c r="AB89" s="71" t="n"/>
       <c r="AC89" s="71" t="n"/>
       <c r="AD89" s="71" t="n"/>
-      <c r="AE89" s="6" t="n"/>
+      <c r="AE89" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF89" s="6" t="n"/>
       <c r="AG89" s="6" t="n"/>
       <c r="AH89" s="6" t="n"/>
@@ -7173,7 +7525,11 @@
       <c r="AB90" s="71" t="n"/>
       <c r="AC90" s="71" t="n"/>
       <c r="AD90" s="71" t="n"/>
-      <c r="AE90" s="6" t="n"/>
+      <c r="AE90" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF90" s="6" t="n"/>
       <c r="AG90" s="6" t="n"/>
       <c r="AH90" s="6" t="n"/>
@@ -7241,7 +7597,11 @@
       <c r="AB91" s="71" t="n"/>
       <c r="AC91" s="71" t="n"/>
       <c r="AD91" s="71" t="n"/>
-      <c r="AE91" s="6" t="n"/>
+      <c r="AE91" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF91" s="6" t="n"/>
       <c r="AG91" s="6" t="n"/>
       <c r="AH91" s="6" t="n"/>
@@ -7309,7 +7669,11 @@
       <c r="AB92" s="71" t="n"/>
       <c r="AC92" s="71" t="n"/>
       <c r="AD92" s="71" t="n"/>
-      <c r="AE92" s="6" t="n"/>
+      <c r="AE92" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF92" s="6" t="n"/>
       <c r="AG92" s="6" t="n"/>
       <c r="AH92" s="6" t="n"/>
@@ -7377,7 +7741,11 @@
       <c r="AB93" s="71" t="n"/>
       <c r="AC93" s="71" t="n"/>
       <c r="AD93" s="71" t="n"/>
-      <c r="AE93" s="6" t="n"/>
+      <c r="AE93" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF93" s="6" t="n"/>
       <c r="AG93" s="6" t="n"/>
       <c r="AH93" s="6" t="n"/>
@@ -7445,7 +7813,11 @@
       <c r="AB94" s="71" t="n"/>
       <c r="AC94" s="71" t="n"/>
       <c r="AD94" s="71" t="n"/>
-      <c r="AE94" s="6" t="n"/>
+      <c r="AE94" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF94" s="6" t="n"/>
       <c r="AG94" s="6" t="n"/>
       <c r="AH94" s="6" t="n"/>
@@ -7513,7 +7885,11 @@
       <c r="AB95" s="71" t="n"/>
       <c r="AC95" s="71" t="n"/>
       <c r="AD95" s="71" t="n"/>
-      <c r="AE95" s="6" t="n"/>
+      <c r="AE95" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF95" s="6" t="n"/>
       <c r="AG95" s="6" t="n"/>
       <c r="AH95" s="6" t="n"/>
@@ -7581,7 +7957,11 @@
       <c r="AB96" s="71" t="n"/>
       <c r="AC96" s="71" t="n"/>
       <c r="AD96" s="71" t="n"/>
-      <c r="AE96" s="6" t="n"/>
+      <c r="AE96" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF96" s="6" t="n"/>
       <c r="AG96" s="6" t="n"/>
       <c r="AH96" s="6" t="n"/>
@@ -7649,7 +8029,11 @@
       <c r="AB97" s="71" t="n"/>
       <c r="AC97" s="71" t="n"/>
       <c r="AD97" s="71" t="n"/>
-      <c r="AE97" s="6" t="n"/>
+      <c r="AE97" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF97" s="6" t="n"/>
       <c r="AG97" s="6" t="n"/>
       <c r="AH97" s="6" t="n"/>
@@ -7717,7 +8101,11 @@
       <c r="AB98" s="71" t="n"/>
       <c r="AC98" s="71" t="n"/>
       <c r="AD98" s="71" t="n"/>
-      <c r="AE98" s="6" t="n"/>
+      <c r="AE98" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF98" s="6" t="n"/>
       <c r="AG98" s="6" t="n"/>
       <c r="AH98" s="6" t="n"/>
@@ -7785,7 +8173,11 @@
       <c r="AB99" s="71" t="n"/>
       <c r="AC99" s="71" t="n"/>
       <c r="AD99" s="71" t="n"/>
-      <c r="AE99" s="6" t="n"/>
+      <c r="AE99" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF99" s="6" t="n"/>
       <c r="AG99" s="6" t="n"/>
       <c r="AH99" s="6" t="n"/>
@@ -7853,7 +8245,11 @@
       <c r="AB100" s="71" t="n"/>
       <c r="AC100" s="71" t="n"/>
       <c r="AD100" s="71" t="n"/>
-      <c r="AE100" s="6" t="n"/>
+      <c r="AE100" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF100" s="6" t="n"/>
       <c r="AG100" s="6" t="n"/>
       <c r="AH100" s="6" t="n"/>
@@ -7921,7 +8317,11 @@
       <c r="AB101" s="71" t="n"/>
       <c r="AC101" s="71" t="n"/>
       <c r="AD101" s="71" t="n"/>
-      <c r="AE101" s="6" t="n"/>
+      <c r="AE101" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF101" s="6" t="n"/>
       <c r="AG101" s="6" t="n"/>
       <c r="AH101" s="6" t="n"/>
@@ -7989,7 +8389,11 @@
       <c r="AB102" s="71" t="n"/>
       <c r="AC102" s="71" t="n"/>
       <c r="AD102" s="71" t="n"/>
-      <c r="AE102" s="6" t="n"/>
+      <c r="AE102" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF102" s="6" t="n"/>
       <c r="AG102" s="6" t="n"/>
       <c r="AH102" s="6" t="n"/>
@@ -8057,7 +8461,11 @@
       <c r="AB103" s="71" t="n"/>
       <c r="AC103" s="71" t="n"/>
       <c r="AD103" s="71" t="n"/>
-      <c r="AE103" s="6" t="n"/>
+      <c r="AE103" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF103" s="6" t="n"/>
       <c r="AG103" s="6" t="n"/>
       <c r="AH103" s="6" t="n"/>
@@ -8125,7 +8533,11 @@
       <c r="AB104" s="71" t="n"/>
       <c r="AC104" s="71" t="n"/>
       <c r="AD104" s="71" t="n"/>
-      <c r="AE104" s="6" t="n"/>
+      <c r="AE104" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF104" s="6" t="n"/>
       <c r="AG104" s="6" t="n"/>
       <c r="AH104" s="6" t="n"/>
@@ -8193,7 +8605,11 @@
       <c r="AB105" s="71" t="n"/>
       <c r="AC105" s="71" t="n"/>
       <c r="AD105" s="71" t="n"/>
-      <c r="AE105" s="6" t="n"/>
+      <c r="AE105" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF105" s="6" t="n"/>
       <c r="AG105" s="6" t="n"/>
       <c r="AH105" s="6" t="n"/>
@@ -8261,7 +8677,11 @@
       <c r="AB106" s="71" t="n"/>
       <c r="AC106" s="71" t="n"/>
       <c r="AD106" s="71" t="n"/>
-      <c r="AE106" s="6" t="n"/>
+      <c r="AE106" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF106" s="6" t="n"/>
       <c r="AG106" s="6" t="n"/>
       <c r="AH106" s="6" t="n"/>
@@ -8329,7 +8749,11 @@
       <c r="AB107" s="71" t="n"/>
       <c r="AC107" s="71" t="n"/>
       <c r="AD107" s="71" t="n"/>
-      <c r="AE107" s="6" t="n"/>
+      <c r="AE107" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF107" s="6" t="n"/>
       <c r="AG107" s="6" t="n"/>
       <c r="AH107" s="6" t="n"/>
@@ -8397,7 +8821,11 @@
       <c r="AB108" s="71" t="n"/>
       <c r="AC108" s="71" t="n"/>
       <c r="AD108" s="71" t="n"/>
-      <c r="AE108" s="6" t="n"/>
+      <c r="AE108" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF108" s="6" t="n"/>
       <c r="AG108" s="6" t="n"/>
       <c r="AH108" s="6" t="n"/>
@@ -8465,7 +8893,11 @@
       <c r="AB109" s="71" t="n"/>
       <c r="AC109" s="71" t="n"/>
       <c r="AD109" s="71" t="n"/>
-      <c r="AE109" s="6" t="n"/>
+      <c r="AE109" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF109" s="6" t="n"/>
       <c r="AG109" s="6" t="n"/>
       <c r="AH109" s="6" t="n"/>
@@ -8533,7 +8965,11 @@
       <c r="AB110" s="71" t="n"/>
       <c r="AC110" s="71" t="n"/>
       <c r="AD110" s="71" t="n"/>
-      <c r="AE110" s="6" t="n"/>
+      <c r="AE110" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF110" s="6" t="n"/>
       <c r="AG110" s="6" t="n"/>
       <c r="AH110" s="6" t="n"/>
@@ -8601,7 +9037,11 @@
       <c r="AB111" s="71" t="n"/>
       <c r="AC111" s="71" t="n"/>
       <c r="AD111" s="71" t="n"/>
-      <c r="AE111" s="6" t="n"/>
+      <c r="AE111" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF111" s="6" t="n"/>
       <c r="AG111" s="6" t="n"/>
       <c r="AH111" s="6" t="n"/>
@@ -8669,7 +9109,11 @@
       <c r="AB112" s="71" t="n"/>
       <c r="AC112" s="71" t="n"/>
       <c r="AD112" s="71" t="n"/>
-      <c r="AE112" s="6" t="n"/>
+      <c r="AE112" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF112" s="6" t="n"/>
       <c r="AG112" s="6" t="n"/>
       <c r="AH112" s="6" t="n"/>
@@ -8737,7 +9181,11 @@
       <c r="AB113" s="71" t="n"/>
       <c r="AC113" s="71" t="n"/>
       <c r="AD113" s="71" t="n"/>
-      <c r="AE113" s="6" t="n"/>
+      <c r="AE113" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF113" s="6" t="n"/>
       <c r="AG113" s="6" t="n"/>
       <c r="AH113" s="6" t="n"/>
@@ -8805,7 +9253,11 @@
       <c r="AB114" s="71" t="n"/>
       <c r="AC114" s="71" t="n"/>
       <c r="AD114" s="71" t="n"/>
-      <c r="AE114" s="6" t="n"/>
+      <c r="AE114" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF114" s="6" t="n"/>
       <c r="AG114" s="6" t="n"/>
       <c r="AH114" s="6" t="n"/>
@@ -8873,7 +9325,11 @@
       <c r="AB115" s="71" t="n"/>
       <c r="AC115" s="71" t="n"/>
       <c r="AD115" s="71" t="n"/>
-      <c r="AE115" s="6" t="n"/>
+      <c r="AE115" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF115" s="6" t="n"/>
       <c r="AG115" s="6" t="n"/>
       <c r="AH115" s="6" t="n"/>
@@ -8941,7 +9397,11 @@
       <c r="AB116" s="71" t="n"/>
       <c r="AC116" s="71" t="n"/>
       <c r="AD116" s="71" t="n"/>
-      <c r="AE116" s="6" t="n"/>
+      <c r="AE116" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF116" s="6" t="n"/>
       <c r="AG116" s="6" t="n"/>
       <c r="AH116" s="6" t="n"/>
@@ -9009,7 +9469,11 @@
       <c r="AB117" s="71" t="n"/>
       <c r="AC117" s="71" t="n"/>
       <c r="AD117" s="71" t="n"/>
-      <c r="AE117" s="6" t="n"/>
+      <c r="AE117" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF117" s="6" t="n"/>
       <c r="AG117" s="6" t="n"/>
       <c r="AH117" s="6" t="n"/>
@@ -9077,7 +9541,11 @@
       <c r="AB118" s="71" t="n"/>
       <c r="AC118" s="71" t="n"/>
       <c r="AD118" s="71" t="n"/>
-      <c r="AE118" s="6" t="n"/>
+      <c r="AE118" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF118" s="6" t="n"/>
       <c r="AG118" s="6" t="n"/>
       <c r="AH118" s="6" t="n"/>
@@ -9145,7 +9613,11 @@
       <c r="AB119" s="71" t="n"/>
       <c r="AC119" s="71" t="n"/>
       <c r="AD119" s="71" t="n"/>
-      <c r="AE119" s="6" t="n"/>
+      <c r="AE119" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF119" s="6" t="n"/>
       <c r="AG119" s="6" t="n"/>
       <c r="AH119" s="6" t="n"/>
@@ -9213,7 +9685,11 @@
       <c r="AB120" s="71" t="n"/>
       <c r="AC120" s="71" t="n"/>
       <c r="AD120" s="71" t="n"/>
-      <c r="AE120" s="6" t="n"/>
+      <c r="AE120" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF120" s="6" t="n"/>
       <c r="AG120" s="6" t="n"/>
       <c r="AH120" s="6" t="n"/>
@@ -9281,7 +9757,11 @@
       <c r="AB121" s="71" t="n"/>
       <c r="AC121" s="71" t="n"/>
       <c r="AD121" s="71" t="n"/>
-      <c r="AE121" s="6" t="n"/>
+      <c r="AE121" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF121" s="6" t="n"/>
       <c r="AG121" s="6" t="n"/>
       <c r="AH121" s="6" t="n"/>
@@ -9349,7 +9829,11 @@
       <c r="AB122" s="71" t="n"/>
       <c r="AC122" s="71" t="n"/>
       <c r="AD122" s="71" t="n"/>
-      <c r="AE122" s="6" t="n"/>
+      <c r="AE122" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF122" s="6" t="n"/>
       <c r="AG122" s="6" t="n"/>
       <c r="AH122" s="6" t="n"/>
@@ -9417,7 +9901,11 @@
       <c r="AB123" s="71" t="n"/>
       <c r="AC123" s="71" t="n"/>
       <c r="AD123" s="71" t="n"/>
-      <c r="AE123" s="6" t="n"/>
+      <c r="AE123" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF123" s="6" t="n"/>
       <c r="AG123" s="6" t="n"/>
       <c r="AH123" s="6" t="n"/>
@@ -9485,7 +9973,11 @@
       <c r="AB124" s="71" t="n"/>
       <c r="AC124" s="71" t="n"/>
       <c r="AD124" s="71" t="n"/>
-      <c r="AE124" s="6" t="n"/>
+      <c r="AE124" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF124" s="6" t="n"/>
       <c r="AG124" s="6" t="n"/>
       <c r="AH124" s="6" t="n"/>
@@ -9553,7 +10045,11 @@
       <c r="AB125" s="71" t="n"/>
       <c r="AC125" s="71" t="n"/>
       <c r="AD125" s="71" t="n"/>
-      <c r="AE125" s="6" t="n"/>
+      <c r="AE125" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF125" s="6" t="n"/>
       <c r="AG125" s="6" t="n"/>
       <c r="AH125" s="6" t="n"/>
@@ -9621,7 +10117,11 @@
       <c r="AB126" s="71" t="n"/>
       <c r="AC126" s="71" t="n"/>
       <c r="AD126" s="71" t="n"/>
-      <c r="AE126" s="6" t="n"/>
+      <c r="AE126" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF126" s="6" t="n"/>
       <c r="AG126" s="6" t="n"/>
       <c r="AH126" s="6" t="n"/>
@@ -9689,7 +10189,11 @@
       <c r="AB127" s="71" t="n"/>
       <c r="AC127" s="71" t="n"/>
       <c r="AD127" s="71" t="n"/>
-      <c r="AE127" s="6" t="n"/>
+      <c r="AE127" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF127" s="6" t="n"/>
       <c r="AG127" s="6" t="n"/>
       <c r="AH127" s="6" t="n"/>
@@ -9757,7 +10261,11 @@
       <c r="AB128" s="71" t="n"/>
       <c r="AC128" s="71" t="n"/>
       <c r="AD128" s="71" t="n"/>
-      <c r="AE128" s="6" t="n"/>
+      <c r="AE128" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF128" s="6" t="n"/>
       <c r="AG128" s="6" t="n"/>
       <c r="AH128" s="6" t="n"/>
@@ -9825,7 +10333,11 @@
       <c r="AB129" s="71" t="n"/>
       <c r="AC129" s="71" t="n"/>
       <c r="AD129" s="71" t="n"/>
-      <c r="AE129" s="6" t="n"/>
+      <c r="AE129" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF129" s="6" t="n"/>
       <c r="AG129" s="6" t="n"/>
       <c r="AH129" s="6" t="n"/>
@@ -9893,7 +10405,11 @@
       <c r="AB130" s="71" t="n"/>
       <c r="AC130" s="71" t="n"/>
       <c r="AD130" s="71" t="n"/>
-      <c r="AE130" s="6" t="n"/>
+      <c r="AE130" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF130" s="6" t="n"/>
       <c r="AG130" s="6" t="n"/>
       <c r="AH130" s="6" t="n"/>
@@ -9961,7 +10477,11 @@
       <c r="AB131" s="71" t="n"/>
       <c r="AC131" s="71" t="n"/>
       <c r="AD131" s="71" t="n"/>
-      <c r="AE131" s="6" t="n"/>
+      <c r="AE131" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF131" s="6" t="n"/>
       <c r="AG131" s="6" t="n"/>
       <c r="AH131" s="6" t="n"/>
@@ -10029,7 +10549,11 @@
       <c r="AB132" s="71" t="n"/>
       <c r="AC132" s="71" t="n"/>
       <c r="AD132" s="71" t="n"/>
-      <c r="AE132" s="6" t="n"/>
+      <c r="AE132" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF132" s="6" t="n"/>
       <c r="AG132" s="6" t="n"/>
       <c r="AH132" s="6" t="n"/>
@@ -10105,7 +10629,11 @@
       <c r="AB133" s="71" t="n"/>
       <c r="AC133" s="71" t="n"/>
       <c r="AD133" s="71" t="n"/>
-      <c r="AE133" s="6" t="n"/>
+      <c r="AE133" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF133" s="6" t="n"/>
       <c r="AG133" s="6" t="n"/>
       <c r="AH133" s="6" t="n"/>
@@ -10181,7 +10709,11 @@
       <c r="AB134" s="71" t="n"/>
       <c r="AC134" s="71" t="n"/>
       <c r="AD134" s="71" t="n"/>
-      <c r="AE134" s="6" t="n"/>
+      <c r="AE134" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF134" s="6" t="n"/>
       <c r="AG134" s="6" t="n"/>
       <c r="AH134" s="6" t="n"/>
@@ -10257,7 +10789,11 @@
       <c r="AB135" s="71" t="n"/>
       <c r="AC135" s="71" t="n"/>
       <c r="AD135" s="71" t="n"/>
-      <c r="AE135" s="6" t="n"/>
+      <c r="AE135" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF135" s="6" t="n"/>
       <c r="AG135" s="6" t="n"/>
       <c r="AH135" s="6" t="n"/>
@@ -10325,7 +10861,11 @@
       <c r="AB136" s="71" t="n"/>
       <c r="AC136" s="71" t="n"/>
       <c r="AD136" s="71" t="n"/>
-      <c r="AE136" s="6" t="n"/>
+      <c r="AE136" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF136" s="6" t="n"/>
       <c r="AG136" s="6" t="n"/>
       <c r="AH136" s="6" t="n"/>
@@ -10401,7 +10941,11 @@
       <c r="AB137" s="71" t="n"/>
       <c r="AC137" s="71" t="n"/>
       <c r="AD137" s="71" t="n"/>
-      <c r="AE137" s="6" t="n"/>
+      <c r="AE137" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF137" s="6" t="n"/>
       <c r="AG137" s="6" t="n"/>
       <c r="AH137" s="6" t="n"/>
@@ -10469,7 +11013,11 @@
       <c r="AB138" s="71" t="n"/>
       <c r="AC138" s="71" t="n"/>
       <c r="AD138" s="71" t="n"/>
-      <c r="AE138" s="6" t="n"/>
+      <c r="AE138" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF138" s="6" t="n"/>
       <c r="AG138" s="6" t="n"/>
       <c r="AH138" s="6" t="n"/>
@@ -10545,7 +11093,11 @@
       <c r="AB139" s="71" t="n"/>
       <c r="AC139" s="71" t="n"/>
       <c r="AD139" s="71" t="n"/>
-      <c r="AE139" s="6" t="n"/>
+      <c r="AE139" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF139" s="6" t="n"/>
       <c r="AG139" s="6" t="n"/>
       <c r="AH139" s="6" t="n"/>
@@ -10613,7 +11165,11 @@
       <c r="AB140" s="71" t="n"/>
       <c r="AC140" s="71" t="n"/>
       <c r="AD140" s="71" t="n"/>
-      <c r="AE140" s="6" t="n"/>
+      <c r="AE140" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF140" s="6" t="n"/>
       <c r="AG140" s="6" t="n"/>
       <c r="AH140" s="6" t="n"/>
@@ -10681,7 +11237,11 @@
       <c r="AB141" s="71" t="n"/>
       <c r="AC141" s="71" t="n"/>
       <c r="AD141" s="71" t="n"/>
-      <c r="AE141" s="6" t="n"/>
+      <c r="AE141" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF141" s="6" t="n"/>
       <c r="AG141" s="6" t="n"/>
       <c r="AH141" s="6" t="n"/>
@@ -10749,7 +11309,11 @@
       <c r="AB142" s="71" t="n"/>
       <c r="AC142" s="71" t="n"/>
       <c r="AD142" s="71" t="n"/>
-      <c r="AE142" s="6" t="n"/>
+      <c r="AE142" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF142" s="6" t="n"/>
       <c r="AG142" s="6" t="n"/>
       <c r="AH142" s="6" t="n"/>
@@ -10817,7 +11381,11 @@
       <c r="AB143" s="71" t="n"/>
       <c r="AC143" s="71" t="n"/>
       <c r="AD143" s="71" t="n"/>
-      <c r="AE143" s="6" t="n"/>
+      <c r="AE143" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF143" s="6" t="n"/>
       <c r="AG143" s="6" t="n"/>
       <c r="AH143" s="6" t="n"/>
@@ -10885,7 +11453,11 @@
       <c r="AB144" s="71" t="n"/>
       <c r="AC144" s="71" t="n"/>
       <c r="AD144" s="71" t="n"/>
-      <c r="AE144" s="6" t="n"/>
+      <c r="AE144" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF144" s="6" t="n"/>
       <c r="AG144" s="6" t="n"/>
       <c r="AH144" s="6" t="n"/>
@@ -10953,7 +11525,11 @@
       <c r="AB145" s="71" t="n"/>
       <c r="AC145" s="71" t="n"/>
       <c r="AD145" s="71" t="n"/>
-      <c r="AE145" s="6" t="n"/>
+      <c r="AE145" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF145" s="6" t="n"/>
       <c r="AG145" s="6" t="n"/>
       <c r="AH145" s="6" t="n"/>
@@ -11029,7 +11605,11 @@
       <c r="AB146" s="71" t="n"/>
       <c r="AC146" s="71" t="n"/>
       <c r="AD146" s="71" t="n"/>
-      <c r="AE146" s="6" t="n"/>
+      <c r="AE146" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF146" s="6" t="n"/>
       <c r="AG146" s="6" t="n"/>
       <c r="AH146" s="6" t="n"/>
@@ -11105,7 +11685,11 @@
       <c r="AB147" s="71" t="n"/>
       <c r="AC147" s="71" t="n"/>
       <c r="AD147" s="71" t="n"/>
-      <c r="AE147" s="6" t="n"/>
+      <c r="AE147" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF147" s="6" t="n"/>
       <c r="AG147" s="6" t="n"/>
       <c r="AH147" s="6" t="n"/>
@@ -11181,7 +11765,11 @@
       <c r="AB148" s="71" t="n"/>
       <c r="AC148" s="71" t="n"/>
       <c r="AD148" s="71" t="n"/>
-      <c r="AE148" s="6" t="n"/>
+      <c r="AE148" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF148" s="6" t="n"/>
       <c r="AG148" s="6" t="n"/>
       <c r="AH148" s="6" t="n"/>
@@ -11257,7 +11845,11 @@
       <c r="AB149" s="71" t="n"/>
       <c r="AC149" s="71" t="n"/>
       <c r="AD149" s="71" t="n"/>
-      <c r="AE149" s="6" t="n"/>
+      <c r="AE149" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF149" s="6" t="n"/>
       <c r="AG149" s="6" t="n"/>
       <c r="AH149" s="6" t="n"/>
@@ -11325,7 +11917,11 @@
       <c r="AB150" s="71" t="n"/>
       <c r="AC150" s="71" t="n"/>
       <c r="AD150" s="71" t="n"/>
-      <c r="AE150" s="6" t="n"/>
+      <c r="AE150" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF150" s="6" t="n"/>
       <c r="AG150" s="6" t="n"/>
       <c r="AH150" s="6" t="n"/>
@@ -11393,7 +11989,11 @@
       <c r="AB151" s="71" t="n"/>
       <c r="AC151" s="71" t="n"/>
       <c r="AD151" s="71" t="n"/>
-      <c r="AE151" s="6" t="n"/>
+      <c r="AE151" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF151" s="6" t="n"/>
       <c r="AG151" s="6" t="n"/>
       <c r="AH151" s="6" t="n"/>
@@ -11461,7 +12061,11 @@
       <c r="AB152" s="71" t="n"/>
       <c r="AC152" s="71" t="n"/>
       <c r="AD152" s="71" t="n"/>
-      <c r="AE152" s="6" t="n"/>
+      <c r="AE152" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF152" s="6" t="n"/>
       <c r="AG152" s="6" t="n"/>
       <c r="AH152" s="6" t="n"/>
@@ -11529,7 +12133,11 @@
       <c r="AB153" s="71" t="n"/>
       <c r="AC153" s="71" t="n"/>
       <c r="AD153" s="71" t="n"/>
-      <c r="AE153" s="6" t="n"/>
+      <c r="AE153" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF153" s="6" t="n"/>
       <c r="AG153" s="6" t="n"/>
       <c r="AH153" s="6" t="n"/>
@@ -11597,7 +12205,11 @@
       <c r="AB154" s="71" t="n"/>
       <c r="AC154" s="71" t="n"/>
       <c r="AD154" s="71" t="n"/>
-      <c r="AE154" s="6" t="n"/>
+      <c r="AE154" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF154" s="6" t="n"/>
       <c r="AG154" s="6" t="n"/>
       <c r="AH154" s="6" t="n"/>
@@ -11665,7 +12277,11 @@
       <c r="AB155" s="71" t="n"/>
       <c r="AC155" s="71" t="n"/>
       <c r="AD155" s="71" t="n"/>
-      <c r="AE155" s="6" t="n"/>
+      <c r="AE155" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF155" s="6" t="n"/>
       <c r="AG155" s="6" t="n"/>
       <c r="AH155" s="6" t="n"/>
@@ -11733,7 +12349,11 @@
       <c r="AB156" s="71" t="n"/>
       <c r="AC156" s="71" t="n"/>
       <c r="AD156" s="71" t="n"/>
-      <c r="AE156" s="6" t="n"/>
+      <c r="AE156" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF156" s="6" t="n"/>
       <c r="AG156" s="6" t="n"/>
       <c r="AH156" s="6" t="n"/>
@@ -11801,7 +12421,11 @@
       <c r="AB157" s="71" t="n"/>
       <c r="AC157" s="71" t="n"/>
       <c r="AD157" s="71" t="n"/>
-      <c r="AE157" s="6" t="n"/>
+      <c r="AE157" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF157" s="6" t="n"/>
       <c r="AG157" s="6" t="n"/>
       <c r="AH157" s="6" t="n"/>
@@ -11869,7 +12493,11 @@
       <c r="AB158" s="71" t="n"/>
       <c r="AC158" s="71" t="n"/>
       <c r="AD158" s="71" t="n"/>
-      <c r="AE158" s="6" t="n"/>
+      <c r="AE158" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF158" s="6" t="n"/>
       <c r="AG158" s="6" t="n"/>
       <c r="AH158" s="6" t="n"/>
@@ -11937,7 +12565,11 @@
       <c r="AB159" s="71" t="n"/>
       <c r="AC159" s="71" t="n"/>
       <c r="AD159" s="71" t="n"/>
-      <c r="AE159" s="6" t="n"/>
+      <c r="AE159" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF159" s="6" t="n"/>
       <c r="AG159" s="6" t="n"/>
       <c r="AH159" s="6" t="n"/>
@@ -12005,7 +12637,11 @@
       <c r="AB160" s="71" t="n"/>
       <c r="AC160" s="71" t="n"/>
       <c r="AD160" s="71" t="n"/>
-      <c r="AE160" s="6" t="n"/>
+      <c r="AE160" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF160" s="6" t="n"/>
       <c r="AG160" s="6" t="n"/>
       <c r="AH160" s="6" t="n"/>
@@ -12073,7 +12709,11 @@
       <c r="AB161" s="71" t="n"/>
       <c r="AC161" s="71" t="n"/>
       <c r="AD161" s="71" t="n"/>
-      <c r="AE161" s="6" t="n"/>
+      <c r="AE161" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF161" s="6" t="n"/>
       <c r="AG161" s="6" t="n"/>
       <c r="AH161" s="6" t="n"/>
@@ -12141,7 +12781,11 @@
       <c r="AB162" s="71" t="n"/>
       <c r="AC162" s="71" t="n"/>
       <c r="AD162" s="71" t="n"/>
-      <c r="AE162" s="6" t="n"/>
+      <c r="AE162" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF162" s="6" t="n"/>
       <c r="AG162" s="6" t="n"/>
       <c r="AH162" s="6" t="n"/>
@@ -12209,7 +12853,11 @@
       <c r="AB163" s="71" t="n"/>
       <c r="AC163" s="71" t="n"/>
       <c r="AD163" s="71" t="n"/>
-      <c r="AE163" s="6" t="n"/>
+      <c r="AE163" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF163" s="6" t="n"/>
       <c r="AG163" s="6" t="n"/>
       <c r="AH163" s="6" t="n"/>
@@ -12277,7 +12925,11 @@
       <c r="AB164" s="71" t="n"/>
       <c r="AC164" s="71" t="n"/>
       <c r="AD164" s="71" t="n"/>
-      <c r="AE164" s="6" t="n"/>
+      <c r="AE164" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF164" s="6" t="n"/>
       <c r="AG164" s="6" t="n"/>
       <c r="AH164" s="6" t="n"/>
@@ -12345,7 +12997,11 @@
       <c r="AB165" s="71" t="n"/>
       <c r="AC165" s="71" t="n"/>
       <c r="AD165" s="71" t="n"/>
-      <c r="AE165" s="6" t="n"/>
+      <c r="AE165" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF165" s="6" t="n"/>
       <c r="AG165" s="6" t="n"/>
       <c r="AH165" s="6" t="n"/>
@@ -12413,7 +13069,11 @@
       <c r="AB166" s="71" t="n"/>
       <c r="AC166" s="71" t="n"/>
       <c r="AD166" s="71" t="n"/>
-      <c r="AE166" s="6" t="n"/>
+      <c r="AE166" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF166" s="6" t="n"/>
       <c r="AG166" s="6" t="n"/>
       <c r="AH166" s="6" t="n"/>
@@ -12481,7 +13141,11 @@
       <c r="AB167" s="71" t="n"/>
       <c r="AC167" s="71" t="n"/>
       <c r="AD167" s="71" t="n"/>
-      <c r="AE167" s="6" t="n"/>
+      <c r="AE167" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF167" s="6" t="n"/>
       <c r="AG167" s="6" t="n"/>
       <c r="AH167" s="6" t="n"/>
@@ -12549,7 +13213,11 @@
       <c r="AB168" s="71" t="n"/>
       <c r="AC168" s="71" t="n"/>
       <c r="AD168" s="71" t="n"/>
-      <c r="AE168" s="6" t="n"/>
+      <c r="AE168" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF168" s="6" t="n"/>
       <c r="AG168" s="6" t="n"/>
       <c r="AH168" s="6" t="n"/>
@@ -12617,7 +13285,11 @@
       <c r="AB169" s="71" t="n"/>
       <c r="AC169" s="71" t="n"/>
       <c r="AD169" s="71" t="n"/>
-      <c r="AE169" s="6" t="n"/>
+      <c r="AE169" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF169" s="6" t="n"/>
       <c r="AG169" s="6" t="n"/>
       <c r="AH169" s="6" t="n"/>
@@ -12685,7 +13357,11 @@
       <c r="AB170" s="71" t="n"/>
       <c r="AC170" s="71" t="n"/>
       <c r="AD170" s="71" t="n"/>
-      <c r="AE170" s="6" t="n"/>
+      <c r="AE170" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF170" s="6" t="n"/>
       <c r="AG170" s="6" t="n"/>
       <c r="AH170" s="6" t="n"/>
@@ -12753,7 +13429,11 @@
       <c r="AB171" s="71" t="n"/>
       <c r="AC171" s="71" t="n"/>
       <c r="AD171" s="71" t="n"/>
-      <c r="AE171" s="6" t="n"/>
+      <c r="AE171" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF171" s="6" t="n"/>
       <c r="AG171" s="6" t="n"/>
       <c r="AH171" s="6" t="n"/>
@@ -12821,7 +13501,11 @@
       <c r="AB172" s="71" t="n"/>
       <c r="AC172" s="71" t="n"/>
       <c r="AD172" s="71" t="n"/>
-      <c r="AE172" s="6" t="n"/>
+      <c r="AE172" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF172" s="6" t="n"/>
       <c r="AG172" s="6" t="n"/>
       <c r="AH172" s="6" t="n"/>
@@ -12889,7 +13573,11 @@
       <c r="AB173" s="71" t="n"/>
       <c r="AC173" s="71" t="n"/>
       <c r="AD173" s="71" t="n"/>
-      <c r="AE173" s="6" t="n"/>
+      <c r="AE173" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF173" s="6" t="n"/>
       <c r="AG173" s="6" t="n"/>
       <c r="AH173" s="6" t="n"/>
@@ -12957,7 +13645,11 @@
       <c r="AB174" s="71" t="n"/>
       <c r="AC174" s="71" t="n"/>
       <c r="AD174" s="71" t="n"/>
-      <c r="AE174" s="6" t="n"/>
+      <c r="AE174" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF174" s="6" t="n"/>
       <c r="AG174" s="6" t="n"/>
       <c r="AH174" s="6" t="n"/>
@@ -13025,7 +13717,11 @@
       <c r="AB175" s="71" t="n"/>
       <c r="AC175" s="71" t="n"/>
       <c r="AD175" s="71" t="n"/>
-      <c r="AE175" s="6" t="n"/>
+      <c r="AE175" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF175" s="6" t="n"/>
       <c r="AG175" s="6" t="n"/>
       <c r="AH175" s="6" t="n"/>
@@ -13093,7 +13789,11 @@
       <c r="AB176" s="71" t="n"/>
       <c r="AC176" s="71" t="n"/>
       <c r="AD176" s="71" t="n"/>
-      <c r="AE176" s="6" t="n"/>
+      <c r="AE176" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF176" s="6" t="n"/>
       <c r="AG176" s="6" t="n"/>
       <c r="AH176" s="6" t="n"/>
@@ -13161,7 +13861,11 @@
       <c r="AB177" s="71" t="n"/>
       <c r="AC177" s="71" t="n"/>
       <c r="AD177" s="71" t="n"/>
-      <c r="AE177" s="6" t="n"/>
+      <c r="AE177" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF177" s="6" t="n"/>
       <c r="AG177" s="6" t="n"/>
       <c r="AH177" s="6" t="n"/>
@@ -13229,7 +13933,11 @@
       <c r="AB178" s="71" t="n"/>
       <c r="AC178" s="71" t="n"/>
       <c r="AD178" s="71" t="n"/>
-      <c r="AE178" s="6" t="n"/>
+      <c r="AE178" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF178" s="6" t="n"/>
       <c r="AG178" s="6" t="n"/>
       <c r="AH178" s="6" t="n"/>
@@ -13297,7 +14005,11 @@
       <c r="AB179" s="71" t="n"/>
       <c r="AC179" s="71" t="n"/>
       <c r="AD179" s="71" t="n"/>
-      <c r="AE179" s="6" t="n"/>
+      <c r="AE179" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF179" s="6" t="n"/>
       <c r="AG179" s="6" t="n"/>
       <c r="AH179" s="6" t="n"/>
@@ -13365,7 +14077,11 @@
       <c r="AB180" s="71" t="n"/>
       <c r="AC180" s="71" t="n"/>
       <c r="AD180" s="71" t="n"/>
-      <c r="AE180" s="6" t="n"/>
+      <c r="AE180" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF180" s="6" t="n"/>
       <c r="AG180" s="6" t="n"/>
       <c r="AH180" s="6" t="n"/>
@@ -13433,7 +14149,11 @@
       <c r="AB181" s="71" t="n"/>
       <c r="AC181" s="71" t="n"/>
       <c r="AD181" s="71" t="n"/>
-      <c r="AE181" s="6" t="n"/>
+      <c r="AE181" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF181" s="6" t="n"/>
       <c r="AG181" s="6" t="n"/>
       <c r="AH181" s="6" t="n"/>
@@ -13501,7 +14221,11 @@
       <c r="AB182" s="71" t="n"/>
       <c r="AC182" s="71" t="n"/>
       <c r="AD182" s="71" t="n"/>
-      <c r="AE182" s="6" t="n"/>
+      <c r="AE182" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF182" s="6" t="n"/>
       <c r="AG182" s="6" t="n"/>
       <c r="AH182" s="6" t="n"/>
@@ -13569,7 +14293,11 @@
       <c r="AB183" s="71" t="n"/>
       <c r="AC183" s="71" t="n"/>
       <c r="AD183" s="71" t="n"/>
-      <c r="AE183" s="6" t="n"/>
+      <c r="AE183" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF183" s="6" t="n"/>
       <c r="AG183" s="6" t="n"/>
       <c r="AH183" s="6" t="n"/>
@@ -13637,7 +14365,11 @@
       <c r="AB184" s="71" t="n"/>
       <c r="AC184" s="71" t="n"/>
       <c r="AD184" s="71" t="n"/>
-      <c r="AE184" s="6" t="n"/>
+      <c r="AE184" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF184" s="6" t="n"/>
       <c r="AG184" s="6" t="n"/>
       <c r="AH184" s="6" t="n"/>
@@ -13705,7 +14437,11 @@
       <c r="AB185" s="71" t="n"/>
       <c r="AC185" s="71" t="n"/>
       <c r="AD185" s="71" t="n"/>
-      <c r="AE185" s="6" t="n"/>
+      <c r="AE185" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF185" s="6" t="n"/>
       <c r="AG185" s="6" t="n"/>
       <c r="AH185" s="6" t="n"/>
@@ -13773,7 +14509,11 @@
       <c r="AB186" s="71" t="n"/>
       <c r="AC186" s="71" t="n"/>
       <c r="AD186" s="71" t="n"/>
-      <c r="AE186" s="6" t="n"/>
+      <c r="AE186" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF186" s="6" t="n"/>
       <c r="AG186" s="6" t="n"/>
       <c r="AH186" s="6" t="n"/>
@@ -13841,7 +14581,11 @@
       <c r="AB187" s="71" t="n"/>
       <c r="AC187" s="71" t="n"/>
       <c r="AD187" s="71" t="n"/>
-      <c r="AE187" s="6" t="n"/>
+      <c r="AE187" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF187" s="6" t="n"/>
       <c r="AG187" s="6" t="n"/>
       <c r="AH187" s="6" t="n"/>
@@ -13909,7 +14653,11 @@
       <c r="AB188" s="71" t="n"/>
       <c r="AC188" s="71" t="n"/>
       <c r="AD188" s="71" t="n"/>
-      <c r="AE188" s="6" t="n"/>
+      <c r="AE188" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF188" s="6" t="n"/>
       <c r="AG188" s="6" t="n"/>
       <c r="AH188" s="6" t="n"/>
@@ -13977,7 +14725,11 @@
       <c r="AB189" s="71" t="n"/>
       <c r="AC189" s="71" t="n"/>
       <c r="AD189" s="71" t="n"/>
-      <c r="AE189" s="6" t="n"/>
+      <c r="AE189" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF189" s="6" t="n"/>
       <c r="AG189" s="6" t="n"/>
       <c r="AH189" s="6" t="n"/>
@@ -14045,7 +14797,11 @@
       <c r="AB190" s="71" t="n"/>
       <c r="AC190" s="71" t="n"/>
       <c r="AD190" s="71" t="n"/>
-      <c r="AE190" s="6" t="n"/>
+      <c r="AE190" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF190" s="6" t="n"/>
       <c r="AG190" s="6" t="n"/>
       <c r="AH190" s="6" t="n"/>
@@ -14113,7 +14869,11 @@
       <c r="AB191" s="71" t="n"/>
       <c r="AC191" s="71" t="n"/>
       <c r="AD191" s="71" t="n"/>
-      <c r="AE191" s="6" t="n"/>
+      <c r="AE191" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF191" s="6" t="n"/>
       <c r="AG191" s="6" t="n"/>
       <c r="AH191" s="6" t="n"/>
@@ -14181,7 +14941,11 @@
       <c r="AB192" s="71" t="n"/>
       <c r="AC192" s="71" t="n"/>
       <c r="AD192" s="71" t="n"/>
-      <c r="AE192" s="6" t="n"/>
+      <c r="AE192" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF192" s="6" t="n"/>
       <c r="AG192" s="6" t="n"/>
       <c r="AH192" s="6" t="n"/>
@@ -14249,7 +15013,11 @@
       <c r="AB193" s="71" t="n"/>
       <c r="AC193" s="71" t="n"/>
       <c r="AD193" s="71" t="n"/>
-      <c r="AE193" s="6" t="n"/>
+      <c r="AE193" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF193" s="6" t="n"/>
       <c r="AG193" s="6" t="n"/>
       <c r="AH193" s="6" t="n"/>
@@ -14317,7 +15085,11 @@
       <c r="AB194" s="71" t="n"/>
       <c r="AC194" s="71" t="n"/>
       <c r="AD194" s="71" t="n"/>
-      <c r="AE194" s="6" t="n"/>
+      <c r="AE194" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF194" s="6" t="n"/>
       <c r="AG194" s="6" t="n"/>
       <c r="AH194" s="6" t="n"/>
@@ -14385,7 +15157,11 @@
       <c r="AB195" s="71" t="n"/>
       <c r="AC195" s="71" t="n"/>
       <c r="AD195" s="71" t="n"/>
-      <c r="AE195" s="6" t="n"/>
+      <c r="AE195" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF195" s="6" t="n"/>
       <c r="AG195" s="6" t="n"/>
       <c r="AH195" s="6" t="n"/>
@@ -14453,7 +15229,11 @@
       <c r="AB196" s="71" t="n"/>
       <c r="AC196" s="71" t="n"/>
       <c r="AD196" s="71" t="n"/>
-      <c r="AE196" s="6" t="n"/>
+      <c r="AE196" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF196" s="6" t="n"/>
       <c r="AG196" s="6" t="n"/>
       <c r="AH196" s="6" t="n"/>
@@ -14521,7 +15301,11 @@
       <c r="AB197" s="71" t="n"/>
       <c r="AC197" s="71" t="n"/>
       <c r="AD197" s="71" t="n"/>
-      <c r="AE197" s="6" t="n"/>
+      <c r="AE197" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF197" s="6" t="n"/>
       <c r="AG197" s="6" t="n"/>
       <c r="AH197" s="6" t="n"/>
@@ -14589,7 +15373,11 @@
       <c r="AB198" s="71" t="n"/>
       <c r="AC198" s="71" t="n"/>
       <c r="AD198" s="71" t="n"/>
-      <c r="AE198" s="6" t="n"/>
+      <c r="AE198" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF198" s="6" t="n"/>
       <c r="AG198" s="6" t="n"/>
       <c r="AH198" s="6" t="n"/>
@@ -14657,7 +15445,11 @@
       <c r="AB199" s="71" t="n"/>
       <c r="AC199" s="71" t="n"/>
       <c r="AD199" s="71" t="n"/>
-      <c r="AE199" s="6" t="n"/>
+      <c r="AE199" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF199" s="6" t="n"/>
       <c r="AG199" s="6" t="n"/>
       <c r="AH199" s="6" t="n"/>
@@ -14725,7 +15517,11 @@
       <c r="AB200" s="71" t="n"/>
       <c r="AC200" s="71" t="n"/>
       <c r="AD200" s="71" t="n"/>
-      <c r="AE200" s="6" t="n"/>
+      <c r="AE200" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF200" s="6" t="n"/>
       <c r="AG200" s="6" t="n"/>
       <c r="AH200" s="6" t="n"/>
@@ -14793,7 +15589,11 @@
       <c r="AB201" s="71" t="n"/>
       <c r="AC201" s="71" t="n"/>
       <c r="AD201" s="71" t="n"/>
-      <c r="AE201" s="6" t="n"/>
+      <c r="AE201" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF201" s="6" t="n"/>
       <c r="AG201" s="6" t="n"/>
       <c r="AH201" s="6" t="n"/>
@@ -14861,7 +15661,11 @@
       <c r="AB202" s="71" t="n"/>
       <c r="AC202" s="71" t="n"/>
       <c r="AD202" s="71" t="n"/>
-      <c r="AE202" s="6" t="n"/>
+      <c r="AE202" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF202" s="6" t="n"/>
       <c r="AG202" s="6" t="n"/>
       <c r="AH202" s="6" t="n"/>
@@ -14929,7 +15733,11 @@
       <c r="AB203" s="71" t="n"/>
       <c r="AC203" s="71" t="n"/>
       <c r="AD203" s="71" t="n"/>
-      <c r="AE203" s="6" t="n"/>
+      <c r="AE203" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF203" s="6" t="n"/>
       <c r="AG203" s="6" t="n"/>
       <c r="AH203" s="6" t="n"/>
@@ -14997,7 +15805,11 @@
       <c r="AB204" s="71" t="n"/>
       <c r="AC204" s="71" t="n"/>
       <c r="AD204" s="71" t="n"/>
-      <c r="AE204" s="6" t="n"/>
+      <c r="AE204" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF204" s="6" t="n"/>
       <c r="AG204" s="6" t="n"/>
       <c r="AH204" s="6" t="n"/>
@@ -15065,7 +15877,11 @@
       <c r="AB205" s="71" t="n"/>
       <c r="AC205" s="71" t="n"/>
       <c r="AD205" s="71" t="n"/>
-      <c r="AE205" s="6" t="n"/>
+      <c r="AE205" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF205" s="6" t="n"/>
       <c r="AG205" s="6" t="n"/>
       <c r="AH205" s="6" t="n"/>
@@ -15133,7 +15949,11 @@
       <c r="AB206" s="71" t="n"/>
       <c r="AC206" s="71" t="n"/>
       <c r="AD206" s="71" t="n"/>
-      <c r="AE206" s="6" t="n"/>
+      <c r="AE206" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF206" s="6" t="n"/>
       <c r="AG206" s="6" t="n"/>
       <c r="AH206" s="6" t="n"/>
@@ -15201,7 +16021,11 @@
       <c r="AB207" s="71" t="n"/>
       <c r="AC207" s="71" t="n"/>
       <c r="AD207" s="71" t="n"/>
-      <c r="AE207" s="6" t="n"/>
+      <c r="AE207" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF207" s="6" t="n"/>
       <c r="AG207" s="6" t="n"/>
       <c r="AH207" s="6" t="n"/>
@@ -15269,7 +16093,11 @@
       <c r="AB208" s="71" t="n"/>
       <c r="AC208" s="71" t="n"/>
       <c r="AD208" s="71" t="n"/>
-      <c r="AE208" s="6" t="n"/>
+      <c r="AE208" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF208" s="6" t="n"/>
       <c r="AG208" s="6" t="n"/>
       <c r="AH208" s="6" t="n"/>
@@ -15337,7 +16165,11 @@
       <c r="AB209" s="71" t="n"/>
       <c r="AC209" s="71" t="n"/>
       <c r="AD209" s="71" t="n"/>
-      <c r="AE209" s="6" t="n"/>
+      <c r="AE209" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF209" s="6" t="n"/>
       <c r="AG209" s="6" t="n"/>
       <c r="AH209" s="6" t="n"/>
@@ -15405,7 +16237,11 @@
       <c r="AB210" s="71" t="n"/>
       <c r="AC210" s="71" t="n"/>
       <c r="AD210" s="71" t="n"/>
-      <c r="AE210" s="6" t="n"/>
+      <c r="AE210" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF210" s="6" t="n"/>
       <c r="AG210" s="6" t="n"/>
       <c r="AH210" s="6" t="n"/>
@@ -15473,7 +16309,11 @@
       <c r="AB211" s="71" t="n"/>
       <c r="AC211" s="71" t="n"/>
       <c r="AD211" s="71" t="n"/>
-      <c r="AE211" s="6" t="n"/>
+      <c r="AE211" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF211" s="6" t="n"/>
       <c r="AG211" s="6" t="n"/>
       <c r="AH211" s="6" t="n"/>
@@ -15541,7 +16381,11 @@
       <c r="AB212" s="71" t="n"/>
       <c r="AC212" s="71" t="n"/>
       <c r="AD212" s="71" t="n"/>
-      <c r="AE212" s="6" t="n"/>
+      <c r="AE212" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF212" s="6" t="n"/>
       <c r="AG212" s="6" t="n"/>
       <c r="AH212" s="6" t="n"/>
@@ -15609,7 +16453,11 @@
       <c r="AB213" s="71" t="n"/>
       <c r="AC213" s="71" t="n"/>
       <c r="AD213" s="71" t="n"/>
-      <c r="AE213" s="6" t="n"/>
+      <c r="AE213" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF213" s="6" t="n"/>
       <c r="AG213" s="6" t="n"/>
       <c r="AH213" s="6" t="n"/>
@@ -15677,7 +16525,11 @@
       <c r="AB214" s="71" t="n"/>
       <c r="AC214" s="71" t="n"/>
       <c r="AD214" s="71" t="n"/>
-      <c r="AE214" s="6" t="n"/>
+      <c r="AE214" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF214" s="6" t="n"/>
       <c r="AG214" s="6" t="n"/>
       <c r="AH214" s="6" t="n"/>
@@ -15745,7 +16597,11 @@
       <c r="AB215" s="71" t="n"/>
       <c r="AC215" s="71" t="n"/>
       <c r="AD215" s="71" t="n"/>
-      <c r="AE215" s="6" t="n"/>
+      <c r="AE215" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF215" s="6" t="n"/>
       <c r="AG215" s="6" t="n"/>
       <c r="AH215" s="6" t="n"/>
@@ -15813,7 +16669,11 @@
       <c r="AB216" s="71" t="n"/>
       <c r="AC216" s="71" t="n"/>
       <c r="AD216" s="71" t="n"/>
-      <c r="AE216" s="6" t="n"/>
+      <c r="AE216" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF216" s="6" t="n"/>
       <c r="AG216" s="6" t="n"/>
       <c r="AH216" s="6" t="n"/>
@@ -15881,7 +16741,11 @@
       <c r="AB217" s="71" t="n"/>
       <c r="AC217" s="71" t="n"/>
       <c r="AD217" s="71" t="n"/>
-      <c r="AE217" s="6" t="n"/>
+      <c r="AE217" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF217" s="6" t="n"/>
       <c r="AG217" s="6" t="n"/>
       <c r="AH217" s="6" t="n"/>
@@ -15949,7 +16813,11 @@
       <c r="AB218" s="71" t="n"/>
       <c r="AC218" s="71" t="n"/>
       <c r="AD218" s="71" t="n"/>
-      <c r="AE218" s="6" t="n"/>
+      <c r="AE218" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF218" s="6" t="n"/>
       <c r="AG218" s="6" t="n"/>
       <c r="AH218" s="6" t="n"/>
@@ -16017,7 +16885,11 @@
       <c r="AB219" s="71" t="n"/>
       <c r="AC219" s="71" t="n"/>
       <c r="AD219" s="71" t="n"/>
-      <c r="AE219" s="6" t="n"/>
+      <c r="AE219" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF219" s="6" t="n"/>
       <c r="AG219" s="6" t="n"/>
       <c r="AH219" s="6" t="n"/>
@@ -16085,7 +16957,11 @@
       <c r="AB220" s="71" t="n"/>
       <c r="AC220" s="71" t="n"/>
       <c r="AD220" s="71" t="n"/>
-      <c r="AE220" s="6" t="n"/>
+      <c r="AE220" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF220" s="6" t="n"/>
       <c r="AG220" s="6" t="n"/>
       <c r="AH220" s="6" t="n"/>
@@ -16153,7 +17029,11 @@
       <c r="AB221" s="71" t="n"/>
       <c r="AC221" s="71" t="n"/>
       <c r="AD221" s="71" t="n"/>
-      <c r="AE221" s="6" t="n"/>
+      <c r="AE221" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF221" s="6" t="n"/>
       <c r="AG221" s="6" t="n"/>
       <c r="AH221" s="6" t="n"/>
@@ -16225,7 +17105,11 @@
       <c r="AB222" s="71" t="n"/>
       <c r="AC222" s="71" t="n"/>
       <c r="AD222" s="71" t="n"/>
-      <c r="AE222" s="6" t="n"/>
+      <c r="AE222" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF222" s="6" t="n"/>
       <c r="AG222" s="6" t="n"/>
       <c r="AH222" s="6" t="n"/>
@@ -16297,7 +17181,11 @@
       <c r="AB223" s="71" t="n"/>
       <c r="AC223" s="71" t="n"/>
       <c r="AD223" s="71" t="n"/>
-      <c r="AE223" s="6" t="n"/>
+      <c r="AE223" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF223" s="6" t="n"/>
       <c r="AG223" s="6" t="n"/>
       <c r="AH223" s="6" t="n"/>

--- a/Шаблон ЛМК проф ОПО — Машково и Руднево.xlsx
+++ b/Шаблон ЛМК проф ОПО — Машково и Руднево.xlsx
@@ -17207,37 +17207,57 @@
       <c r="AX223" s="6" t="n"/>
     </row>
     <row r="224" ht="12.75" customHeight="1" s="30">
-      <c r="A224" s="63" t="n"/>
-      <c r="B224" s="64" t="n"/>
-      <c r="C224" s="36" t="n"/>
-      <c r="D224" s="56" t="n"/>
-      <c r="E224" s="36" t="n"/>
-      <c r="F224" s="35" t="n"/>
-      <c r="G224" s="65" t="n"/>
-      <c r="H224" s="66" t="n"/>
-      <c r="I224" s="64" t="n"/>
-      <c r="J224" s="66" t="n"/>
-      <c r="K224" s="35" t="n"/>
-      <c r="L224" s="35" t="n"/>
-      <c r="M224" s="35" t="n"/>
-      <c r="N224" s="35" t="n"/>
-      <c r="O224" s="36" t="n"/>
-      <c r="P224" s="36" t="n"/>
-      <c r="Q224" s="36" t="n"/>
-      <c r="R224" s="36" t="n"/>
-      <c r="S224" s="36" t="n"/>
-      <c r="T224" s="36" t="n"/>
-      <c r="U224" s="36" t="n"/>
-      <c r="V224" s="36" t="n"/>
-      <c r="W224" s="36" t="n"/>
-      <c r="X224" s="36" t="n"/>
-      <c r="Y224" s="36" t="n"/>
-      <c r="Z224" s="36" t="n"/>
-      <c r="AA224" s="36" t="n"/>
-      <c r="AB224" s="36" t="n"/>
-      <c r="AC224" s="36" t="n"/>
-      <c r="AD224" s="35" t="n"/>
-      <c r="AE224" s="6" t="n"/>
+      <c r="A224" s="67" t="inlineStr">
+        <is>
+          <t>Максимов Юрий Анатольевич</t>
+        </is>
+      </c>
+      <c r="B224" s="68" t="n"/>
+      <c r="C224" s="69" t="n"/>
+      <c r="D224" s="70" t="n"/>
+      <c r="E224" s="71" t="n"/>
+      <c r="F224" s="72" t="n"/>
+      <c r="G224" s="73" t="inlineStr">
+        <is>
+          <t>п.4.3.1, п.4.4, п.4.7, п.4.8, п.5.1, п.6.1</t>
+        </is>
+      </c>
+      <c r="H224" s="71" t="n"/>
+      <c r="I224" s="74" t="inlineStr">
+        <is>
+          <t>Инженер-программист станков с ЧПУ 2 категории</t>
+        </is>
+      </c>
+      <c r="J224" s="74" t="inlineStr">
+        <is>
+          <t>Мебельный участок МШ</t>
+        </is>
+      </c>
+      <c r="K224" s="75" t="n"/>
+      <c r="L224" s="76" t="n"/>
+      <c r="M224" s="77" t="n"/>
+      <c r="N224" s="77" t="n"/>
+      <c r="O224" s="71" t="n"/>
+      <c r="P224" s="71" t="n"/>
+      <c r="Q224" s="70" t="n"/>
+      <c r="R224" s="71" t="n"/>
+      <c r="S224" s="71" t="n"/>
+      <c r="T224" s="71" t="n"/>
+      <c r="U224" s="77" t="n"/>
+      <c r="V224" s="71" t="n"/>
+      <c r="W224" s="71" t="n"/>
+      <c r="X224" s="70" t="n"/>
+      <c r="Y224" s="71" t="n"/>
+      <c r="Z224" s="71" t="n"/>
+      <c r="AA224" s="71" t="n"/>
+      <c r="AB224" s="71" t="n"/>
+      <c r="AC224" s="71" t="n"/>
+      <c r="AD224" s="71" t="n"/>
+      <c r="AE224" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF224" s="6" t="n"/>
       <c r="AG224" s="6" t="n"/>
       <c r="AH224" s="6" t="n"/>
@@ -17259,37 +17279,57 @@
       <c r="AX224" s="6" t="n"/>
     </row>
     <row r="225" ht="12.75" customHeight="1" s="30">
-      <c r="A225" s="63" t="n"/>
-      <c r="B225" s="64" t="n"/>
-      <c r="C225" s="36" t="n"/>
-      <c r="D225" s="56" t="n"/>
-      <c r="E225" s="36" t="n"/>
-      <c r="F225" s="35" t="n"/>
-      <c r="G225" s="65" t="n"/>
-      <c r="H225" s="66" t="n"/>
-      <c r="I225" s="64" t="n"/>
-      <c r="J225" s="66" t="n"/>
-      <c r="K225" s="35" t="n"/>
-      <c r="L225" s="35" t="n"/>
-      <c r="M225" s="35" t="n"/>
-      <c r="N225" s="35" t="n"/>
-      <c r="O225" s="36" t="n"/>
-      <c r="P225" s="36" t="n"/>
-      <c r="Q225" s="36" t="n"/>
-      <c r="R225" s="36" t="n"/>
-      <c r="S225" s="36" t="n"/>
-      <c r="T225" s="36" t="n"/>
-      <c r="U225" s="36" t="n"/>
-      <c r="V225" s="36" t="n"/>
-      <c r="W225" s="36" t="n"/>
-      <c r="X225" s="36" t="n"/>
-      <c r="Y225" s="36" t="n"/>
-      <c r="Z225" s="36" t="n"/>
-      <c r="AA225" s="36" t="n"/>
-      <c r="AB225" s="36" t="n"/>
-      <c r="AC225" s="36" t="n"/>
-      <c r="AD225" s="35" t="n"/>
-      <c r="AE225" s="6" t="n"/>
+      <c r="A225" s="67" t="inlineStr">
+        <is>
+          <t>Чусов Иван Леонидович</t>
+        </is>
+      </c>
+      <c r="B225" s="68" t="n"/>
+      <c r="C225" s="69" t="n"/>
+      <c r="D225" s="70" t="n"/>
+      <c r="E225" s="71" t="n"/>
+      <c r="F225" s="72" t="n"/>
+      <c r="G225" s="73" t="inlineStr">
+        <is>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+        </is>
+      </c>
+      <c r="H225" s="71" t="n"/>
+      <c r="I225" s="74" t="inlineStr">
+        <is>
+          <t>Техник-сборщик 2 разряда</t>
+        </is>
+      </c>
+      <c r="J225" s="74" t="inlineStr">
+        <is>
+          <t>Мебельный участок (МШ н/д)</t>
+        </is>
+      </c>
+      <c r="K225" s="75" t="n"/>
+      <c r="L225" s="76" t="n"/>
+      <c r="M225" s="77" t="n"/>
+      <c r="N225" s="77" t="n"/>
+      <c r="O225" s="71" t="n"/>
+      <c r="P225" s="71" t="n"/>
+      <c r="Q225" s="70" t="n"/>
+      <c r="R225" s="71" t="n"/>
+      <c r="S225" s="71" t="n"/>
+      <c r="T225" s="71" t="n"/>
+      <c r="U225" s="77" t="n"/>
+      <c r="V225" s="71" t="n"/>
+      <c r="W225" s="71" t="n"/>
+      <c r="X225" s="70" t="n"/>
+      <c r="Y225" s="71" t="n"/>
+      <c r="Z225" s="71" t="n"/>
+      <c r="AA225" s="71" t="n"/>
+      <c r="AB225" s="71" t="n"/>
+      <c r="AC225" s="71" t="n"/>
+      <c r="AD225" s="71" t="n"/>
+      <c r="AE225" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF225" s="6" t="n"/>
       <c r="AG225" s="6" t="n"/>
       <c r="AH225" s="6" t="n"/>
@@ -17311,37 +17351,57 @@
       <c r="AX225" s="6" t="n"/>
     </row>
     <row r="226" ht="12.75" customHeight="1" s="30">
-      <c r="A226" s="63" t="n"/>
-      <c r="B226" s="64" t="n"/>
-      <c r="C226" s="36" t="n"/>
-      <c r="D226" s="56" t="n"/>
-      <c r="E226" s="36" t="n"/>
-      <c r="F226" s="35" t="n"/>
-      <c r="G226" s="65" t="n"/>
-      <c r="H226" s="66" t="n"/>
-      <c r="I226" s="64" t="n"/>
-      <c r="J226" s="66" t="n"/>
-      <c r="K226" s="35" t="n"/>
-      <c r="L226" s="35" t="n"/>
-      <c r="M226" s="35" t="n"/>
-      <c r="N226" s="35" t="n"/>
-      <c r="O226" s="36" t="n"/>
-      <c r="P226" s="36" t="n"/>
-      <c r="Q226" s="36" t="n"/>
-      <c r="R226" s="36" t="n"/>
-      <c r="S226" s="36" t="n"/>
-      <c r="T226" s="36" t="n"/>
-      <c r="U226" s="36" t="n"/>
-      <c r="V226" s="36" t="n"/>
-      <c r="W226" s="36" t="n"/>
-      <c r="X226" s="36" t="n"/>
-      <c r="Y226" s="36" t="n"/>
-      <c r="Z226" s="36" t="n"/>
-      <c r="AA226" s="36" t="n"/>
-      <c r="AB226" s="36" t="n"/>
-      <c r="AC226" s="36" t="n"/>
-      <c r="AD226" s="35" t="n"/>
-      <c r="AE226" s="6" t="n"/>
+      <c r="A226" s="67" t="inlineStr">
+        <is>
+          <t>Гимадиев Евгений Искандерович</t>
+        </is>
+      </c>
+      <c r="B226" s="68" t="n"/>
+      <c r="C226" s="69" t="n"/>
+      <c r="D226" s="70" t="n"/>
+      <c r="E226" s="71" t="n"/>
+      <c r="F226" s="72" t="n"/>
+      <c r="G226" s="73" t="inlineStr">
+        <is>
+          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
+        </is>
+      </c>
+      <c r="H226" s="71" t="n"/>
+      <c r="I226" s="74" t="inlineStr">
+        <is>
+          <t>Техник 3 разряда</t>
+        </is>
+      </c>
+      <c r="J226" s="74" t="inlineStr">
+        <is>
+          <t>Участок декоративной отделки (МШ н/д)</t>
+        </is>
+      </c>
+      <c r="K226" s="75" t="n"/>
+      <c r="L226" s="76" t="n"/>
+      <c r="M226" s="77" t="n"/>
+      <c r="N226" s="77" t="n"/>
+      <c r="O226" s="71" t="n"/>
+      <c r="P226" s="71" t="n"/>
+      <c r="Q226" s="70" t="n"/>
+      <c r="R226" s="71" t="n"/>
+      <c r="S226" s="71" t="n"/>
+      <c r="T226" s="71" t="n"/>
+      <c r="U226" s="77" t="n"/>
+      <c r="V226" s="71" t="n"/>
+      <c r="W226" s="71" t="n"/>
+      <c r="X226" s="70" t="n"/>
+      <c r="Y226" s="71" t="n"/>
+      <c r="Z226" s="71" t="n"/>
+      <c r="AA226" s="71" t="n"/>
+      <c r="AB226" s="71" t="n"/>
+      <c r="AC226" s="71" t="n"/>
+      <c r="AD226" s="71" t="n"/>
+      <c r="AE226" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF226" s="6" t="n"/>
       <c r="AG226" s="6" t="n"/>
       <c r="AH226" s="6" t="n"/>
@@ -17363,37 +17423,57 @@
       <c r="AX226" s="6" t="n"/>
     </row>
     <row r="227" ht="12.75" customHeight="1" s="30">
-      <c r="A227" s="63" t="n"/>
-      <c r="B227" s="64" t="n"/>
-      <c r="C227" s="36" t="n"/>
-      <c r="D227" s="56" t="n"/>
-      <c r="E227" s="36" t="n"/>
-      <c r="F227" s="35" t="n"/>
-      <c r="G227" s="65" t="n"/>
-      <c r="H227" s="66" t="n"/>
-      <c r="I227" s="64" t="n"/>
-      <c r="J227" s="66" t="n"/>
-      <c r="K227" s="35" t="n"/>
-      <c r="L227" s="35" t="n"/>
-      <c r="M227" s="35" t="n"/>
-      <c r="N227" s="35" t="n"/>
-      <c r="O227" s="36" t="n"/>
-      <c r="P227" s="36" t="n"/>
-      <c r="Q227" s="36" t="n"/>
-      <c r="R227" s="36" t="n"/>
-      <c r="S227" s="36" t="n"/>
-      <c r="T227" s="36" t="n"/>
-      <c r="U227" s="36" t="n"/>
-      <c r="V227" s="36" t="n"/>
-      <c r="W227" s="36" t="n"/>
-      <c r="X227" s="36" t="n"/>
-      <c r="Y227" s="36" t="n"/>
-      <c r="Z227" s="36" t="n"/>
-      <c r="AA227" s="36" t="n"/>
-      <c r="AB227" s="36" t="n"/>
-      <c r="AC227" s="36" t="n"/>
-      <c r="AD227" s="35" t="n"/>
-      <c r="AE227" s="6" t="n"/>
+      <c r="A227" s="67" t="inlineStr">
+        <is>
+          <t>Тишин Алексей Владимирович</t>
+        </is>
+      </c>
+      <c r="B227" s="68" t="n"/>
+      <c r="C227" s="69" t="n"/>
+      <c r="D227" s="70" t="n"/>
+      <c r="E227" s="71" t="n"/>
+      <c r="F227" s="72" t="n"/>
+      <c r="G227" s="73" t="inlineStr">
+        <is>
+          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
+        </is>
+      </c>
+      <c r="H227" s="71" t="n"/>
+      <c r="I227" s="74" t="inlineStr">
+        <is>
+          <t>Техник 3 разряда</t>
+        </is>
+      </c>
+      <c r="J227" s="74" t="inlineStr">
+        <is>
+          <t>Участок декоративной отделки (МШ н/д)</t>
+        </is>
+      </c>
+      <c r="K227" s="75" t="n"/>
+      <c r="L227" s="76" t="n"/>
+      <c r="M227" s="77" t="n"/>
+      <c r="N227" s="77" t="n"/>
+      <c r="O227" s="71" t="n"/>
+      <c r="P227" s="71" t="n"/>
+      <c r="Q227" s="70" t="n"/>
+      <c r="R227" s="71" t="n"/>
+      <c r="S227" s="71" t="n"/>
+      <c r="T227" s="71" t="n"/>
+      <c r="U227" s="77" t="n"/>
+      <c r="V227" s="71" t="n"/>
+      <c r="W227" s="71" t="n"/>
+      <c r="X227" s="70" t="n"/>
+      <c r="Y227" s="71" t="n"/>
+      <c r="Z227" s="71" t="n"/>
+      <c r="AA227" s="71" t="n"/>
+      <c r="AB227" s="71" t="n"/>
+      <c r="AC227" s="71" t="n"/>
+      <c r="AD227" s="71" t="n"/>
+      <c r="AE227" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF227" s="6" t="n"/>
       <c r="AG227" s="6" t="n"/>
       <c r="AH227" s="6" t="n"/>
@@ -17415,37 +17495,57 @@
       <c r="AX227" s="6" t="n"/>
     </row>
     <row r="228" ht="12.75" customHeight="1" s="30">
-      <c r="A228" s="63" t="n"/>
-      <c r="B228" s="64" t="n"/>
-      <c r="C228" s="36" t="n"/>
-      <c r="D228" s="56" t="n"/>
-      <c r="E228" s="36" t="n"/>
-      <c r="F228" s="35" t="n"/>
-      <c r="G228" s="65" t="n"/>
-      <c r="H228" s="66" t="n"/>
-      <c r="I228" s="64" t="n"/>
-      <c r="J228" s="66" t="n"/>
-      <c r="K228" s="35" t="n"/>
-      <c r="L228" s="35" t="n"/>
-      <c r="M228" s="35" t="n"/>
-      <c r="N228" s="35" t="n"/>
-      <c r="O228" s="36" t="n"/>
-      <c r="P228" s="36" t="n"/>
-      <c r="Q228" s="36" t="n"/>
-      <c r="R228" s="36" t="n"/>
-      <c r="S228" s="36" t="n"/>
-      <c r="T228" s="36" t="n"/>
-      <c r="U228" s="36" t="n"/>
-      <c r="V228" s="36" t="n"/>
-      <c r="W228" s="36" t="n"/>
-      <c r="X228" s="36" t="n"/>
-      <c r="Y228" s="36" t="n"/>
-      <c r="Z228" s="36" t="n"/>
-      <c r="AA228" s="36" t="n"/>
-      <c r="AB228" s="36" t="n"/>
-      <c r="AC228" s="36" t="n"/>
-      <c r="AD228" s="35" t="n"/>
-      <c r="AE228" s="6" t="n"/>
+      <c r="A228" s="67" t="inlineStr">
+        <is>
+          <t>Евменчук Елизавета Александровна</t>
+        </is>
+      </c>
+      <c r="B228" s="68" t="n"/>
+      <c r="C228" s="69" t="n"/>
+      <c r="D228" s="70" t="n"/>
+      <c r="E228" s="71" t="n"/>
+      <c r="F228" s="72" t="n"/>
+      <c r="G228" s="73" t="inlineStr">
+        <is>
+          <t>п.4.4, п.5.1, п.6.2</t>
+        </is>
+      </c>
+      <c r="H228" s="71" t="n"/>
+      <c r="I228" s="74" t="inlineStr">
+        <is>
+          <t>Кладовщик</t>
+        </is>
+      </c>
+      <c r="J228" s="74" t="inlineStr">
+        <is>
+          <t>Склад МШ</t>
+        </is>
+      </c>
+      <c r="K228" s="75" t="n"/>
+      <c r="L228" s="76" t="n"/>
+      <c r="M228" s="77" t="n"/>
+      <c r="N228" s="77" t="n"/>
+      <c r="O228" s="71" t="n"/>
+      <c r="P228" s="71" t="n"/>
+      <c r="Q228" s="70" t="n"/>
+      <c r="R228" s="71" t="n"/>
+      <c r="S228" s="71" t="n"/>
+      <c r="T228" s="71" t="n"/>
+      <c r="U228" s="77" t="n"/>
+      <c r="V228" s="71" t="n"/>
+      <c r="W228" s="71" t="n"/>
+      <c r="X228" s="70" t="n"/>
+      <c r="Y228" s="71" t="n"/>
+      <c r="Z228" s="71" t="n"/>
+      <c r="AA228" s="71" t="n"/>
+      <c r="AB228" s="71" t="n"/>
+      <c r="AC228" s="71" t="n"/>
+      <c r="AD228" s="71" t="n"/>
+      <c r="AE228" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF228" s="6" t="n"/>
       <c r="AG228" s="6" t="n"/>
       <c r="AH228" s="6" t="n"/>
@@ -17467,37 +17567,57 @@
       <c r="AX228" s="6" t="n"/>
     </row>
     <row r="229" ht="12.75" customHeight="1" s="30">
-      <c r="A229" s="63" t="n"/>
-      <c r="B229" s="64" t="n"/>
-      <c r="C229" s="36" t="n"/>
-      <c r="D229" s="56" t="n"/>
-      <c r="E229" s="36" t="n"/>
-      <c r="F229" s="35" t="n"/>
-      <c r="G229" s="65" t="n"/>
-      <c r="H229" s="66" t="n"/>
-      <c r="I229" s="64" t="n"/>
-      <c r="J229" s="66" t="n"/>
-      <c r="K229" s="35" t="n"/>
-      <c r="L229" s="35" t="n"/>
-      <c r="M229" s="35" t="n"/>
-      <c r="N229" s="35" t="n"/>
-      <c r="O229" s="36" t="n"/>
-      <c r="P229" s="36" t="n"/>
-      <c r="Q229" s="36" t="n"/>
-      <c r="R229" s="36" t="n"/>
-      <c r="S229" s="36" t="n"/>
-      <c r="T229" s="36" t="n"/>
-      <c r="U229" s="36" t="n"/>
-      <c r="V229" s="36" t="n"/>
-      <c r="W229" s="36" t="n"/>
-      <c r="X229" s="36" t="n"/>
-      <c r="Y229" s="36" t="n"/>
-      <c r="Z229" s="36" t="n"/>
-      <c r="AA229" s="36" t="n"/>
-      <c r="AB229" s="36" t="n"/>
-      <c r="AC229" s="36" t="n"/>
-      <c r="AD229" s="35" t="n"/>
-      <c r="AE229" s="6" t="n"/>
+      <c r="A229" s="67" t="inlineStr">
+        <is>
+          <t>Картузов Павел Борисович</t>
+        </is>
+      </c>
+      <c r="B229" s="68" t="n"/>
+      <c r="C229" s="69" t="n"/>
+      <c r="D229" s="70" t="n"/>
+      <c r="E229" s="71" t="n"/>
+      <c r="F229" s="72" t="n"/>
+      <c r="G229" s="73" t="inlineStr">
+        <is>
+          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
+        </is>
+      </c>
+      <c r="H229" s="71" t="n"/>
+      <c r="I229" s="74" t="inlineStr">
+        <is>
+          <t>Сборщик стеклопластиковых изделий 3 разряда</t>
+        </is>
+      </c>
+      <c r="J229" s="74" t="inlineStr">
+        <is>
+          <t>Мебельный участок МШ</t>
+        </is>
+      </c>
+      <c r="K229" s="75" t="n"/>
+      <c r="L229" s="76" t="n"/>
+      <c r="M229" s="77" t="n"/>
+      <c r="N229" s="77" t="n"/>
+      <c r="O229" s="71" t="n"/>
+      <c r="P229" s="71" t="n"/>
+      <c r="Q229" s="70" t="n"/>
+      <c r="R229" s="71" t="n"/>
+      <c r="S229" s="71" t="n"/>
+      <c r="T229" s="71" t="n"/>
+      <c r="U229" s="77" t="n"/>
+      <c r="V229" s="71" t="n"/>
+      <c r="W229" s="71" t="n"/>
+      <c r="X229" s="70" t="n"/>
+      <c r="Y229" s="71" t="n"/>
+      <c r="Z229" s="71" t="n"/>
+      <c r="AA229" s="71" t="n"/>
+      <c r="AB229" s="71" t="n"/>
+      <c r="AC229" s="71" t="n"/>
+      <c r="AD229" s="71" t="n"/>
+      <c r="AE229" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF229" s="6" t="n"/>
       <c r="AG229" s="6" t="n"/>
       <c r="AH229" s="6" t="n"/>
@@ -17519,37 +17639,57 @@
       <c r="AX229" s="6" t="n"/>
     </row>
     <row r="230" ht="12.75" customHeight="1" s="30">
-      <c r="A230" s="63" t="n"/>
-      <c r="B230" s="64" t="n"/>
-      <c r="C230" s="36" t="n"/>
-      <c r="D230" s="56" t="n"/>
-      <c r="E230" s="36" t="n"/>
-      <c r="F230" s="35" t="n"/>
-      <c r="G230" s="65" t="n"/>
-      <c r="H230" s="66" t="n"/>
-      <c r="I230" s="64" t="n"/>
-      <c r="J230" s="66" t="n"/>
-      <c r="K230" s="35" t="n"/>
-      <c r="L230" s="35" t="n"/>
-      <c r="M230" s="35" t="n"/>
-      <c r="N230" s="35" t="n"/>
-      <c r="O230" s="36" t="n"/>
-      <c r="P230" s="36" t="n"/>
-      <c r="Q230" s="36" t="n"/>
-      <c r="R230" s="36" t="n"/>
-      <c r="S230" s="36" t="n"/>
-      <c r="T230" s="36" t="n"/>
-      <c r="U230" s="36" t="n"/>
-      <c r="V230" s="36" t="n"/>
-      <c r="W230" s="36" t="n"/>
-      <c r="X230" s="36" t="n"/>
-      <c r="Y230" s="36" t="n"/>
-      <c r="Z230" s="36" t="n"/>
-      <c r="AA230" s="36" t="n"/>
-      <c r="AB230" s="36" t="n"/>
-      <c r="AC230" s="36" t="n"/>
-      <c r="AD230" s="35" t="n"/>
-      <c r="AE230" s="6" t="n"/>
+      <c r="A230" s="67" t="inlineStr">
+        <is>
+          <t>Каретников Роман Григорьевич</t>
+        </is>
+      </c>
+      <c r="B230" s="68" t="n"/>
+      <c r="C230" s="69" t="n"/>
+      <c r="D230" s="70" t="n"/>
+      <c r="E230" s="71" t="n"/>
+      <c r="F230" s="72" t="n"/>
+      <c r="G230" s="73" t="inlineStr">
+        <is>
+          <t>п.1.14.2, п.1.36, п.1.37.1, п.1.45.1, п.1.45.2, п.1.50, п.4.3.1, п.4.4, п.5.1, п.17</t>
+        </is>
+      </c>
+      <c r="H230" s="71" t="n"/>
+      <c r="I230" s="74" t="inlineStr">
+        <is>
+          <t>Техник 3 разряда</t>
+        </is>
+      </c>
+      <c r="J230" s="74" t="inlineStr">
+        <is>
+          <t>Участок декоративной отделки МШ</t>
+        </is>
+      </c>
+      <c r="K230" s="75" t="n"/>
+      <c r="L230" s="76" t="n"/>
+      <c r="M230" s="77" t="n"/>
+      <c r="N230" s="77" t="n"/>
+      <c r="O230" s="71" t="n"/>
+      <c r="P230" s="71" t="n"/>
+      <c r="Q230" s="70" t="n"/>
+      <c r="R230" s="71" t="n"/>
+      <c r="S230" s="71" t="n"/>
+      <c r="T230" s="71" t="n"/>
+      <c r="U230" s="77" t="n"/>
+      <c r="V230" s="71" t="n"/>
+      <c r="W230" s="71" t="n"/>
+      <c r="X230" s="70" t="n"/>
+      <c r="Y230" s="71" t="n"/>
+      <c r="Z230" s="71" t="n"/>
+      <c r="AA230" s="71" t="n"/>
+      <c r="AB230" s="71" t="n"/>
+      <c r="AC230" s="71" t="n"/>
+      <c r="AD230" s="71" t="n"/>
+      <c r="AE230" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF230" s="6" t="n"/>
       <c r="AG230" s="6" t="n"/>
       <c r="AH230" s="6" t="n"/>
@@ -17571,37 +17711,57 @@
       <c r="AX230" s="6" t="n"/>
     </row>
     <row r="231" ht="12.75" customHeight="1" s="30">
-      <c r="A231" s="63" t="n"/>
-      <c r="B231" s="64" t="n"/>
-      <c r="C231" s="36" t="n"/>
-      <c r="D231" s="56" t="n"/>
-      <c r="E231" s="36" t="n"/>
-      <c r="F231" s="35" t="n"/>
-      <c r="G231" s="65" t="n"/>
-      <c r="H231" s="66" t="n"/>
-      <c r="I231" s="64" t="n"/>
-      <c r="J231" s="66" t="n"/>
-      <c r="K231" s="35" t="n"/>
-      <c r="L231" s="35" t="n"/>
-      <c r="M231" s="35" t="n"/>
-      <c r="N231" s="35" t="n"/>
-      <c r="O231" s="36" t="n"/>
-      <c r="P231" s="36" t="n"/>
-      <c r="Q231" s="36" t="n"/>
-      <c r="R231" s="36" t="n"/>
-      <c r="S231" s="36" t="n"/>
-      <c r="T231" s="36" t="n"/>
-      <c r="U231" s="36" t="n"/>
-      <c r="V231" s="36" t="n"/>
-      <c r="W231" s="36" t="n"/>
-      <c r="X231" s="36" t="n"/>
-      <c r="Y231" s="36" t="n"/>
-      <c r="Z231" s="36" t="n"/>
-      <c r="AA231" s="36" t="n"/>
-      <c r="AB231" s="36" t="n"/>
-      <c r="AC231" s="36" t="n"/>
-      <c r="AD231" s="35" t="n"/>
-      <c r="AE231" s="6" t="n"/>
+      <c r="A231" s="67" t="inlineStr">
+        <is>
+          <t>Дубинкин Александр Сергеевич</t>
+        </is>
+      </c>
+      <c r="B231" s="68" t="n"/>
+      <c r="C231" s="69" t="n"/>
+      <c r="D231" s="70" t="n"/>
+      <c r="E231" s="71" t="n"/>
+      <c r="F231" s="72" t="n"/>
+      <c r="G231" s="73" t="inlineStr">
+        <is>
+          <t>п.4.4, п.5.1, п.5.2</t>
+        </is>
+      </c>
+      <c r="H231" s="71" t="n"/>
+      <c r="I231" s="74" t="inlineStr">
+        <is>
+          <t>Мастер участка</t>
+        </is>
+      </c>
+      <c r="J231" s="74" t="inlineStr">
+        <is>
+          <t>Механический участок МШ</t>
+        </is>
+      </c>
+      <c r="K231" s="75" t="n"/>
+      <c r="L231" s="76" t="n"/>
+      <c r="M231" s="77" t="n"/>
+      <c r="N231" s="77" t="n"/>
+      <c r="O231" s="71" t="n"/>
+      <c r="P231" s="71" t="n"/>
+      <c r="Q231" s="70" t="n"/>
+      <c r="R231" s="71" t="n"/>
+      <c r="S231" s="71" t="n"/>
+      <c r="T231" s="71" t="n"/>
+      <c r="U231" s="77" t="n"/>
+      <c r="V231" s="71" t="n"/>
+      <c r="W231" s="71" t="n"/>
+      <c r="X231" s="70" t="n"/>
+      <c r="Y231" s="71" t="n"/>
+      <c r="Z231" s="71" t="n"/>
+      <c r="AA231" s="71" t="n"/>
+      <c r="AB231" s="71" t="n"/>
+      <c r="AC231" s="71" t="n"/>
+      <c r="AD231" s="71" t="n"/>
+      <c r="AE231" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF231" s="6" t="n"/>
       <c r="AG231" s="6" t="n"/>
       <c r="AH231" s="6" t="n"/>
@@ -17623,37 +17783,57 @@
       <c r="AX231" s="6" t="n"/>
     </row>
     <row r="232" ht="12.75" customHeight="1" s="30">
-      <c r="A232" s="63" t="n"/>
-      <c r="B232" s="64" t="n"/>
-      <c r="C232" s="36" t="n"/>
-      <c r="D232" s="56" t="n"/>
-      <c r="E232" s="36" t="n"/>
-      <c r="F232" s="35" t="n"/>
-      <c r="G232" s="65" t="n"/>
-      <c r="H232" s="66" t="n"/>
-      <c r="I232" s="64" t="n"/>
-      <c r="J232" s="66" t="n"/>
-      <c r="K232" s="35" t="n"/>
-      <c r="L232" s="35" t="n"/>
-      <c r="M232" s="35" t="n"/>
-      <c r="N232" s="35" t="n"/>
-      <c r="O232" s="36" t="n"/>
-      <c r="P232" s="36" t="n"/>
-      <c r="Q232" s="36" t="n"/>
-      <c r="R232" s="36" t="n"/>
-      <c r="S232" s="36" t="n"/>
-      <c r="T232" s="36" t="n"/>
-      <c r="U232" s="36" t="n"/>
-      <c r="V232" s="36" t="n"/>
-      <c r="W232" s="36" t="n"/>
-      <c r="X232" s="36" t="n"/>
-      <c r="Y232" s="36" t="n"/>
-      <c r="Z232" s="36" t="n"/>
-      <c r="AA232" s="36" t="n"/>
-      <c r="AB232" s="36" t="n"/>
-      <c r="AC232" s="36" t="n"/>
-      <c r="AD232" s="35" t="n"/>
-      <c r="AE232" s="6" t="n"/>
+      <c r="A232" s="67" t="inlineStr">
+        <is>
+          <t>Иванов Юрий Сергеевич</t>
+        </is>
+      </c>
+      <c r="B232" s="68" t="n"/>
+      <c r="C232" s="69" t="n"/>
+      <c r="D232" s="70" t="n"/>
+      <c r="E232" s="71" t="n"/>
+      <c r="F232" s="72" t="n"/>
+      <c r="G232" s="73" t="inlineStr">
+        <is>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+        </is>
+      </c>
+      <c r="H232" s="71" t="n"/>
+      <c r="I232" s="74" t="inlineStr">
+        <is>
+          <t>Оператор станков с ЧПУ 4 разряда</t>
+        </is>
+      </c>
+      <c r="J232" s="74" t="inlineStr">
+        <is>
+          <t>Механический участок МШ</t>
+        </is>
+      </c>
+      <c r="K232" s="75" t="n"/>
+      <c r="L232" s="76" t="n"/>
+      <c r="M232" s="77" t="n"/>
+      <c r="N232" s="77" t="n"/>
+      <c r="O232" s="71" t="n"/>
+      <c r="P232" s="71" t="n"/>
+      <c r="Q232" s="70" t="n"/>
+      <c r="R232" s="71" t="n"/>
+      <c r="S232" s="71" t="n"/>
+      <c r="T232" s="71" t="n"/>
+      <c r="U232" s="77" t="n"/>
+      <c r="V232" s="71" t="n"/>
+      <c r="W232" s="71" t="n"/>
+      <c r="X232" s="70" t="n"/>
+      <c r="Y232" s="71" t="n"/>
+      <c r="Z232" s="71" t="n"/>
+      <c r="AA232" s="71" t="n"/>
+      <c r="AB232" s="71" t="n"/>
+      <c r="AC232" s="71" t="n"/>
+      <c r="AD232" s="71" t="n"/>
+      <c r="AE232" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF232" s="6" t="n"/>
       <c r="AG232" s="6" t="n"/>
       <c r="AH232" s="6" t="n"/>
@@ -17675,37 +17855,57 @@
       <c r="AX232" s="6" t="n"/>
     </row>
     <row r="233" ht="12.75" customHeight="1" s="30">
-      <c r="A233" s="63" t="n"/>
-      <c r="B233" s="64" t="n"/>
-      <c r="C233" s="36" t="n"/>
-      <c r="D233" s="56" t="n"/>
-      <c r="E233" s="36" t="n"/>
-      <c r="F233" s="35" t="n"/>
-      <c r="G233" s="65" t="n"/>
-      <c r="H233" s="66" t="n"/>
-      <c r="I233" s="64" t="n"/>
-      <c r="J233" s="66" t="n"/>
-      <c r="K233" s="35" t="n"/>
-      <c r="L233" s="35" t="n"/>
-      <c r="M233" s="35" t="n"/>
-      <c r="N233" s="35" t="n"/>
-      <c r="O233" s="36" t="n"/>
-      <c r="P233" s="36" t="n"/>
-      <c r="Q233" s="36" t="n"/>
-      <c r="R233" s="36" t="n"/>
-      <c r="S233" s="36" t="n"/>
-      <c r="T233" s="36" t="n"/>
-      <c r="U233" s="36" t="n"/>
-      <c r="V233" s="36" t="n"/>
-      <c r="W233" s="36" t="n"/>
-      <c r="X233" s="36" t="n"/>
-      <c r="Y233" s="36" t="n"/>
-      <c r="Z233" s="36" t="n"/>
-      <c r="AA233" s="36" t="n"/>
-      <c r="AB233" s="36" t="n"/>
-      <c r="AC233" s="36" t="n"/>
-      <c r="AD233" s="35" t="n"/>
-      <c r="AE233" s="6" t="n"/>
+      <c r="A233" s="67" t="inlineStr">
+        <is>
+          <t>Серебреников Артем Андреевич</t>
+        </is>
+      </c>
+      <c r="B233" s="68" t="n"/>
+      <c r="C233" s="69" t="n"/>
+      <c r="D233" s="70" t="n"/>
+      <c r="E233" s="71" t="n"/>
+      <c r="F233" s="72" t="n"/>
+      <c r="G233" s="73" t="inlineStr">
+        <is>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+        </is>
+      </c>
+      <c r="H233" s="71" t="n"/>
+      <c r="I233" s="74" t="inlineStr">
+        <is>
+          <t>Оператор станков с ЧПУ 3 разряда</t>
+        </is>
+      </c>
+      <c r="J233" s="74" t="inlineStr">
+        <is>
+          <t>Механический участок МШ</t>
+        </is>
+      </c>
+      <c r="K233" s="75" t="n"/>
+      <c r="L233" s="76" t="n"/>
+      <c r="M233" s="77" t="n"/>
+      <c r="N233" s="77" t="n"/>
+      <c r="O233" s="71" t="n"/>
+      <c r="P233" s="71" t="n"/>
+      <c r="Q233" s="70" t="n"/>
+      <c r="R233" s="71" t="n"/>
+      <c r="S233" s="71" t="n"/>
+      <c r="T233" s="71" t="n"/>
+      <c r="U233" s="77" t="n"/>
+      <c r="V233" s="71" t="n"/>
+      <c r="W233" s="71" t="n"/>
+      <c r="X233" s="70" t="n"/>
+      <c r="Y233" s="71" t="n"/>
+      <c r="Z233" s="71" t="n"/>
+      <c r="AA233" s="71" t="n"/>
+      <c r="AB233" s="71" t="n"/>
+      <c r="AC233" s="71" t="n"/>
+      <c r="AD233" s="71" t="n"/>
+      <c r="AE233" s="71" t="inlineStr">
+        <is>
+          <t>Машково</t>
+        </is>
+      </c>
       <c r="AF233" s="6" t="n"/>
       <c r="AG233" s="6" t="n"/>
       <c r="AH233" s="6" t="n"/>
@@ -17727,37 +17927,57 @@
       <c r="AX233" s="6" t="n"/>
     </row>
     <row r="234" ht="12.75" customHeight="1" s="30">
-      <c r="A234" s="63" t="n"/>
-      <c r="B234" s="64" t="n"/>
-      <c r="C234" s="36" t="n"/>
-      <c r="D234" s="56" t="n"/>
-      <c r="E234" s="36" t="n"/>
-      <c r="F234" s="35" t="n"/>
-      <c r="G234" s="65" t="n"/>
-      <c r="H234" s="66" t="n"/>
-      <c r="I234" s="64" t="n"/>
-      <c r="J234" s="66" t="n"/>
-      <c r="K234" s="35" t="n"/>
-      <c r="L234" s="35" t="n"/>
-      <c r="M234" s="35" t="n"/>
-      <c r="N234" s="35" t="n"/>
-      <c r="O234" s="36" t="n"/>
-      <c r="P234" s="36" t="n"/>
-      <c r="Q234" s="36" t="n"/>
-      <c r="R234" s="36" t="n"/>
-      <c r="S234" s="36" t="n"/>
-      <c r="T234" s="36" t="n"/>
-      <c r="U234" s="36" t="n"/>
-      <c r="V234" s="36" t="n"/>
-      <c r="W234" s="36" t="n"/>
-      <c r="X234" s="36" t="n"/>
-      <c r="Y234" s="36" t="n"/>
-      <c r="Z234" s="36" t="n"/>
-      <c r="AA234" s="36" t="n"/>
-      <c r="AB234" s="36" t="n"/>
-      <c r="AC234" s="36" t="n"/>
-      <c r="AD234" s="35" t="n"/>
-      <c r="AE234" s="6" t="n"/>
+      <c r="A234" s="67" t="inlineStr">
+        <is>
+          <t>Галимзянова Гузель Раисовна</t>
+        </is>
+      </c>
+      <c r="B234" s="68" t="n"/>
+      <c r="C234" s="69" t="n"/>
+      <c r="D234" s="70" t="n"/>
+      <c r="E234" s="71" t="n"/>
+      <c r="F234" s="72" t="n"/>
+      <c r="G234" s="73" t="inlineStr">
+        <is>
+          <t>п.4.4, п.5.1, п.5.2</t>
+        </is>
+      </c>
+      <c r="H234" s="71" t="n"/>
+      <c r="I234" s="74" t="inlineStr">
+        <is>
+          <t>Специалист</t>
+        </is>
+      </c>
+      <c r="J234" s="74" t="inlineStr">
+        <is>
+          <t>Административно-хозяйственный отдел Р</t>
+        </is>
+      </c>
+      <c r="K234" s="75" t="n"/>
+      <c r="L234" s="76" t="n"/>
+      <c r="M234" s="77" t="n"/>
+      <c r="N234" s="77" t="n"/>
+      <c r="O234" s="71" t="n"/>
+      <c r="P234" s="71" t="n"/>
+      <c r="Q234" s="70" t="n"/>
+      <c r="R234" s="71" t="n"/>
+      <c r="S234" s="71" t="n"/>
+      <c r="T234" s="71" t="n"/>
+      <c r="U234" s="77" t="n"/>
+      <c r="V234" s="71" t="n"/>
+      <c r="W234" s="71" t="n"/>
+      <c r="X234" s="70" t="n"/>
+      <c r="Y234" s="71" t="n"/>
+      <c r="Z234" s="71" t="n"/>
+      <c r="AA234" s="71" t="n"/>
+      <c r="AB234" s="71" t="n"/>
+      <c r="AC234" s="71" t="n"/>
+      <c r="AD234" s="71" t="n"/>
+      <c r="AE234" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF234" s="6" t="n"/>
       <c r="AG234" s="6" t="n"/>
       <c r="AH234" s="6" t="n"/>
@@ -17779,37 +17999,57 @@
       <c r="AX234" s="6" t="n"/>
     </row>
     <row r="235" ht="12.75" customHeight="1" s="30">
-      <c r="A235" s="63" t="n"/>
-      <c r="B235" s="64" t="n"/>
-      <c r="C235" s="36" t="n"/>
-      <c r="D235" s="56" t="n"/>
-      <c r="E235" s="36" t="n"/>
-      <c r="F235" s="35" t="n"/>
-      <c r="G235" s="65" t="n"/>
-      <c r="H235" s="66" t="n"/>
-      <c r="I235" s="64" t="n"/>
-      <c r="J235" s="66" t="n"/>
-      <c r="K235" s="35" t="n"/>
-      <c r="L235" s="35" t="n"/>
-      <c r="M235" s="35" t="n"/>
-      <c r="N235" s="35" t="n"/>
-      <c r="O235" s="36" t="n"/>
-      <c r="P235" s="36" t="n"/>
-      <c r="Q235" s="36" t="n"/>
-      <c r="R235" s="36" t="n"/>
-      <c r="S235" s="36" t="n"/>
-      <c r="T235" s="36" t="n"/>
-      <c r="U235" s="36" t="n"/>
-      <c r="V235" s="36" t="n"/>
-      <c r="W235" s="36" t="n"/>
-      <c r="X235" s="36" t="n"/>
-      <c r="Y235" s="36" t="n"/>
-      <c r="Z235" s="36" t="n"/>
-      <c r="AA235" s="36" t="n"/>
-      <c r="AB235" s="36" t="n"/>
-      <c r="AC235" s="36" t="n"/>
-      <c r="AD235" s="35" t="n"/>
-      <c r="AE235" s="6" t="n"/>
+      <c r="A235" s="67" t="inlineStr">
+        <is>
+          <t>Донин Алексей Валентинович</t>
+        </is>
+      </c>
+      <c r="B235" s="68" t="n"/>
+      <c r="C235" s="69" t="n"/>
+      <c r="D235" s="70" t="n"/>
+      <c r="E235" s="71" t="n"/>
+      <c r="F235" s="72" t="n"/>
+      <c r="G235" s="73" t="inlineStr">
+        <is>
+          <t>п.4.3.1, п.4.4, п.4.7, п.4.8, п.5.1, п.6.1</t>
+        </is>
+      </c>
+      <c r="H235" s="71" t="n"/>
+      <c r="I235" s="74" t="inlineStr">
+        <is>
+          <t>Разнорабочий</t>
+        </is>
+      </c>
+      <c r="J235" s="74" t="inlineStr">
+        <is>
+          <t>Административно-хозяйственный отдел Р</t>
+        </is>
+      </c>
+      <c r="K235" s="75" t="n"/>
+      <c r="L235" s="76" t="n"/>
+      <c r="M235" s="77" t="n"/>
+      <c r="N235" s="77" t="n"/>
+      <c r="O235" s="71" t="n"/>
+      <c r="P235" s="71" t="n"/>
+      <c r="Q235" s="70" t="n"/>
+      <c r="R235" s="71" t="n"/>
+      <c r="S235" s="71" t="n"/>
+      <c r="T235" s="71" t="n"/>
+      <c r="U235" s="77" t="n"/>
+      <c r="V235" s="71" t="n"/>
+      <c r="W235" s="71" t="n"/>
+      <c r="X235" s="70" t="n"/>
+      <c r="Y235" s="71" t="n"/>
+      <c r="Z235" s="71" t="n"/>
+      <c r="AA235" s="71" t="n"/>
+      <c r="AB235" s="71" t="n"/>
+      <c r="AC235" s="71" t="n"/>
+      <c r="AD235" s="71" t="n"/>
+      <c r="AE235" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF235" s="6" t="n"/>
       <c r="AG235" s="6" t="n"/>
       <c r="AH235" s="6" t="n"/>
@@ -17831,37 +18071,57 @@
       <c r="AX235" s="6" t="n"/>
     </row>
     <row r="236" ht="12.75" customHeight="1" s="30">
-      <c r="A236" s="63" t="n"/>
-      <c r="B236" s="64" t="n"/>
-      <c r="C236" s="36" t="n"/>
-      <c r="D236" s="56" t="n"/>
-      <c r="E236" s="36" t="n"/>
-      <c r="F236" s="35" t="n"/>
-      <c r="G236" s="65" t="n"/>
-      <c r="H236" s="66" t="n"/>
-      <c r="I236" s="64" t="n"/>
-      <c r="J236" s="66" t="n"/>
-      <c r="K236" s="35" t="n"/>
-      <c r="L236" s="35" t="n"/>
-      <c r="M236" s="35" t="n"/>
-      <c r="N236" s="35" t="n"/>
-      <c r="O236" s="36" t="n"/>
-      <c r="P236" s="36" t="n"/>
-      <c r="Q236" s="36" t="n"/>
-      <c r="R236" s="36" t="n"/>
-      <c r="S236" s="36" t="n"/>
-      <c r="T236" s="36" t="n"/>
-      <c r="U236" s="36" t="n"/>
-      <c r="V236" s="36" t="n"/>
-      <c r="W236" s="36" t="n"/>
-      <c r="X236" s="36" t="n"/>
-      <c r="Y236" s="36" t="n"/>
-      <c r="Z236" s="36" t="n"/>
-      <c r="AA236" s="36" t="n"/>
-      <c r="AB236" s="36" t="n"/>
-      <c r="AC236" s="36" t="n"/>
-      <c r="AD236" s="35" t="n"/>
-      <c r="AE236" s="6" t="n"/>
+      <c r="A236" s="67" t="inlineStr">
+        <is>
+          <t>Раззакова Светлана Владимировна</t>
+        </is>
+      </c>
+      <c r="B236" s="68" t="n"/>
+      <c r="C236" s="69" t="n"/>
+      <c r="D236" s="70" t="n"/>
+      <c r="E236" s="71" t="n"/>
+      <c r="F236" s="72" t="n"/>
+      <c r="G236" s="73" t="inlineStr">
+        <is>
+          <t>п.1.48, п.4.3.1, п.4.4, п.5.1</t>
+        </is>
+      </c>
+      <c r="H236" s="71" t="n"/>
+      <c r="I236" s="74" t="inlineStr">
+        <is>
+          <t>Уборщик производственных и служебных помещений</t>
+        </is>
+      </c>
+      <c r="J236" s="74" t="inlineStr">
+        <is>
+          <t>Административно-хозяйственный отдел Р</t>
+        </is>
+      </c>
+      <c r="K236" s="75" t="n"/>
+      <c r="L236" s="76" t="n"/>
+      <c r="M236" s="77" t="n"/>
+      <c r="N236" s="77" t="n"/>
+      <c r="O236" s="71" t="n"/>
+      <c r="P236" s="71" t="n"/>
+      <c r="Q236" s="70" t="n"/>
+      <c r="R236" s="71" t="n"/>
+      <c r="S236" s="71" t="n"/>
+      <c r="T236" s="71" t="n"/>
+      <c r="U236" s="77" t="n"/>
+      <c r="V236" s="71" t="n"/>
+      <c r="W236" s="71" t="n"/>
+      <c r="X236" s="70" t="n"/>
+      <c r="Y236" s="71" t="n"/>
+      <c r="Z236" s="71" t="n"/>
+      <c r="AA236" s="71" t="n"/>
+      <c r="AB236" s="71" t="n"/>
+      <c r="AC236" s="71" t="n"/>
+      <c r="AD236" s="71" t="n"/>
+      <c r="AE236" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF236" s="6" t="n"/>
       <c r="AG236" s="6" t="n"/>
       <c r="AH236" s="6" t="n"/>
@@ -17883,37 +18143,57 @@
       <c r="AX236" s="6" t="n"/>
     </row>
     <row r="237" ht="12.75" customHeight="1" s="30">
-      <c r="A237" s="63" t="n"/>
-      <c r="B237" s="64" t="n"/>
-      <c r="C237" s="36" t="n"/>
-      <c r="D237" s="56" t="n"/>
-      <c r="E237" s="36" t="n"/>
-      <c r="F237" s="35" t="n"/>
-      <c r="G237" s="65" t="n"/>
-      <c r="H237" s="66" t="n"/>
-      <c r="I237" s="64" t="n"/>
-      <c r="J237" s="66" t="n"/>
-      <c r="K237" s="35" t="n"/>
-      <c r="L237" s="35" t="n"/>
-      <c r="M237" s="35" t="n"/>
-      <c r="N237" s="35" t="n"/>
-      <c r="O237" s="36" t="n"/>
-      <c r="P237" s="36" t="n"/>
-      <c r="Q237" s="36" t="n"/>
-      <c r="R237" s="36" t="n"/>
-      <c r="S237" s="36" t="n"/>
-      <c r="T237" s="36" t="n"/>
-      <c r="U237" s="36" t="n"/>
-      <c r="V237" s="36" t="n"/>
-      <c r="W237" s="36" t="n"/>
-      <c r="X237" s="36" t="n"/>
-      <c r="Y237" s="36" t="n"/>
-      <c r="Z237" s="36" t="n"/>
-      <c r="AA237" s="36" t="n"/>
-      <c r="AB237" s="36" t="n"/>
-      <c r="AC237" s="36" t="n"/>
-      <c r="AD237" s="35" t="n"/>
-      <c r="AE237" s="6" t="n"/>
+      <c r="A237" s="67" t="inlineStr">
+        <is>
+          <t>Степанов Максим Анатольевич</t>
+        </is>
+      </c>
+      <c r="B237" s="68" t="n"/>
+      <c r="C237" s="69" t="n"/>
+      <c r="D237" s="70" t="n"/>
+      <c r="E237" s="71" t="n"/>
+      <c r="F237" s="72" t="n"/>
+      <c r="G237" s="73" t="inlineStr">
+        <is>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+        </is>
+      </c>
+      <c r="H237" s="71" t="n"/>
+      <c r="I237" s="74" t="inlineStr">
+        <is>
+          <t>Оператор станка с ЧПУ 4 разряда</t>
+        </is>
+      </c>
+      <c r="J237" s="74" t="inlineStr">
+        <is>
+          <t>Механический участок Р</t>
+        </is>
+      </c>
+      <c r="K237" s="75" t="n"/>
+      <c r="L237" s="76" t="n"/>
+      <c r="M237" s="77" t="n"/>
+      <c r="N237" s="77" t="n"/>
+      <c r="O237" s="71" t="n"/>
+      <c r="P237" s="71" t="n"/>
+      <c r="Q237" s="70" t="n"/>
+      <c r="R237" s="71" t="n"/>
+      <c r="S237" s="71" t="n"/>
+      <c r="T237" s="71" t="n"/>
+      <c r="U237" s="77" t="n"/>
+      <c r="V237" s="71" t="n"/>
+      <c r="W237" s="71" t="n"/>
+      <c r="X237" s="70" t="n"/>
+      <c r="Y237" s="71" t="n"/>
+      <c r="Z237" s="71" t="n"/>
+      <c r="AA237" s="71" t="n"/>
+      <c r="AB237" s="71" t="n"/>
+      <c r="AC237" s="71" t="n"/>
+      <c r="AD237" s="71" t="n"/>
+      <c r="AE237" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF237" s="6" t="n"/>
       <c r="AG237" s="6" t="n"/>
       <c r="AH237" s="6" t="n"/>
@@ -17935,37 +18215,57 @@
       <c r="AX237" s="6" t="n"/>
     </row>
     <row r="238" ht="12.75" customHeight="1" s="30">
-      <c r="A238" s="63" t="n"/>
-      <c r="B238" s="64" t="n"/>
-      <c r="C238" s="36" t="n"/>
-      <c r="D238" s="56" t="n"/>
-      <c r="E238" s="36" t="n"/>
-      <c r="F238" s="35" t="n"/>
-      <c r="G238" s="65" t="n"/>
-      <c r="H238" s="66" t="n"/>
-      <c r="I238" s="64" t="n"/>
-      <c r="J238" s="66" t="n"/>
-      <c r="K238" s="35" t="n"/>
-      <c r="L238" s="35" t="n"/>
-      <c r="M238" s="35" t="n"/>
-      <c r="N238" s="35" t="n"/>
-      <c r="O238" s="36" t="n"/>
-      <c r="P238" s="36" t="n"/>
-      <c r="Q238" s="36" t="n"/>
-      <c r="R238" s="36" t="n"/>
-      <c r="S238" s="36" t="n"/>
-      <c r="T238" s="36" t="n"/>
-      <c r="U238" s="36" t="n"/>
-      <c r="V238" s="36" t="n"/>
-      <c r="W238" s="36" t="n"/>
-      <c r="X238" s="36" t="n"/>
-      <c r="Y238" s="36" t="n"/>
-      <c r="Z238" s="36" t="n"/>
-      <c r="AA238" s="36" t="n"/>
-      <c r="AB238" s="36" t="n"/>
-      <c r="AC238" s="36" t="n"/>
-      <c r="AD238" s="35" t="n"/>
-      <c r="AE238" s="6" t="n"/>
+      <c r="A238" s="67" t="inlineStr">
+        <is>
+          <t>Мартынов Гавриил Викторович</t>
+        </is>
+      </c>
+      <c r="B238" s="68" t="n"/>
+      <c r="C238" s="69" t="n"/>
+      <c r="D238" s="70" t="n"/>
+      <c r="E238" s="71" t="n"/>
+      <c r="F238" s="72" t="n"/>
+      <c r="G238" s="73" t="inlineStr">
+        <is>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
+        </is>
+      </c>
+      <c r="H238" s="71" t="n"/>
+      <c r="I238" s="74" t="inlineStr">
+        <is>
+          <t>Слесарь-сборщик 3 разряда</t>
+        </is>
+      </c>
+      <c r="J238" s="74" t="inlineStr">
+        <is>
+          <t>Участок сборки Р</t>
+        </is>
+      </c>
+      <c r="K238" s="75" t="n"/>
+      <c r="L238" s="76" t="n"/>
+      <c r="M238" s="77" t="n"/>
+      <c r="N238" s="77" t="n"/>
+      <c r="O238" s="71" t="n"/>
+      <c r="P238" s="71" t="n"/>
+      <c r="Q238" s="70" t="n"/>
+      <c r="R238" s="71" t="n"/>
+      <c r="S238" s="71" t="n"/>
+      <c r="T238" s="71" t="n"/>
+      <c r="U238" s="77" t="n"/>
+      <c r="V238" s="71" t="n"/>
+      <c r="W238" s="71" t="n"/>
+      <c r="X238" s="70" t="n"/>
+      <c r="Y238" s="71" t="n"/>
+      <c r="Z238" s="71" t="n"/>
+      <c r="AA238" s="71" t="n"/>
+      <c r="AB238" s="71" t="n"/>
+      <c r="AC238" s="71" t="n"/>
+      <c r="AD238" s="71" t="n"/>
+      <c r="AE238" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF238" s="6" t="n"/>
       <c r="AG238" s="6" t="n"/>
       <c r="AH238" s="6" t="n"/>
@@ -17987,37 +18287,57 @@
       <c r="AX238" s="6" t="n"/>
     </row>
     <row r="239" ht="12.75" customHeight="1" s="30">
-      <c r="A239" s="63" t="n"/>
-      <c r="B239" s="64" t="n"/>
-      <c r="C239" s="36" t="n"/>
-      <c r="D239" s="56" t="n"/>
-      <c r="E239" s="36" t="n"/>
-      <c r="F239" s="35" t="n"/>
-      <c r="G239" s="65" t="n"/>
-      <c r="H239" s="66" t="n"/>
-      <c r="I239" s="64" t="n"/>
-      <c r="J239" s="66" t="n"/>
-      <c r="K239" s="35" t="n"/>
-      <c r="L239" s="35" t="n"/>
-      <c r="M239" s="35" t="n"/>
-      <c r="N239" s="35" t="n"/>
-      <c r="O239" s="36" t="n"/>
-      <c r="P239" s="36" t="n"/>
-      <c r="Q239" s="36" t="n"/>
-      <c r="R239" s="36" t="n"/>
-      <c r="S239" s="36" t="n"/>
-      <c r="T239" s="36" t="n"/>
-      <c r="U239" s="36" t="n"/>
-      <c r="V239" s="36" t="n"/>
-      <c r="W239" s="36" t="n"/>
-      <c r="X239" s="36" t="n"/>
-      <c r="Y239" s="36" t="n"/>
-      <c r="Z239" s="36" t="n"/>
-      <c r="AA239" s="36" t="n"/>
-      <c r="AB239" s="36" t="n"/>
-      <c r="AC239" s="36" t="n"/>
-      <c r="AD239" s="35" t="n"/>
-      <c r="AE239" s="6" t="n"/>
+      <c r="A239" s="67" t="inlineStr">
+        <is>
+          <t>Сабирова Альфия Фаузиевна</t>
+        </is>
+      </c>
+      <c r="B239" s="68" t="n"/>
+      <c r="C239" s="69" t="n"/>
+      <c r="D239" s="70" t="n"/>
+      <c r="E239" s="71" t="n"/>
+      <c r="F239" s="72" t="n"/>
+      <c r="G239" s="73" t="inlineStr">
+        <is>
+          <t>п.4.4, п.5.1, п.5.2</t>
+        </is>
+      </c>
+      <c r="H239" s="71" t="n"/>
+      <c r="I239" s="74" t="inlineStr">
+        <is>
+          <t>Диспетчер</t>
+        </is>
+      </c>
+      <c r="J239" s="74" t="inlineStr">
+        <is>
+          <t>Планово-диспетчерский отдел Р</t>
+        </is>
+      </c>
+      <c r="K239" s="75" t="n"/>
+      <c r="L239" s="76" t="n"/>
+      <c r="M239" s="77" t="n"/>
+      <c r="N239" s="77" t="n"/>
+      <c r="O239" s="71" t="n"/>
+      <c r="P239" s="71" t="n"/>
+      <c r="Q239" s="70" t="n"/>
+      <c r="R239" s="71" t="n"/>
+      <c r="S239" s="71" t="n"/>
+      <c r="T239" s="71" t="n"/>
+      <c r="U239" s="77" t="n"/>
+      <c r="V239" s="71" t="n"/>
+      <c r="W239" s="71" t="n"/>
+      <c r="X239" s="70" t="n"/>
+      <c r="Y239" s="71" t="n"/>
+      <c r="Z239" s="71" t="n"/>
+      <c r="AA239" s="71" t="n"/>
+      <c r="AB239" s="71" t="n"/>
+      <c r="AC239" s="71" t="n"/>
+      <c r="AD239" s="71" t="n"/>
+      <c r="AE239" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF239" s="6" t="n"/>
       <c r="AG239" s="6" t="n"/>
       <c r="AH239" s="6" t="n"/>
@@ -18039,37 +18359,57 @@
       <c r="AX239" s="6" t="n"/>
     </row>
     <row r="240" ht="12.75" customHeight="1" s="30">
-      <c r="A240" s="63" t="n"/>
-      <c r="B240" s="64" t="n"/>
-      <c r="C240" s="36" t="n"/>
-      <c r="D240" s="56" t="n"/>
-      <c r="E240" s="36" t="n"/>
-      <c r="F240" s="35" t="n"/>
-      <c r="G240" s="65" t="n"/>
-      <c r="H240" s="66" t="n"/>
-      <c r="I240" s="64" t="n"/>
-      <c r="J240" s="66" t="n"/>
-      <c r="K240" s="35" t="n"/>
-      <c r="L240" s="35" t="n"/>
-      <c r="M240" s="35" t="n"/>
-      <c r="N240" s="35" t="n"/>
-      <c r="O240" s="36" t="n"/>
-      <c r="P240" s="36" t="n"/>
-      <c r="Q240" s="36" t="n"/>
-      <c r="R240" s="36" t="n"/>
-      <c r="S240" s="36" t="n"/>
-      <c r="T240" s="36" t="n"/>
-      <c r="U240" s="36" t="n"/>
-      <c r="V240" s="36" t="n"/>
-      <c r="W240" s="36" t="n"/>
-      <c r="X240" s="36" t="n"/>
-      <c r="Y240" s="36" t="n"/>
-      <c r="Z240" s="36" t="n"/>
-      <c r="AA240" s="36" t="n"/>
-      <c r="AB240" s="36" t="n"/>
-      <c r="AC240" s="36" t="n"/>
-      <c r="AD240" s="35" t="n"/>
-      <c r="AE240" s="6" t="n"/>
+      <c r="A240" s="67" t="inlineStr">
+        <is>
+          <t>Трофимов Максим Михайлович</t>
+        </is>
+      </c>
+      <c r="B240" s="68" t="n"/>
+      <c r="C240" s="69" t="n"/>
+      <c r="D240" s="70" t="n"/>
+      <c r="E240" s="71" t="n"/>
+      <c r="F240" s="72" t="n"/>
+      <c r="G240" s="73" t="inlineStr">
+        <is>
+          <t>п.4.4, п.5.1, п.6.2</t>
+        </is>
+      </c>
+      <c r="H240" s="71" t="n"/>
+      <c r="I240" s="74" t="inlineStr">
+        <is>
+          <t>Кладовщик</t>
+        </is>
+      </c>
+      <c r="J240" s="74" t="inlineStr">
+        <is>
+          <t>Склад Р</t>
+        </is>
+      </c>
+      <c r="K240" s="75" t="n"/>
+      <c r="L240" s="76" t="n"/>
+      <c r="M240" s="77" t="n"/>
+      <c r="N240" s="77" t="n"/>
+      <c r="O240" s="71" t="n"/>
+      <c r="P240" s="71" t="n"/>
+      <c r="Q240" s="70" t="n"/>
+      <c r="R240" s="71" t="n"/>
+      <c r="S240" s="71" t="n"/>
+      <c r="T240" s="71" t="n"/>
+      <c r="U240" s="77" t="n"/>
+      <c r="V240" s="71" t="n"/>
+      <c r="W240" s="71" t="n"/>
+      <c r="X240" s="70" t="n"/>
+      <c r="Y240" s="71" t="n"/>
+      <c r="Z240" s="71" t="n"/>
+      <c r="AA240" s="71" t="n"/>
+      <c r="AB240" s="71" t="n"/>
+      <c r="AC240" s="71" t="n"/>
+      <c r="AD240" s="71" t="n"/>
+      <c r="AE240" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF240" s="6" t="n"/>
       <c r="AG240" s="6" t="n"/>
       <c r="AH240" s="6" t="n"/>
@@ -18091,37 +18431,57 @@
       <c r="AX240" s="6" t="n"/>
     </row>
     <row r="241" ht="12.75" customHeight="1" s="30">
-      <c r="A241" s="63" t="n"/>
-      <c r="B241" s="64" t="n"/>
-      <c r="C241" s="36" t="n"/>
-      <c r="D241" s="56" t="n"/>
-      <c r="E241" s="36" t="n"/>
-      <c r="F241" s="35" t="n"/>
-      <c r="G241" s="65" t="n"/>
-      <c r="H241" s="66" t="n"/>
-      <c r="I241" s="64" t="n"/>
-      <c r="J241" s="66" t="n"/>
-      <c r="K241" s="35" t="n"/>
-      <c r="L241" s="35" t="n"/>
-      <c r="M241" s="35" t="n"/>
-      <c r="N241" s="35" t="n"/>
-      <c r="O241" s="36" t="n"/>
-      <c r="P241" s="36" t="n"/>
-      <c r="Q241" s="36" t="n"/>
-      <c r="R241" s="36" t="n"/>
-      <c r="S241" s="36" t="n"/>
-      <c r="T241" s="36" t="n"/>
-      <c r="U241" s="36" t="n"/>
-      <c r="V241" s="36" t="n"/>
-      <c r="W241" s="36" t="n"/>
-      <c r="X241" s="36" t="n"/>
-      <c r="Y241" s="36" t="n"/>
-      <c r="Z241" s="36" t="n"/>
-      <c r="AA241" s="36" t="n"/>
-      <c r="AB241" s="36" t="n"/>
-      <c r="AC241" s="36" t="n"/>
-      <c r="AD241" s="35" t="n"/>
-      <c r="AE241" s="6" t="n"/>
+      <c r="A241" s="67" t="inlineStr">
+        <is>
+          <t>Гагарин Алексей Владимирович</t>
+        </is>
+      </c>
+      <c r="B241" s="68" t="n"/>
+      <c r="C241" s="69" t="n"/>
+      <c r="D241" s="70" t="n"/>
+      <c r="E241" s="71" t="n"/>
+      <c r="F241" s="72" t="n"/>
+      <c r="G241" s="73" t="inlineStr">
+        <is>
+          <t>п.4.4, п.5.1, п.6.2</t>
+        </is>
+      </c>
+      <c r="H241" s="71" t="n"/>
+      <c r="I241" s="74" t="inlineStr">
+        <is>
+          <t>Кладовщик-комплектовщик</t>
+        </is>
+      </c>
+      <c r="J241" s="74" t="inlineStr">
+        <is>
+          <t>Склад Р</t>
+        </is>
+      </c>
+      <c r="K241" s="75" t="n"/>
+      <c r="L241" s="76" t="n"/>
+      <c r="M241" s="77" t="n"/>
+      <c r="N241" s="77" t="n"/>
+      <c r="O241" s="71" t="n"/>
+      <c r="P241" s="71" t="n"/>
+      <c r="Q241" s="70" t="n"/>
+      <c r="R241" s="71" t="n"/>
+      <c r="S241" s="71" t="n"/>
+      <c r="T241" s="71" t="n"/>
+      <c r="U241" s="77" t="n"/>
+      <c r="V241" s="71" t="n"/>
+      <c r="W241" s="71" t="n"/>
+      <c r="X241" s="70" t="n"/>
+      <c r="Y241" s="71" t="n"/>
+      <c r="Z241" s="71" t="n"/>
+      <c r="AA241" s="71" t="n"/>
+      <c r="AB241" s="71" t="n"/>
+      <c r="AC241" s="71" t="n"/>
+      <c r="AD241" s="71" t="n"/>
+      <c r="AE241" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF241" s="6" t="n"/>
       <c r="AG241" s="6" t="n"/>
       <c r="AH241" s="6" t="n"/>
@@ -18143,37 +18503,57 @@
       <c r="AX241" s="6" t="n"/>
     </row>
     <row r="242" ht="12.75" customHeight="1" s="30">
-      <c r="A242" s="63" t="n"/>
-      <c r="B242" s="64" t="n"/>
-      <c r="C242" s="36" t="n"/>
-      <c r="D242" s="56" t="n"/>
-      <c r="E242" s="36" t="n"/>
-      <c r="F242" s="35" t="n"/>
-      <c r="G242" s="65" t="n"/>
-      <c r="H242" s="66" t="n"/>
-      <c r="I242" s="64" t="n"/>
-      <c r="J242" s="66" t="n"/>
-      <c r="K242" s="35" t="n"/>
-      <c r="L242" s="35" t="n"/>
-      <c r="M242" s="35" t="n"/>
-      <c r="N242" s="35" t="n"/>
-      <c r="O242" s="36" t="n"/>
-      <c r="P242" s="36" t="n"/>
-      <c r="Q242" s="36" t="n"/>
-      <c r="R242" s="36" t="n"/>
-      <c r="S242" s="36" t="n"/>
-      <c r="T242" s="36" t="n"/>
-      <c r="U242" s="36" t="n"/>
-      <c r="V242" s="36" t="n"/>
-      <c r="W242" s="36" t="n"/>
-      <c r="X242" s="36" t="n"/>
-      <c r="Y242" s="36" t="n"/>
-      <c r="Z242" s="36" t="n"/>
-      <c r="AA242" s="36" t="n"/>
-      <c r="AB242" s="36" t="n"/>
-      <c r="AC242" s="36" t="n"/>
-      <c r="AD242" s="35" t="n"/>
-      <c r="AE242" s="6" t="n"/>
+      <c r="A242" s="67" t="inlineStr">
+        <is>
+          <t>Иванов Дмитрий Сергеевич</t>
+        </is>
+      </c>
+      <c r="B242" s="68" t="n"/>
+      <c r="C242" s="69" t="n"/>
+      <c r="D242" s="70" t="n"/>
+      <c r="E242" s="71" t="n"/>
+      <c r="F242" s="72" t="n"/>
+      <c r="G242" s="73" t="inlineStr">
+        <is>
+          <t>п.4.4, п.5.1, п.6.2</t>
+        </is>
+      </c>
+      <c r="H242" s="71" t="n"/>
+      <c r="I242" s="74" t="inlineStr">
+        <is>
+          <t>Кладовщик-комплектовщик</t>
+        </is>
+      </c>
+      <c r="J242" s="74" t="inlineStr">
+        <is>
+          <t>Склад Р</t>
+        </is>
+      </c>
+      <c r="K242" s="75" t="n"/>
+      <c r="L242" s="76" t="n"/>
+      <c r="M242" s="77" t="n"/>
+      <c r="N242" s="77" t="n"/>
+      <c r="O242" s="71" t="n"/>
+      <c r="P242" s="71" t="n"/>
+      <c r="Q242" s="70" t="n"/>
+      <c r="R242" s="71" t="n"/>
+      <c r="S242" s="71" t="n"/>
+      <c r="T242" s="71" t="n"/>
+      <c r="U242" s="77" t="n"/>
+      <c r="V242" s="71" t="n"/>
+      <c r="W242" s="71" t="n"/>
+      <c r="X242" s="70" t="n"/>
+      <c r="Y242" s="71" t="n"/>
+      <c r="Z242" s="71" t="n"/>
+      <c r="AA242" s="71" t="n"/>
+      <c r="AB242" s="71" t="n"/>
+      <c r="AC242" s="71" t="n"/>
+      <c r="AD242" s="71" t="n"/>
+      <c r="AE242" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF242" s="6" t="n"/>
       <c r="AG242" s="6" t="n"/>
       <c r="AH242" s="6" t="n"/>
@@ -18195,37 +18575,57 @@
       <c r="AX242" s="6" t="n"/>
     </row>
     <row r="243" ht="12.75" customHeight="1" s="30">
-      <c r="A243" s="63" t="n"/>
-      <c r="B243" s="64" t="n"/>
-      <c r="C243" s="36" t="n"/>
-      <c r="D243" s="56" t="n"/>
-      <c r="E243" s="36" t="n"/>
-      <c r="F243" s="35" t="n"/>
-      <c r="G243" s="65" t="n"/>
-      <c r="H243" s="66" t="n"/>
-      <c r="I243" s="64" t="n"/>
-      <c r="J243" s="66" t="n"/>
-      <c r="K243" s="35" t="n"/>
-      <c r="L243" s="35" t="n"/>
-      <c r="M243" s="35" t="n"/>
-      <c r="N243" s="35" t="n"/>
-      <c r="O243" s="36" t="n"/>
-      <c r="P243" s="36" t="n"/>
-      <c r="Q243" s="36" t="n"/>
-      <c r="R243" s="36" t="n"/>
-      <c r="S243" s="36" t="n"/>
-      <c r="T243" s="36" t="n"/>
-      <c r="U243" s="36" t="n"/>
-      <c r="V243" s="36" t="n"/>
-      <c r="W243" s="36" t="n"/>
-      <c r="X243" s="36" t="n"/>
-      <c r="Y243" s="36" t="n"/>
-      <c r="Z243" s="36" t="n"/>
-      <c r="AA243" s="36" t="n"/>
-      <c r="AB243" s="36" t="n"/>
-      <c r="AC243" s="36" t="n"/>
-      <c r="AD243" s="35" t="n"/>
-      <c r="AE243" s="6" t="n"/>
+      <c r="A243" s="67" t="inlineStr">
+        <is>
+          <t>Поляков Александр Валентинович</t>
+        </is>
+      </c>
+      <c r="B243" s="68" t="n"/>
+      <c r="C243" s="69" t="n"/>
+      <c r="D243" s="70" t="n"/>
+      <c r="E243" s="71" t="n"/>
+      <c r="F243" s="72" t="n"/>
+      <c r="G243" s="73" t="inlineStr">
+        <is>
+          <t>п.4.4, п.5.1, п.6.2</t>
+        </is>
+      </c>
+      <c r="H243" s="71" t="n"/>
+      <c r="I243" s="74" t="inlineStr">
+        <is>
+          <t>Кладовщик-комплектовщик</t>
+        </is>
+      </c>
+      <c r="J243" s="74" t="inlineStr">
+        <is>
+          <t>Склад Р</t>
+        </is>
+      </c>
+      <c r="K243" s="75" t="n"/>
+      <c r="L243" s="76" t="n"/>
+      <c r="M243" s="77" t="n"/>
+      <c r="N243" s="77" t="n"/>
+      <c r="O243" s="71" t="n"/>
+      <c r="P243" s="71" t="n"/>
+      <c r="Q243" s="70" t="n"/>
+      <c r="R243" s="71" t="n"/>
+      <c r="S243" s="71" t="n"/>
+      <c r="T243" s="71" t="n"/>
+      <c r="U243" s="77" t="n"/>
+      <c r="V243" s="71" t="n"/>
+      <c r="W243" s="71" t="n"/>
+      <c r="X243" s="70" t="n"/>
+      <c r="Y243" s="71" t="n"/>
+      <c r="Z243" s="71" t="n"/>
+      <c r="AA243" s="71" t="n"/>
+      <c r="AB243" s="71" t="n"/>
+      <c r="AC243" s="71" t="n"/>
+      <c r="AD243" s="71" t="n"/>
+      <c r="AE243" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF243" s="6" t="n"/>
       <c r="AG243" s="6" t="n"/>
       <c r="AH243" s="6" t="n"/>
@@ -18247,37 +18647,57 @@
       <c r="AX243" s="6" t="n"/>
     </row>
     <row r="244" ht="12.75" customHeight="1" s="30">
-      <c r="A244" s="63" t="n"/>
-      <c r="B244" s="64" t="n"/>
-      <c r="C244" s="36" t="n"/>
-      <c r="D244" s="56" t="n"/>
-      <c r="E244" s="36" t="n"/>
-      <c r="F244" s="35" t="n"/>
-      <c r="G244" s="65" t="n"/>
-      <c r="H244" s="66" t="n"/>
-      <c r="I244" s="64" t="n"/>
-      <c r="J244" s="66" t="n"/>
-      <c r="K244" s="35" t="n"/>
-      <c r="L244" s="35" t="n"/>
-      <c r="M244" s="35" t="n"/>
-      <c r="N244" s="35" t="n"/>
-      <c r="O244" s="36" t="n"/>
-      <c r="P244" s="36" t="n"/>
-      <c r="Q244" s="36" t="n"/>
-      <c r="R244" s="36" t="n"/>
-      <c r="S244" s="36" t="n"/>
-      <c r="T244" s="36" t="n"/>
-      <c r="U244" s="36" t="n"/>
-      <c r="V244" s="36" t="n"/>
-      <c r="W244" s="36" t="n"/>
-      <c r="X244" s="36" t="n"/>
-      <c r="Y244" s="36" t="n"/>
-      <c r="Z244" s="36" t="n"/>
-      <c r="AA244" s="36" t="n"/>
-      <c r="AB244" s="36" t="n"/>
-      <c r="AC244" s="36" t="n"/>
-      <c r="AD244" s="35" t="n"/>
-      <c r="AE244" s="6" t="n"/>
+      <c r="A244" s="67" t="inlineStr">
+        <is>
+          <t>Козлов Никита Андреевич</t>
+        </is>
+      </c>
+      <c r="B244" s="68" t="n"/>
+      <c r="C244" s="69" t="n"/>
+      <c r="D244" s="70" t="n"/>
+      <c r="E244" s="71" t="n"/>
+      <c r="F244" s="72" t="n"/>
+      <c r="G244" s="73" t="inlineStr">
+        <is>
+          <t>п.4.4, п.5.1, п.5.2</t>
+        </is>
+      </c>
+      <c r="H244" s="71" t="n"/>
+      <c r="I244" s="74" t="inlineStr">
+        <is>
+          <t>Инженер 3 категории</t>
+        </is>
+      </c>
+      <c r="J244" s="74" t="inlineStr">
+        <is>
+          <t>Отдел технического контроля Р</t>
+        </is>
+      </c>
+      <c r="K244" s="75" t="n"/>
+      <c r="L244" s="76" t="n"/>
+      <c r="M244" s="77" t="n"/>
+      <c r="N244" s="77" t="n"/>
+      <c r="O244" s="71" t="n"/>
+      <c r="P244" s="71" t="n"/>
+      <c r="Q244" s="70" t="n"/>
+      <c r="R244" s="71" t="n"/>
+      <c r="S244" s="71" t="n"/>
+      <c r="T244" s="71" t="n"/>
+      <c r="U244" s="77" t="n"/>
+      <c r="V244" s="71" t="n"/>
+      <c r="W244" s="71" t="n"/>
+      <c r="X244" s="70" t="n"/>
+      <c r="Y244" s="71" t="n"/>
+      <c r="Z244" s="71" t="n"/>
+      <c r="AA244" s="71" t="n"/>
+      <c r="AB244" s="71" t="n"/>
+      <c r="AC244" s="71" t="n"/>
+      <c r="AD244" s="71" t="n"/>
+      <c r="AE244" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF244" s="6" t="n"/>
       <c r="AG244" s="6" t="n"/>
       <c r="AH244" s="6" t="n"/>
@@ -18299,37 +18719,57 @@
       <c r="AX244" s="6" t="n"/>
     </row>
     <row r="245" ht="12.75" customHeight="1" s="30">
-      <c r="A245" s="63" t="n"/>
-      <c r="B245" s="64" t="n"/>
-      <c r="C245" s="36" t="n"/>
-      <c r="D245" s="56" t="n"/>
-      <c r="E245" s="36" t="n"/>
-      <c r="F245" s="35" t="n"/>
-      <c r="G245" s="65" t="n"/>
-      <c r="H245" s="66" t="n"/>
-      <c r="I245" s="64" t="n"/>
-      <c r="J245" s="66" t="n"/>
-      <c r="K245" s="35" t="n"/>
-      <c r="L245" s="35" t="n"/>
-      <c r="M245" s="35" t="n"/>
-      <c r="N245" s="35" t="n"/>
-      <c r="O245" s="36" t="n"/>
-      <c r="P245" s="36" t="n"/>
-      <c r="Q245" s="36" t="n"/>
-      <c r="R245" s="36" t="n"/>
-      <c r="S245" s="36" t="n"/>
-      <c r="T245" s="36" t="n"/>
-      <c r="U245" s="36" t="n"/>
-      <c r="V245" s="36" t="n"/>
-      <c r="W245" s="36" t="n"/>
-      <c r="X245" s="36" t="n"/>
-      <c r="Y245" s="36" t="n"/>
-      <c r="Z245" s="36" t="n"/>
-      <c r="AA245" s="36" t="n"/>
-      <c r="AB245" s="36" t="n"/>
-      <c r="AC245" s="36" t="n"/>
-      <c r="AD245" s="35" t="n"/>
-      <c r="AE245" s="6" t="n"/>
+      <c r="A245" s="67" t="inlineStr">
+        <is>
+          <t>Елсуков Имант Арьевич</t>
+        </is>
+      </c>
+      <c r="B245" s="68" t="n"/>
+      <c r="C245" s="69" t="n"/>
+      <c r="D245" s="70" t="n"/>
+      <c r="E245" s="71" t="n"/>
+      <c r="F245" s="72" t="n"/>
+      <c r="G245" s="73" t="inlineStr">
+        <is>
+          <t>п.4.4, п.5.1, п.5.2</t>
+        </is>
+      </c>
+      <c r="H245" s="71" t="n"/>
+      <c r="I245" s="74" t="inlineStr">
+        <is>
+          <t>Инженер 2 категории</t>
+        </is>
+      </c>
+      <c r="J245" s="74" t="inlineStr">
+        <is>
+          <t>Отдел технического контроля Р</t>
+        </is>
+      </c>
+      <c r="K245" s="75" t="n"/>
+      <c r="L245" s="76" t="n"/>
+      <c r="M245" s="77" t="n"/>
+      <c r="N245" s="77" t="n"/>
+      <c r="O245" s="71" t="n"/>
+      <c r="P245" s="71" t="n"/>
+      <c r="Q245" s="70" t="n"/>
+      <c r="R245" s="71" t="n"/>
+      <c r="S245" s="71" t="n"/>
+      <c r="T245" s="71" t="n"/>
+      <c r="U245" s="77" t="n"/>
+      <c r="V245" s="71" t="n"/>
+      <c r="W245" s="71" t="n"/>
+      <c r="X245" s="70" t="n"/>
+      <c r="Y245" s="71" t="n"/>
+      <c r="Z245" s="71" t="n"/>
+      <c r="AA245" s="71" t="n"/>
+      <c r="AB245" s="71" t="n"/>
+      <c r="AC245" s="71" t="n"/>
+      <c r="AD245" s="71" t="n"/>
+      <c r="AE245" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF245" s="6" t="n"/>
       <c r="AG245" s="6" t="n"/>
       <c r="AH245" s="6" t="n"/>
@@ -18351,37 +18791,57 @@
       <c r="AX245" s="6" t="n"/>
     </row>
     <row r="246" ht="12.75" customHeight="1" s="30">
-      <c r="A246" s="63" t="n"/>
-      <c r="B246" s="64" t="n"/>
-      <c r="C246" s="36" t="n"/>
-      <c r="D246" s="56" t="n"/>
-      <c r="E246" s="36" t="n"/>
-      <c r="F246" s="35" t="n"/>
-      <c r="G246" s="65" t="n"/>
-      <c r="H246" s="66" t="n"/>
-      <c r="I246" s="64" t="n"/>
-      <c r="J246" s="66" t="n"/>
-      <c r="K246" s="35" t="n"/>
-      <c r="L246" s="35" t="n"/>
-      <c r="M246" s="35" t="n"/>
-      <c r="N246" s="35" t="n"/>
-      <c r="O246" s="36" t="n"/>
-      <c r="P246" s="36" t="n"/>
-      <c r="Q246" s="36" t="n"/>
-      <c r="R246" s="36" t="n"/>
-      <c r="S246" s="36" t="n"/>
-      <c r="T246" s="36" t="n"/>
-      <c r="U246" s="36" t="n"/>
-      <c r="V246" s="36" t="n"/>
-      <c r="W246" s="36" t="n"/>
-      <c r="X246" s="36" t="n"/>
-      <c r="Y246" s="36" t="n"/>
-      <c r="Z246" s="36" t="n"/>
-      <c r="AA246" s="36" t="n"/>
-      <c r="AB246" s="36" t="n"/>
-      <c r="AC246" s="36" t="n"/>
-      <c r="AD246" s="35" t="n"/>
-      <c r="AE246" s="6" t="n"/>
+      <c r="A246" s="67" t="inlineStr">
+        <is>
+          <t>Тверитин Сергей Алексеевич</t>
+        </is>
+      </c>
+      <c r="B246" s="68" t="n"/>
+      <c r="C246" s="69" t="n"/>
+      <c r="D246" s="70" t="n"/>
+      <c r="E246" s="71" t="n"/>
+      <c r="F246" s="72" t="n"/>
+      <c r="G246" s="73" t="inlineStr">
+        <is>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.4.6, п.5.1, п.6.2</t>
+        </is>
+      </c>
+      <c r="H246" s="71" t="n"/>
+      <c r="I246" s="74" t="inlineStr">
+        <is>
+          <t>Инженер-механик</t>
+        </is>
+      </c>
+      <c r="J246" s="74" t="inlineStr">
+        <is>
+          <t>Служба главного инженера Р</t>
+        </is>
+      </c>
+      <c r="K246" s="75" t="n"/>
+      <c r="L246" s="76" t="n"/>
+      <c r="M246" s="77" t="n"/>
+      <c r="N246" s="77" t="n"/>
+      <c r="O246" s="71" t="n"/>
+      <c r="P246" s="71" t="n"/>
+      <c r="Q246" s="70" t="n"/>
+      <c r="R246" s="71" t="n"/>
+      <c r="S246" s="71" t="n"/>
+      <c r="T246" s="71" t="n"/>
+      <c r="U246" s="77" t="n"/>
+      <c r="V246" s="71" t="n"/>
+      <c r="W246" s="71" t="n"/>
+      <c r="X246" s="70" t="n"/>
+      <c r="Y246" s="71" t="n"/>
+      <c r="Z246" s="71" t="n"/>
+      <c r="AA246" s="71" t="n"/>
+      <c r="AB246" s="71" t="n"/>
+      <c r="AC246" s="71" t="n"/>
+      <c r="AD246" s="71" t="n"/>
+      <c r="AE246" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF246" s="6" t="n"/>
       <c r="AG246" s="6" t="n"/>
       <c r="AH246" s="6" t="n"/>
@@ -18403,37 +18863,57 @@
       <c r="AX246" s="6" t="n"/>
     </row>
     <row r="247" ht="12.75" customHeight="1" s="30">
-      <c r="A247" s="63" t="n"/>
-      <c r="B247" s="64" t="n"/>
-      <c r="C247" s="36" t="n"/>
-      <c r="D247" s="56" t="n"/>
-      <c r="E247" s="36" t="n"/>
-      <c r="F247" s="35" t="n"/>
-      <c r="G247" s="65" t="n"/>
-      <c r="H247" s="66" t="n"/>
-      <c r="I247" s="64" t="n"/>
-      <c r="J247" s="66" t="n"/>
-      <c r="K247" s="35" t="n"/>
-      <c r="L247" s="35" t="n"/>
-      <c r="M247" s="35" t="n"/>
-      <c r="N247" s="35" t="n"/>
-      <c r="O247" s="36" t="n"/>
-      <c r="P247" s="36" t="n"/>
-      <c r="Q247" s="36" t="n"/>
-      <c r="R247" s="36" t="n"/>
-      <c r="S247" s="36" t="n"/>
-      <c r="T247" s="36" t="n"/>
-      <c r="U247" s="36" t="n"/>
-      <c r="V247" s="36" t="n"/>
-      <c r="W247" s="36" t="n"/>
-      <c r="X247" s="36" t="n"/>
-      <c r="Y247" s="36" t="n"/>
-      <c r="Z247" s="36" t="n"/>
-      <c r="AA247" s="36" t="n"/>
-      <c r="AB247" s="36" t="n"/>
-      <c r="AC247" s="36" t="n"/>
-      <c r="AD247" s="35" t="n"/>
-      <c r="AE247" s="6" t="n"/>
+      <c r="A247" s="67" t="inlineStr">
+        <is>
+          <t>Коровин Сергей Юрьевич</t>
+        </is>
+      </c>
+      <c r="B247" s="68" t="n"/>
+      <c r="C247" s="69" t="n"/>
+      <c r="D247" s="70" t="n"/>
+      <c r="E247" s="71" t="n"/>
+      <c r="F247" s="72" t="n"/>
+      <c r="G247" s="73" t="inlineStr">
+        <is>
+          <t>п.4.4, п.5.1, п.6.2</t>
+        </is>
+      </c>
+      <c r="H247" s="71" t="n"/>
+      <c r="I247" s="74" t="inlineStr">
+        <is>
+          <t>Кладовщик</t>
+        </is>
+      </c>
+      <c r="J247" s="74" t="inlineStr">
+        <is>
+          <t>Склад Р</t>
+        </is>
+      </c>
+      <c r="K247" s="75" t="n"/>
+      <c r="L247" s="76" t="n"/>
+      <c r="M247" s="77" t="n"/>
+      <c r="N247" s="77" t="n"/>
+      <c r="O247" s="71" t="n"/>
+      <c r="P247" s="71" t="n"/>
+      <c r="Q247" s="70" t="n"/>
+      <c r="R247" s="71" t="n"/>
+      <c r="S247" s="71" t="n"/>
+      <c r="T247" s="71" t="n"/>
+      <c r="U247" s="77" t="n"/>
+      <c r="V247" s="71" t="n"/>
+      <c r="W247" s="71" t="n"/>
+      <c r="X247" s="70" t="n"/>
+      <c r="Y247" s="71" t="n"/>
+      <c r="Z247" s="71" t="n"/>
+      <c r="AA247" s="71" t="n"/>
+      <c r="AB247" s="71" t="n"/>
+      <c r="AC247" s="71" t="n"/>
+      <c r="AD247" s="71" t="n"/>
+      <c r="AE247" s="71" t="inlineStr">
+        <is>
+          <t>Руднево</t>
+        </is>
+      </c>
       <c r="AF247" s="6" t="n"/>
       <c r="AG247" s="6" t="n"/>
       <c r="AH247" s="6" t="n"/>
